--- a/ch_02_pandas/ch_02_solution.xlsx
+++ b/ch_02_pandas/ch_02_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\python-in-excel-book-staging\new_datasets\ch_02_pandas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02_pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CF1EBA-D11D-47C9-B372-B1F4C2BBB242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2029E3-6D7B-4C54-8EFC-5ABA7277D8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nyc" sheetId="1" r:id="rId1"/>
@@ -49,11 +49,18 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
         </ext>
       </extLst>
     </bk>
@@ -63,9 +70,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="1">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
+    </bk>
+    <bk>
+      <rc t="2" v="1"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -967,9 +977,6 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -985,6 +992,9 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <font>
@@ -1160,30 +1170,36 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <rv s="0">
-    <v>0</v>
+    <v>14</v>
   </rv>
   <rv s="1">
-    <v>DataFrame</v>
-    <v>1</v>
     <v>0</v>
   </rv>
   <rv s="2">
+    <v>DataFrame</v>
+    <v>1</v>
+    <v>1</v>
+  </rv>
+  <rv s="3">
     <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
     <v>DataFrame</v>
     <v xml:space="preserve">     order_id        product         category  unit_price  quantity  \
 0    ORD-0001           Desk        Furniture       68.76         5   
 1    ORD-0002           Lamp        Furniture      115.20         7   
 2    ORD-0003           Lamp        Fur...</v>
-    <v>1</v>
+    <v>2</v>
     <v>2</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+  </s>
   <s t="_array">
     <k n="array" t="a"/>
   </s>
@@ -1249,7 +1265,7 @@
   <autoFilter ref="A1:C6" xr:uid="{A099DEF9-7300-4421-80EE-149706CE1CEA}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{4060128F-DD32-4555-9DB9-CA443A160D2A}" name="borough"/>
-    <tableColumn id="2" xr3:uid="{32E7E197-F690-4580-9F10-846DD215807D}" name="population" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{32E7E197-F690-4580-9F10-846DD215807D}" name="population" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{4D8417DA-D82A-4787-B91D-F9A344C39103}" name="land_area"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1257,7 +1273,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}" name="sales" displayName="sales" ref="A1:G201" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}" name="sales" displayName="sales" ref="A1:G201" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:G201" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{054A5DBB-1F62-4FF0-893D-CA3913FFC271}" name="order_id"/>
@@ -1579,19 +1595,13 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="str" cm="1">
-        <f t="array" ref="E1:H6">_xlfn._xlws.PY(0,0,nyc_pop[#All])</f>
-        <v>borough</v>
-      </c>
-      <c r="F1" s="5" t="str">
-        <v>population</v>
-      </c>
-      <c r="G1" s="5" t="str">
-        <v>land_area</v>
-      </c>
-      <c r="H1" s="5" t="str">
-        <v>density</v>
-      </c>
+      <c r="E1" cm="1">
+        <f t="array" aca="1" ref="E1" ca="1">_xlfn._xlws.PY(0,0,nyc_pop[#All])</f>
+        <v>0</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
@@ -1603,18 +1613,6 @@
       <c r="C2">
         <v>22.83</v>
       </c>
-      <c r="E2" t="str">
-        <v>Manhattan</v>
-      </c>
-      <c r="F2" s="5">
-        <v>1694251</v>
-      </c>
-      <c r="G2" s="5">
-        <v>22.83</v>
-      </c>
-      <c r="H2" s="5">
-        <v>74211.607533946561</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
@@ -1626,18 +1624,6 @@
       <c r="C3">
         <v>69.37</v>
       </c>
-      <c r="E3" t="str">
-        <v>Brooklyn</v>
-      </c>
-      <c r="F3" s="5">
-        <v>2736074</v>
-      </c>
-      <c r="G3" s="5">
-        <v>69.37</v>
-      </c>
-      <c r="H3" s="5">
-        <v>39441.747152947959</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
@@ -1649,18 +1635,6 @@
       <c r="C4">
         <v>108.53</v>
       </c>
-      <c r="E4" t="str">
-        <v>Queens</v>
-      </c>
-      <c r="F4" s="5">
-        <v>2405464</v>
-      </c>
-      <c r="G4" s="5">
-        <v>108.53</v>
-      </c>
-      <c r="H4" s="5">
-        <v>22164.046807334376</v>
-      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
@@ -1672,18 +1646,6 @@
       <c r="C5">
         <v>42.1</v>
       </c>
-      <c r="E5" t="str">
-        <v>Bronx</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1472654</v>
-      </c>
-      <c r="G5" s="5">
-        <v>42.1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>34979.904988123511</v>
-      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
@@ -1695,47 +1657,40 @@
       <c r="C6">
         <v>58.37</v>
       </c>
-      <c r="E6" t="str">
-        <v>Staten Island</v>
-      </c>
-      <c r="F6" s="5">
-        <v>495747</v>
-      </c>
-      <c r="G6" s="5">
-        <v>58.37</v>
-      </c>
-      <c r="H6" s="5">
-        <v>8493.1814288161731</v>
-      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.5">
       <c r="E8" t="str" cm="1">
-        <f t="array" ref="E8:E13">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
+        <f t="array" aca="1" ref="E8:E13" ca="1">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
         <v>population</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.5">
       <c r="E9">
+        <f ca="1"/>
         <v>1694251</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.5">
       <c r="E10">
+        <f ca="1"/>
         <v>2736074</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.5">
       <c r="E11">
+        <f ca="1"/>
         <v>2405464</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.5">
       <c r="E12">
+        <f ca="1"/>
         <v>1472654</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.5">
       <c r="E13">
+        <f ca="1"/>
         <v>495747</v>
       </c>
     </row>
@@ -6390,2596 +6345,3320 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A1" t="e" cm="1" vm="1">
-        <f t="array" ref="A1">_xlfn._xlws.PY(1,1,sales[#All])</f>
+      <c r="A1" t="e" cm="1" vm="2">
+        <f t="array" aca="1" ref="A1" ca="1">_xlfn._xlws.PY(1,1,sales[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A3" t="str" cm="1">
-        <f t="array" ref="A3:G8">_xlfn._xlws.PY(2,0)</f>
+        <f t="array" aca="1" ref="A3:G8" ca="1">_xlfn._xlws.PY(2,0)</f>
         <v>order_id</v>
       </c>
       <c r="B3" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="C3" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="D3" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="E3" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="F3" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="G3" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A4" t="str">
+        <f ca="1"/>
         <v>ORD-0001</v>
       </c>
       <c r="B4" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="C4" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="D4">
+        <f ca="1"/>
         <v>68.760000000000005</v>
       </c>
       <c r="E4">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="F4">
+        <f ca="1"/>
         <v>37</v>
       </c>
       <c r="G4" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A5" t="str">
+        <f ca="1"/>
         <v>ORD-0002</v>
       </c>
       <c r="B5" t="str">
+        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="C5" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="D5">
+        <f ca="1"/>
         <v>115.2</v>
       </c>
       <c r="E5">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="F5">
+        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="G5" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A6" t="str">
+        <f ca="1"/>
         <v>ORD-0003</v>
       </c>
       <c r="B6" t="str">
+        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="C6" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="D6">
+        <f ca="1"/>
         <v>69.900000000000006</v>
       </c>
       <c r="E6">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="F6">
+        <f ca="1"/>
         <v>63</v>
       </c>
       <c r="G6" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A7" t="str">
+        <f ca="1"/>
         <v>ORD-0004</v>
       </c>
       <c r="B7" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="C7" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="D7">
+        <f ca="1"/>
         <v>15.35</v>
       </c>
       <c r="E7">
+        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="F7">
+        <f ca="1"/>
         <v>32</v>
       </c>
       <c r="G7" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A8" t="str">
+        <f ca="1"/>
         <v>ORD-0005</v>
       </c>
       <c r="B8" t="str">
+        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="C8" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="D8">
+        <f ca="1"/>
         <v>479.68</v>
       </c>
       <c r="E8">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="F8">
+        <f ca="1"/>
         <v>28</v>
       </c>
       <c r="G8" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A10" t="str" cm="1">
-        <f t="array" ref="A10:H15">_xlfn._xlws.PY(3,0)</f>
+        <f t="array" aca="1" ref="A10:H15" ca="1">_xlfn._xlws.PY(3,0)</f>
         <v/>
       </c>
       <c r="B10" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C10" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D10" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E10" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F10" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G10" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H10" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A11">
+        <f ca="1"/>
         <v>195</v>
       </c>
       <c r="B11" t="str">
+        <f ca="1"/>
         <v>ORD-0196</v>
       </c>
       <c r="C11" t="str">
+        <f ca="1"/>
         <v>Headphones</v>
       </c>
       <c r="D11" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E11">
+        <f ca="1"/>
         <v>162.49</v>
       </c>
       <c r="F11">
+        <f ca="1"/>
         <v>2</v>
       </c>
       <c r="G11">
+        <f ca="1"/>
         <v>22</v>
       </c>
       <c r="H11" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A12">
+        <f ca="1"/>
         <v>196</v>
       </c>
       <c r="B12" t="str">
+        <f ca="1"/>
         <v>ORD-0197</v>
       </c>
       <c r="C12" t="str">
+        <f ca="1"/>
         <v>Monitor</v>
       </c>
       <c r="D12" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E12">
+        <f ca="1"/>
         <v>277.98</v>
       </c>
       <c r="F12">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="G12">
+        <f ca="1"/>
         <v>54</v>
       </c>
       <c r="H12" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A13">
+        <f ca="1"/>
         <v>197</v>
       </c>
       <c r="B13" t="str">
+        <f ca="1"/>
         <v>ORD-0198</v>
       </c>
       <c r="C13" t="str">
+        <f ca="1"/>
         <v>Printer Paper</v>
       </c>
       <c r="D13" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E13">
+        <f ca="1"/>
         <v>21.06</v>
       </c>
       <c r="F13">
+        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="G13">
+        <f ca="1"/>
         <v>49</v>
       </c>
       <c r="H13" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A14">
+        <f ca="1"/>
         <v>198</v>
       </c>
       <c r="B14" t="str">
+        <f ca="1"/>
         <v>ORD-0199</v>
       </c>
       <c r="C14" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="D14" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E14">
+        <f ca="1"/>
         <v>22.61</v>
       </c>
       <c r="F14">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="G14">
+        <f ca="1"/>
         <v>62</v>
       </c>
       <c r="H14" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A15">
+        <f ca="1"/>
         <v>199</v>
       </c>
       <c r="B15" t="str">
+        <f ca="1"/>
         <v>ORD-0200</v>
       </c>
       <c r="C15" t="str">
+        <f ca="1"/>
         <v>Headphones</v>
       </c>
       <c r="D15" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E15">
+        <f ca="1"/>
         <v>106.64</v>
       </c>
       <c r="F15">
+        <f ca="1"/>
         <v>10</v>
       </c>
       <c r="G15">
+        <f ca="1"/>
         <v>51</v>
       </c>
       <c r="H15" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A17" t="str" cm="1">
-        <f t="array" ref="A17:H22">_xlfn._xlws.PY(4,0)</f>
+        <f t="array" aca="1" ref="A17:H22" ca="1">_xlfn._xlws.PY(4,0)</f>
         <v/>
       </c>
       <c r="B17" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C17" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D17" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E17" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F17" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G17" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H17" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A18">
+        <f ca="1"/>
         <v>112</v>
       </c>
       <c r="B18" t="str">
+        <f ca="1"/>
         <v>ORD-0113</v>
       </c>
       <c r="C18" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="D18" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E18">
+        <f ca="1"/>
         <v>49.52</v>
       </c>
       <c r="F18">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="G18">
+        <f ca="1"/>
         <v>58</v>
       </c>
       <c r="H18" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A19">
+        <f ca="1"/>
         <v>180</v>
       </c>
       <c r="B19" t="str">
+        <f ca="1"/>
         <v>ORD-0181</v>
       </c>
       <c r="C19" t="str">
+        <f ca="1"/>
         <v>Binder</v>
       </c>
       <c r="D19" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E19">
+        <f ca="1"/>
         <v>41.72</v>
       </c>
       <c r="F19">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="G19">
+        <f ca="1"/>
         <v>48</v>
       </c>
       <c r="H19" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A20">
+        <f ca="1"/>
         <v>82</v>
       </c>
       <c r="B20" t="str">
+        <f ca="1"/>
         <v>ORD-0083</v>
       </c>
       <c r="C20" t="str">
+        <f ca="1"/>
         <v>Chair</v>
       </c>
       <c r="D20" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E20">
+        <f ca="1"/>
         <v>680.38</v>
       </c>
       <c r="F20">
+        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="G20">
+        <f ca="1"/>
         <v>61</v>
       </c>
       <c r="H20" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A21">
+        <f ca="1"/>
         <v>46</v>
       </c>
       <c r="B21" t="str">
+        <f ca="1"/>
         <v>ORD-0047</v>
       </c>
       <c r="C21" t="str">
+        <f ca="1"/>
         <v>Chair</v>
       </c>
       <c r="D21" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E21">
+        <f ca="1"/>
         <v>254.26</v>
       </c>
       <c r="F21">
+        <f ca="1"/>
         <v>10</v>
       </c>
       <c r="G21">
+        <f ca="1"/>
         <v>35</v>
       </c>
       <c r="H21" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A22">
+        <f ca="1"/>
         <v>69</v>
       </c>
       <c r="B22" t="str">
+        <f ca="1"/>
         <v>ORD-0070</v>
       </c>
       <c r="C22" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="D22" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E22">
+        <f ca="1"/>
         <v>11.33</v>
       </c>
       <c r="F22">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="G22">
+        <f ca="1"/>
         <v>53</v>
       </c>
       <c r="H22" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A24" t="str" cm="1">
-        <f t="array" ref="A24:B30">_xlfn._xlws.PY(5,0)</f>
+        <f t="array" aca="1" ref="A24:B30" ca="1">_xlfn._xlws.PY(5,0)</f>
         <v>order_id</v>
       </c>
       <c r="B24">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A25" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="B25">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A26" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="B26">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A27" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="B27">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A28" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="B28">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A29" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="B29">
+        <f ca="1"/>
         <v>0.06</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A30" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
       <c r="B30">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A32" t="str" cm="1">
-        <f t="array" ref="A32:B38">_xlfn._xlws.PY(6,0)</f>
+        <f t="array" aca="1" ref="A32:B38" ca="1">_xlfn._xlws.PY(6,0)</f>
         <v>customer_age</v>
       </c>
       <c r="B32">
+        <f ca="1"/>
         <v>0.06</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A33" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="B33">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A34" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="B34">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A35" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="B35">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A36" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="B36">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A37" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="B37">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A38" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
       <c r="B38">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A40" cm="1">
-        <f t="array" ref="A40:A41">_xlfn._xlws.PY(7,0)</f>
+        <f t="array" aca="1" ref="A40:A41" ca="1">_xlfn._xlws.PY(7,0)</f>
         <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A41">
+        <f ca="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A43" t="str" cm="1">
-        <f t="array" ref="A43:D51">_xlfn._xlws.PY(8,0)</f>
+        <f t="array" aca="1" ref="A43:D51" ca="1">_xlfn._xlws.PY(8,0)</f>
         <v/>
       </c>
       <c r="B43" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="C43" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="D43" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A44" t="str">
+        <f ca="1"/>
         <v>count</v>
       </c>
       <c r="B44">
+        <f ca="1"/>
         <v>200</v>
       </c>
       <c r="C44">
+        <f ca="1"/>
         <v>200</v>
       </c>
       <c r="D44">
+        <f ca="1"/>
         <v>194</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A45" t="str">
+        <f ca="1"/>
         <v>mean</v>
       </c>
       <c r="B45">
+        <f ca="1"/>
         <v>211.94830000000002</v>
       </c>
       <c r="C45">
+        <f ca="1"/>
         <v>5.7</v>
       </c>
       <c r="D45">
+        <f ca="1"/>
         <v>43.597938144329895</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A46" t="str">
+        <f ca="1"/>
         <v>std</v>
       </c>
       <c r="B46">
+        <f ca="1"/>
         <v>215.73323312713649</v>
       </c>
       <c r="C46">
+        <f ca="1"/>
         <v>2.7252771745993041</v>
       </c>
       <c r="D46">
+        <f ca="1"/>
         <v>13.286527356620564</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A47" t="str">
+        <f ca="1"/>
         <v>min</v>
       </c>
       <c r="B47">
+        <f ca="1"/>
         <v>2.17</v>
       </c>
       <c r="C47">
+        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="D47">
+        <f ca="1"/>
         <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A48" t="str">
+        <f ca="1"/>
         <v>25%</v>
       </c>
       <c r="B48">
+        <f ca="1"/>
         <v>31.2075</v>
       </c>
       <c r="C48">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="D48">
+        <f ca="1"/>
         <v>33.25</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A49" t="str">
+        <f ca="1"/>
         <v>50%</v>
       </c>
       <c r="B49">
+        <f ca="1"/>
         <v>111.38</v>
       </c>
       <c r="C49">
+        <f ca="1"/>
         <v>5.5</v>
       </c>
       <c r="D49">
+        <f ca="1"/>
         <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A50" t="str">
+        <f ca="1"/>
         <v>75%</v>
       </c>
       <c r="B50">
+        <f ca="1"/>
         <v>378.83</v>
       </c>
       <c r="C50">
+        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="D50">
+        <f ca="1"/>
         <v>55.75</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A51" t="str">
+        <f ca="1"/>
         <v>max</v>
       </c>
       <c r="B51">
+        <f ca="1"/>
         <v>760.69</v>
       </c>
       <c r="C51">
+        <f ca="1"/>
         <v>10</v>
       </c>
       <c r="D51">
+        <f ca="1"/>
         <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A53" t="str" cm="1">
-        <f t="array" ref="A53:D61">_xlfn._xlws.PY(9,0)</f>
+        <f t="array" aca="1" ref="A53:D61" ca="1">_xlfn._xlws.PY(9,0)</f>
         <v/>
       </c>
       <c r="B53" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="C53" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="D53" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A54" t="str">
+        <f ca="1"/>
         <v>count</v>
       </c>
       <c r="B54">
+        <f ca="1"/>
         <v>200</v>
       </c>
       <c r="C54">
+        <f ca="1"/>
         <v>200</v>
       </c>
       <c r="D54">
+        <f ca="1"/>
         <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A55" t="str">
+        <f ca="1"/>
         <v>mean</v>
       </c>
       <c r="B55">
+        <f ca="1"/>
         <v>211.94830000000002</v>
       </c>
       <c r="C55">
+        <f ca="1"/>
         <v>5.7</v>
       </c>
       <c r="D55">
+        <f ca="1"/>
         <v>43.597938144329895</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A56" t="str">
+        <f ca="1"/>
         <v>std</v>
       </c>
       <c r="B56">
+        <f ca="1"/>
         <v>215.73323312713649</v>
       </c>
       <c r="C56">
+        <f ca="1"/>
         <v>2.7252771745993041</v>
       </c>
       <c r="D56">
+        <f ca="1"/>
         <v>13.286527356620564</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A57" t="str">
+        <f ca="1"/>
         <v>min</v>
       </c>
       <c r="B57">
+        <f ca="1"/>
         <v>2.17</v>
       </c>
       <c r="C57">
+        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="D57">
+        <f ca="1"/>
         <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A58" t="str">
+        <f ca="1"/>
         <v>10%</v>
       </c>
       <c r="B58">
+        <f ca="1"/>
         <v>13.033000000000001</v>
       </c>
       <c r="C58">
+        <f ca="1"/>
         <v>2</v>
       </c>
       <c r="D58">
+        <f ca="1"/>
         <v>25.3</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A59" t="str">
+        <f ca="1"/>
         <v>50%</v>
       </c>
       <c r="B59">
+        <f ca="1"/>
         <v>111.38</v>
       </c>
       <c r="C59">
+        <f ca="1"/>
         <v>5.5</v>
       </c>
       <c r="D59">
+        <f ca="1"/>
         <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A60" t="str">
+        <f ca="1"/>
         <v>90%</v>
       </c>
       <c r="B60">
+        <f ca="1"/>
         <v>512.85599999999999</v>
       </c>
       <c r="C60">
+        <f ca="1"/>
         <v>9.0999999999999943</v>
       </c>
       <c r="D60">
+        <f ca="1"/>
         <v>62</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A61" t="str">
+        <f ca="1"/>
         <v>max</v>
       </c>
       <c r="B61">
+        <f ca="1"/>
         <v>760.69</v>
       </c>
       <c r="C61">
+        <f ca="1"/>
         <v>10</v>
       </c>
       <c r="D61">
+        <f ca="1"/>
         <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A63" t="str" cm="1">
-        <f t="array" ref="A63:E67">_xlfn._xlws.PY(10,0)</f>
+        <f t="array" aca="1" ref="A63:E67" ca="1">_xlfn._xlws.PY(10,0)</f>
         <v/>
       </c>
       <c r="B63" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C63" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D63" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E63" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A64" t="str">
+        <f ca="1"/>
         <v>count</v>
       </c>
       <c r="B64">
+        <f ca="1"/>
         <v>200</v>
       </c>
       <c r="C64">
+        <f ca="1"/>
         <v>200</v>
       </c>
       <c r="D64">
+        <f ca="1"/>
         <v>200</v>
       </c>
       <c r="E64">
+        <f ca="1"/>
         <v>200</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A65" t="str">
+        <f ca="1"/>
         <v>unique</v>
       </c>
       <c r="B65">
+        <f ca="1"/>
         <v>200</v>
       </c>
       <c r="C65">
+        <f ca="1"/>
         <v>15</v>
       </c>
       <c r="D65">
+        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="E65">
+        <f ca="1"/>
         <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A66" t="str">
+        <f ca="1"/>
         <v>top</v>
       </c>
       <c r="B66" t="str">
+        <f ca="1"/>
         <v>ORD-0001</v>
       </c>
       <c r="C66" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="D66" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E66" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A67" t="str">
+        <f ca="1"/>
         <v>freq</v>
       </c>
       <c r="B67">
+        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="C67">
+        <f ca="1"/>
         <v>19</v>
       </c>
       <c r="D67">
+        <f ca="1"/>
         <v>80</v>
       </c>
       <c r="E67">
+        <f ca="1"/>
         <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A69" t="str" cm="1">
-        <f t="array" ref="A69:C74">_xlfn._xlws.PY(11,0)</f>
+        <f t="array" aca="1" ref="A69:C74" ca="1">_xlfn._xlws.PY(11,0)</f>
         <v>product</v>
       </c>
       <c r="B69" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="C69" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A70" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="B70" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="C70">
+        <f ca="1"/>
         <v>68.760000000000005</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A71" t="str">
+        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="B71" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="C71">
+        <f ca="1"/>
         <v>115.2</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A72" t="str">
+        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="B72" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="C72">
+        <f ca="1"/>
         <v>69.900000000000006</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A73" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="B73" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="C73">
+        <f ca="1"/>
         <v>15.35</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A74" t="str">
+        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="B74" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="C74">
+        <f ca="1"/>
         <v>479.68</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A76" t="str" cm="1">
-        <f t="array" ref="A76:A81">_xlfn._xlws.PY(12,0)</f>
+        <f t="array" aca="1" ref="A76:A81" ca="1">_xlfn._xlws.PY(12,0)</f>
         <v>country</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A77" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A78" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A79" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A80" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A81" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A84" t="str" cm="1">
-        <f t="array" ref="A84:H89">_xlfn._xlws.PY(13,0)</f>
+        <f t="array" aca="1" ref="A84:H89" ca="1">_xlfn._xlws.PY(13,0)</f>
         <v/>
       </c>
       <c r="B84" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C84" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D84" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E84" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F84" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G84" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H84" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A85">
+        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="B85" t="str">
+        <f ca="1"/>
         <v>ORD-0001</v>
       </c>
       <c r="C85" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D85" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E85">
+        <f ca="1"/>
         <v>68.760000000000005</v>
       </c>
       <c r="F85">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="G85">
+        <f ca="1"/>
         <v>37</v>
       </c>
       <c r="H85" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A86">
+        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="B86" t="str">
+        <f ca="1"/>
         <v>ORD-0002</v>
       </c>
       <c r="C86" t="str">
+        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="D86" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E86">
+        <f ca="1"/>
         <v>115.2</v>
       </c>
       <c r="F86">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="G86">
+        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="H86" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A87">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="B87" t="str">
+        <f ca="1"/>
         <v>ORD-0005</v>
       </c>
       <c r="C87" t="str">
+        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="D87" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E87">
+        <f ca="1"/>
         <v>479.68</v>
       </c>
       <c r="F87">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="G87">
+        <f ca="1"/>
         <v>28</v>
       </c>
       <c r="H87" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A88">
+        <f ca="1"/>
         <v>11</v>
       </c>
       <c r="B88" t="str">
+        <f ca="1"/>
         <v>ORD-0012</v>
       </c>
       <c r="C88" t="str">
+        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="D88" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E88">
+        <f ca="1"/>
         <v>415.36</v>
       </c>
       <c r="F88">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="G88">
+        <f ca="1"/>
         <v>47</v>
       </c>
       <c r="H88" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A89">
+        <f ca="1"/>
         <v>13</v>
       </c>
       <c r="B89" t="str">
+        <f ca="1"/>
         <v>ORD-0014</v>
       </c>
       <c r="C89" t="str">
+        <f ca="1"/>
         <v>Headphones</v>
       </c>
       <c r="D89" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E89">
+        <f ca="1"/>
         <v>91.32</v>
       </c>
       <c r="F89">
+        <f ca="1"/>
         <v>9</v>
       </c>
       <c r="G89">
+        <f ca="1"/>
         <v>56</v>
       </c>
       <c r="H89" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A91" t="str" cm="1">
-        <f t="array" ref="A91:H96">_xlfn._xlws.PY(14,0)</f>
+        <f t="array" aca="1" ref="A91:H96" ca="1">_xlfn._xlws.PY(14,0)</f>
         <v/>
       </c>
       <c r="B91" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C91" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D91" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E91" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F91" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G91" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H91" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A92">
+        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="B92" t="str">
+        <f ca="1"/>
         <v>ORD-0001</v>
       </c>
       <c r="C92" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D92" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E92">
+        <f ca="1"/>
         <v>68.760000000000005</v>
       </c>
       <c r="F92">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="G92">
+        <f ca="1"/>
         <v>37</v>
       </c>
       <c r="H92" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A93">
+        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="B93" t="str">
+        <f ca="1"/>
         <v>ORD-0002</v>
       </c>
       <c r="C93" t="str">
+        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="D93" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E93">
+        <f ca="1"/>
         <v>115.2</v>
       </c>
       <c r="F93">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="G93">
+        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="H93" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A94">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="B94" t="str">
+        <f ca="1"/>
         <v>ORD-0005</v>
       </c>
       <c r="C94" t="str">
+        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="D94" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E94">
+        <f ca="1"/>
         <v>479.68</v>
       </c>
       <c r="F94">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="G94">
+        <f ca="1"/>
         <v>28</v>
       </c>
       <c r="H94" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A95">
+        <f ca="1"/>
         <v>11</v>
       </c>
       <c r="B95" t="str">
+        <f ca="1"/>
         <v>ORD-0012</v>
       </c>
       <c r="C95" t="str">
+        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="D95" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E95">
+        <f ca="1"/>
         <v>415.36</v>
       </c>
       <c r="F95">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="G95">
+        <f ca="1"/>
         <v>47</v>
       </c>
       <c r="H95" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A96">
+        <f ca="1"/>
         <v>13</v>
       </c>
       <c r="B96" t="str">
+        <f ca="1"/>
         <v>ORD-0014</v>
       </c>
       <c r="C96" t="str">
+        <f ca="1"/>
         <v>Headphones</v>
       </c>
       <c r="D96" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E96">
+        <f ca="1"/>
         <v>91.32</v>
       </c>
       <c r="F96">
+        <f ca="1"/>
         <v>9</v>
       </c>
       <c r="G96">
+        <f ca="1"/>
         <v>56</v>
       </c>
       <c r="H96" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A98" t="str" cm="1">
-        <f t="array" ref="A98:H103">_xlfn._xlws.PY(15,0)</f>
+        <f t="array" aca="1" ref="A98:H103" ca="1">_xlfn._xlws.PY(15,0)</f>
         <v/>
       </c>
       <c r="B98" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C98" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D98" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E98" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F98" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G98" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H98" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A99">
+        <f ca="1"/>
         <v>0</v>
       </c>
       <c r="B99" t="str">
+        <f ca="1"/>
         <v>ORD-0001</v>
       </c>
       <c r="C99" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D99" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E99">
+        <f ca="1"/>
         <v>68.760000000000005</v>
       </c>
       <c r="F99">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="G99">
+        <f ca="1"/>
         <v>37</v>
       </c>
       <c r="H99" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A100">
+        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="B100" t="str">
+        <f ca="1"/>
         <v>ORD-0002</v>
       </c>
       <c r="C100" t="str">
+        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="D100" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E100">
+        <f ca="1"/>
         <v>115.2</v>
       </c>
       <c r="F100">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="G100">
+        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="H100" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A101">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="B101" t="str">
+        <f ca="1"/>
         <v>ORD-0005</v>
       </c>
       <c r="C101" t="str">
+        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="D101" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E101">
+        <f ca="1"/>
         <v>479.68</v>
       </c>
       <c r="F101">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="G101">
+        <f ca="1"/>
         <v>28</v>
       </c>
       <c r="H101" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A102">
+        <f ca="1"/>
         <v>11</v>
       </c>
       <c r="B102" t="str">
+        <f ca="1"/>
         <v>ORD-0012</v>
       </c>
       <c r="C102" t="str">
+        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="D102" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E102">
+        <f ca="1"/>
         <v>415.36</v>
       </c>
       <c r="F102">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="G102">
+        <f ca="1"/>
         <v>47</v>
       </c>
       <c r="H102" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A103">
+        <f ca="1"/>
         <v>13</v>
       </c>
       <c r="B103" t="str">
+        <f ca="1"/>
         <v>ORD-0014</v>
       </c>
       <c r="C103" t="str">
+        <f ca="1"/>
         <v>Headphones</v>
       </c>
       <c r="D103" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E103">
+        <f ca="1"/>
         <v>91.32</v>
       </c>
       <c r="F103">
+        <f ca="1"/>
         <v>9</v>
       </c>
       <c r="G103">
+        <f ca="1"/>
         <v>56</v>
       </c>
       <c r="H103" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A105" t="str" cm="1">
-        <f t="array" ref="A105:H110">_xlfn._xlws.PY(16,0)</f>
+        <f t="array" aca="1" ref="A105:H110" ca="1">_xlfn._xlws.PY(16,0)</f>
         <v/>
       </c>
       <c r="B105" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C105" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D105" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E105" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F105" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G105" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H105" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A106">
+        <f ca="1"/>
         <v>48</v>
       </c>
       <c r="B106" t="str">
+        <f ca="1"/>
         <v>ORD-0049</v>
       </c>
       <c r="C106" t="str">
+        <f ca="1"/>
         <v>Printer Paper</v>
       </c>
       <c r="D106" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E106">
+        <f ca="1"/>
         <v>2.17</v>
       </c>
       <c r="F106">
+        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="G106">
+        <f ca="1"/>
         <v>62</v>
       </c>
       <c r="H106" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A107">
+        <f ca="1"/>
         <v>79</v>
       </c>
       <c r="B107" t="str">
+        <f ca="1"/>
         <v>ORD-0080</v>
       </c>
       <c r="C107" t="str">
+        <f ca="1"/>
         <v>Stapler</v>
       </c>
       <c r="D107" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E107">
+        <f ca="1"/>
         <v>2.2799999999999998</v>
       </c>
       <c r="F107">
+        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="G107">
+        <f ca="1"/>
         <v>41</v>
       </c>
       <c r="H107" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A108">
+        <f ca="1"/>
         <v>99</v>
       </c>
       <c r="B108" t="str">
+        <f ca="1"/>
         <v>ORD-0100</v>
       </c>
       <c r="C108" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="D108" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E108">
+        <f ca="1"/>
         <v>2.4900000000000002</v>
       </c>
       <c r="F108">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="G108">
+        <f ca="1"/>
         <v>27</v>
       </c>
       <c r="H108" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A109">
+        <f ca="1"/>
         <v>142</v>
       </c>
       <c r="B109" t="str">
+        <f ca="1"/>
         <v>ORD-0143</v>
       </c>
       <c r="C109" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="D109" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E109">
+        <f ca="1"/>
         <v>3.72</v>
       </c>
       <c r="F109">
+        <f ca="1"/>
         <v>2</v>
       </c>
       <c r="G109">
+        <f ca="1"/>
         <v>37</v>
       </c>
       <c r="H109" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A110">
+        <f ca="1"/>
         <v>21</v>
       </c>
       <c r="B110" t="str">
+        <f ca="1"/>
         <v>ORD-0022</v>
       </c>
       <c r="C110" t="str">
+        <f ca="1"/>
         <v>Pens</v>
       </c>
       <c r="D110" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E110">
+        <f ca="1"/>
         <v>4.78</v>
       </c>
       <c r="F110">
+        <f ca="1"/>
         <v>10</v>
       </c>
       <c r="G110">
+        <f ca="1"/>
         <v>27</v>
       </c>
       <c r="H110" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A113" t="str" cm="1">
-        <f t="array" ref="A113:H118">_xlfn._xlws.PY(17,0)</f>
+        <f t="array" aca="1" ref="A113:H118" ca="1">_xlfn._xlws.PY(17,0)</f>
         <v/>
       </c>
       <c r="B113" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C113" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D113" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E113" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F113" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G113" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H113" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A114">
+        <f ca="1"/>
         <v>113</v>
       </c>
       <c r="B114" t="str">
+        <f ca="1"/>
         <v>ORD-0114</v>
       </c>
       <c r="C114" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D114" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E114">
+        <f ca="1"/>
         <v>760.69</v>
       </c>
       <c r="F114">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="G114">
+        <f ca="1"/>
         <v>62</v>
       </c>
       <c r="H114" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A115">
+        <f ca="1"/>
         <v>165</v>
       </c>
       <c r="B115" t="str">
+        <f ca="1"/>
         <v>ORD-0166</v>
       </c>
       <c r="C115" t="str">
+        <f ca="1"/>
         <v>Filing Cabinet</v>
       </c>
       <c r="D115" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E115">
+        <f ca="1"/>
         <v>754.29</v>
       </c>
       <c r="F115">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="G115">
+        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="H115" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A116">
+        <f ca="1"/>
         <v>45</v>
       </c>
       <c r="B116" t="str">
+        <f ca="1"/>
         <v>ORD-0046</v>
       </c>
       <c r="C116" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D116" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E116">
+        <f ca="1"/>
         <v>754.2</v>
       </c>
       <c r="F116">
+        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="G116">
+        <f ca="1"/>
         <v>38</v>
       </c>
       <c r="H116" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A117">
+        <f ca="1"/>
         <v>40</v>
       </c>
       <c r="B117" t="str">
+        <f ca="1"/>
         <v>ORD-0041</v>
       </c>
       <c r="C117" t="str">
+        <f ca="1"/>
         <v>Bookshelf</v>
       </c>
       <c r="D117" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E117">
+        <f ca="1"/>
         <v>751.03</v>
       </c>
       <c r="F117">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="G117">
+        <f ca="1"/>
         <v>64</v>
       </c>
       <c r="H117" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A118">
+        <f ca="1"/>
         <v>152</v>
       </c>
       <c r="B118" t="str">
+        <f ca="1"/>
         <v>ORD-0153</v>
       </c>
       <c r="C118" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D118" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E118">
+        <f ca="1"/>
         <v>732.96</v>
       </c>
       <c r="F118">
+        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="G118">
+        <f ca="1"/>
         <v>40</v>
       </c>
       <c r="H118" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A121" t="str" cm="1">
-        <f t="array" ref="A121:H126">_xlfn._xlws.PY(18,0)</f>
+        <f t="array" aca="1" ref="A121:H126" ca="1">_xlfn._xlws.PY(18,0)</f>
         <v/>
       </c>
       <c r="B121" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C121" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D121" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E121" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F121" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G121" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H121" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A122">
+        <f ca="1"/>
         <v>48</v>
       </c>
       <c r="B122" t="str">
+        <f ca="1"/>
         <v>ORD-0049</v>
       </c>
       <c r="C122" t="str">
+        <f ca="1"/>
         <v>Printer Paper</v>
       </c>
       <c r="D122" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E122">
+        <f ca="1"/>
         <v>2.17</v>
       </c>
       <c r="F122">
+        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="G122">
+        <f ca="1"/>
         <v>62</v>
       </c>
       <c r="H122" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A123">
+        <f ca="1"/>
         <v>32</v>
       </c>
       <c r="B123" t="str">
+        <f ca="1"/>
         <v>ORD-0033</v>
       </c>
       <c r="C123" t="str">
+        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="D123" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E123">
+        <f ca="1"/>
         <v>6.7</v>
       </c>
       <c r="F123">
+        <f ca="1"/>
         <v>9</v>
       </c>
       <c r="G123">
+        <f ca="1"/>
         <v>22</v>
       </c>
       <c r="H123" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A124">
+        <f ca="1"/>
         <v>119</v>
       </c>
       <c r="B124" t="str">
+        <f ca="1"/>
         <v>ORD-0120</v>
       </c>
       <c r="C124" t="str">
+        <f ca="1"/>
         <v>Stapler</v>
       </c>
       <c r="D124" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E124">
+        <f ca="1"/>
         <v>7.97</v>
       </c>
       <c r="F124">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="G124">
+        <f ca="1"/>
         <v>47</v>
       </c>
       <c r="H124" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A125">
+        <f ca="1"/>
         <v>181</v>
       </c>
       <c r="B125" t="str">
+        <f ca="1"/>
         <v>ORD-0182</v>
       </c>
       <c r="C125" t="str">
+        <f ca="1"/>
         <v>Binder</v>
       </c>
       <c r="D125" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E125">
+        <f ca="1"/>
         <v>19.97</v>
       </c>
       <c r="F125">
+        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="G125">
+        <f ca="1"/>
         <v>65</v>
       </c>
       <c r="H125" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A126">
+        <f ca="1"/>
         <v>34</v>
       </c>
       <c r="B126" t="str">
+        <f ca="1"/>
         <v>ORD-0035</v>
       </c>
       <c r="C126" t="str">
+        <f ca="1"/>
         <v>Monitor</v>
       </c>
       <c r="D126" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E126">
+        <f ca="1"/>
         <v>26.02</v>
       </c>
       <c r="F126">
+        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="G126">
+        <f ca="1"/>
         <v>38</v>
       </c>
       <c r="H126" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A129" t="str" cm="1">
-        <f t="array" ref="A129:H134">_xlfn._xlws.PY(19,0)</f>
+        <f t="array" aca="1" ref="A129:H134" ca="1">_xlfn._xlws.PY(19,0)</f>
         <v/>
       </c>
       <c r="B129" t="str">
+        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C129" t="str">
+        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D129" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E129" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F129" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G129" t="str">
+        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H129" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A130">
+        <f ca="1"/>
         <v>113</v>
       </c>
       <c r="B130" t="str">
+        <f ca="1"/>
         <v>ORD-0114</v>
       </c>
       <c r="C130" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D130" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E130">
+        <f ca="1"/>
         <v>760.69</v>
       </c>
       <c r="F130">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="G130">
+        <f ca="1"/>
         <v>62</v>
       </c>
       <c r="H130" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A131">
+        <f ca="1"/>
         <v>165</v>
       </c>
       <c r="B131" t="str">
+        <f ca="1"/>
         <v>ORD-0166</v>
       </c>
       <c r="C131" t="str">
+        <f ca="1"/>
         <v>Filing Cabinet</v>
       </c>
       <c r="D131" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E131">
+        <f ca="1"/>
         <v>754.29</v>
       </c>
       <c r="F131">
+        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="G131">
+        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="H131" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A132">
+        <f ca="1"/>
         <v>45</v>
       </c>
       <c r="B132" t="str">
+        <f ca="1"/>
         <v>ORD-0046</v>
       </c>
       <c r="C132" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D132" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E132">
+        <f ca="1"/>
         <v>754.2</v>
       </c>
       <c r="F132">
+        <f ca="1"/>
         <v>3</v>
       </c>
       <c r="G132">
+        <f ca="1"/>
         <v>38</v>
       </c>
       <c r="H132" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A133">
+        <f ca="1"/>
         <v>40</v>
       </c>
       <c r="B133" t="str">
+        <f ca="1"/>
         <v>ORD-0041</v>
       </c>
       <c r="C133" t="str">
+        <f ca="1"/>
         <v>Bookshelf</v>
       </c>
       <c r="D133" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E133">
+        <f ca="1"/>
         <v>751.03</v>
       </c>
       <c r="F133">
+        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="G133">
+        <f ca="1"/>
         <v>64</v>
       </c>
       <c r="H133" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A134">
+        <f ca="1"/>
         <v>152</v>
       </c>
       <c r="B134" t="str">
+        <f ca="1"/>
         <v>ORD-0153</v>
       </c>
       <c r="C134" t="str">
+        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="D134" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="E134">
+        <f ca="1"/>
         <v>732.96</v>
       </c>
       <c r="F134">
+        <f ca="1"/>
         <v>8</v>
       </c>
       <c r="G134">
+        <f ca="1"/>
         <v>40</v>
       </c>
       <c r="H134" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A136" t="str" cm="1">
-        <f t="array" ref="A136:B141">_xlfn._xlws.PY(20,0)</f>
+        <f t="array" aca="1" ref="A136:B141" ca="1">_xlfn._xlws.PY(20,0)</f>
         <v>country</v>
       </c>
       <c r="B136" t="str">
+        <f ca="1"/>
         <v>count</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A137" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
       <c r="B137">
+        <f ca="1"/>
         <v>77</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A138" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
       <c r="B138">
+        <f ca="1"/>
         <v>43</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A139" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
       <c r="B139">
+        <f ca="1"/>
         <v>39</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A140" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
       <c r="B140">
+        <f ca="1"/>
         <v>26</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A141" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
       <c r="B141">
+        <f ca="1"/>
         <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A144" t="str" cm="1">
-        <f t="array" ref="A144:B147">_xlfn._xlws.PY(21,0)</f>
+        <f t="array" aca="1" ref="A144:B147" ca="1">_xlfn._xlws.PY(21,0)</f>
         <v>category</v>
       </c>
       <c r="B144" t="str">
+        <f ca="1"/>
         <v>count</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A145" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="B145">
+        <f ca="1"/>
         <v>80</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A146" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="B146">
+        <f ca="1"/>
         <v>65</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A147" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="B147">
+        <f ca="1"/>
         <v>55</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A149" t="str" cm="1">
-        <f t="array" ref="A149:B152">_xlfn._xlws.PY(22,0)</f>
+        <f t="array" aca="1" ref="A149:B152" ca="1">_xlfn._xlws.PY(22,0)</f>
         <v>category</v>
       </c>
       <c r="B149" t="str">
+        <f ca="1"/>
         <v>proportion</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A150" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="B150">
+        <f ca="1"/>
         <v>0.4</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A151" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="B151">
+        <f ca="1"/>
         <v>0.32500000000000001</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A152" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="B152">
+        <f ca="1"/>
         <v>0.27500000000000002</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A154" t="str" cm="1">
-        <f t="array" ref="A154:B159">_xlfn._xlws.PY(23,0)</f>
+        <f t="array" aca="1" ref="A154:B159" ca="1">_xlfn._xlws.PY(23,0)</f>
         <v>country</v>
       </c>
       <c r="B154" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A155" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
       <c r="B155">
+        <f ca="1"/>
         <v>167.16199999999998</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A156" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
       <c r="B156">
+        <f ca="1"/>
         <v>201.18230769230769</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A157" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
       <c r="B157">
+        <f ca="1"/>
         <v>182.58790697674419</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A158" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
       <c r="B158">
+        <f ca="1"/>
         <v>274.43128205128204</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.5">
       <c r="A159" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
       <c r="B159">
+        <f ca="1"/>
         <v>209.05701298701297</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A161" t="str" cm="1">
-        <f t="array" ref="A161:B164">_xlfn._xlws.PY(24,0)</f>
+        <f t="array" aca="1" ref="A161:B164" ca="1">_xlfn._xlws.PY(24,0)</f>
         <v>category</v>
       </c>
       <c r="B161" t="str">
+        <f ca="1"/>
         <v>quantity</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A162" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="B162">
+        <f ca="1"/>
         <v>362</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A163" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="B163">
+        <f ca="1"/>
         <v>288</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A164" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="B164">
+        <f ca="1"/>
         <v>490</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A166" t="str" cm="1">
-        <f t="array" ref="A166:C181">_xlfn._xlws.PY(25,0)</f>
+        <f t="array" aca="1" ref="A166:C181" ca="1">_xlfn._xlws.PY(25,0)</f>
         <v>country</v>
       </c>
       <c r="B166" t="str">
+        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="C166" t="str">
+        <f ca="1"/>
         <v>unit_price</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A167" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
       <c r="B167" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="C167">
+        <f ca="1"/>
         <v>270.6516666666667</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A168" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
       <c r="B168" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="C168">
+        <f ca="1"/>
         <v>256.68</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A169" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
       <c r="B169" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="C169">
+        <f ca="1"/>
         <v>18.91333333333333</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A170" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
       <c r="B170" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="C170">
+        <f ca="1"/>
         <v>274.04250000000002</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A171" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
       <c r="B171" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="C171">
+        <f ca="1"/>
         <v>529.45000000000005</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A172" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
       <c r="B172" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="C172">
+        <f ca="1"/>
         <v>30.088461538461541</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A173" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
       <c r="B173" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="C173">
+        <f ca="1"/>
         <v>230.67818181818183</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A174" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
       <c r="B174" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="C174">
+        <f ca="1"/>
         <v>350.0864285714286</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A175" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
       <c r="B175" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="C175">
+        <f ca="1"/>
         <v>22.922777777777778</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.5">
       <c r="A176" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
       <c r="B176" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="C176">
+        <f ca="1"/>
         <v>272.95764705882351</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A177" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
       <c r="B177" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="C177">
+        <f ca="1"/>
         <v>529.8054545454545</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A178" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
       <c r="B178" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="C178">
+        <f ca="1"/>
         <v>21.334545454545456</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A179" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
       <c r="B179" t="str">
+        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="C179">
+        <f ca="1"/>
         <v>296.6995652173913</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A180" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
       <c r="B180" t="str">
+        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="C180">
+        <f ca="1"/>
         <v>383.92954545454546</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A181" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
       <c r="B181" t="str">
+        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="C181">
+        <f ca="1"/>
         <v>25.839062500000001</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A183" t="str" cm="1">
-        <f t="array" ref="A183:D189">_xlfn._xlws.PY(26,0)</f>
+        <f t="array" aca="1" ref="A183:D189" ca="1">_xlfn._xlws.PY(26,0)</f>
         <v/>
       </c>
       <c r="B183" t="str">
+        <f ca="1"/>
         <v>mean</v>
       </c>
       <c r="C183" t="str">
+        <f ca="1"/>
         <v>min</v>
       </c>
       <c r="D183" t="str">
+        <f ca="1"/>
         <v>max</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A184" t="str">
+        <f ca="1"/>
         <v>country</v>
       </c>
       <c r="B184" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="C184" t="str">
+        <f ca="1"/>
         <v/>
       </c>
       <c r="D184" t="str">
+        <f ca="1"/>
         <v/>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A185" t="str">
+        <f ca="1"/>
         <v>Australia</v>
       </c>
       <c r="B185">
+        <f ca="1"/>
         <v>167.16199999999998</v>
       </c>
       <c r="C185">
+        <f ca="1"/>
         <v>2.17</v>
       </c>
       <c r="D185">
+        <f ca="1"/>
         <v>486.65</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A186" t="str">
+        <f ca="1"/>
         <v>Canada</v>
       </c>
       <c r="B186">
+        <f ca="1"/>
         <v>201.18230769230769</v>
       </c>
       <c r="C186">
+        <f ca="1"/>
         <v>2.2799999999999998</v>
       </c>
       <c r="D186">
+        <f ca="1"/>
         <v>732.96</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A187" t="str">
+        <f ca="1"/>
         <v>Germany</v>
       </c>
       <c r="B187">
+        <f ca="1"/>
         <v>182.58790697674419</v>
       </c>
       <c r="C187">
+        <f ca="1"/>
         <v>3.72</v>
       </c>
       <c r="D187">
+        <f ca="1"/>
         <v>754.29</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A188" t="str">
+        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
       <c r="B188">
+        <f ca="1"/>
         <v>274.43128205128204</v>
       </c>
       <c r="C188">
+        <f ca="1"/>
         <v>7.32</v>
       </c>
       <c r="D188">
+        <f ca="1"/>
         <v>689.59</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.5">
       <c r="A189" t="str">
+        <f ca="1"/>
         <v>United States</v>
       </c>
       <c r="B189">
+        <f ca="1"/>
         <v>209.05701298701297</v>
       </c>
       <c r="C189">
+        <f ca="1"/>
         <v>2.4900000000000002</v>
       </c>
       <c r="D189">
+        <f ca="1"/>
         <v>760.69</v>
       </c>
     </row>

--- a/ch_02_pandas/ch_02_solution.xlsx
+++ b/ch_02_pandas/ch_02_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02_pandas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02_pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2029E3-6D7B-4C54-8EFC-5ABA7277D8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207B83A7-FAB8-4D24-B601-926ABE3E5B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nyc" sheetId="1" r:id="rId1"/>
@@ -49,18 +49,11 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="1">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
+          <xlrd:rvb i="2"/>
         </ext>
       </extLst>
     </bk>
@@ -70,12 +63,9 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="1">
     <bk>
       <rc t="2" v="0"/>
-    </bk>
-    <bk>
-      <rc t="2" v="1"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -171,9 +161,6 @@
     </pythonScript>
     <pythonScript>
       <code>sales_df['country'].value_counts()</code>
-    </pythonScript>
-    <pythonScript>
-      <code>sales_df['category'].value_counts()</code>
     </pythonScript>
     <pythonScript>
       <code>sales_df['category'].value_counts(normalize=True)</code>
@@ -1170,36 +1157,30 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
-    <v>14</v>
+    <v>0</v>
   </rv>
   <rv s="1">
+    <v>DataFrame</v>
+    <v>1</v>
     <v>0</v>
   </rv>
   <rv s="2">
-    <v>DataFrame</v>
-    <v>1</v>
-    <v>1</v>
-  </rv>
-  <rv s="3">
     <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
     <v>DataFrame</v>
     <v xml:space="preserve">     order_id        product         category  unit_price  quantity  \
 0    ORD-0001           Desk        Furniture       68.76         5   
 1    ORD-0002           Lamp        Furniture      115.20         7   
 2    ORD-0003           Lamp        Fur...</v>
-    <v>2</v>
+    <v>1</v>
     <v>2</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
-  <s t="_error">
-    <k n="errorType" t="i"/>
-  </s>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <s t="_array">
     <k n="array" t="a"/>
   </s>
@@ -1574,18 +1555,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" style="4" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10.87890625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.64453125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.05859375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="8.9375" style="5"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1595,15 +1576,21 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" cm="1">
-        <f t="array" aca="1" ref="E1" ca="1">_xlfn._xlws.PY(0,0,nyc_pop[#All])</f>
-        <v>0</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E1" t="str" cm="1">
+        <f t="array" ref="E1:H6">_xlfn._xlws.PY(0,0,nyc_pop[#All])</f>
+        <v>borough</v>
+      </c>
+      <c r="F1" s="5" t="str">
+        <v>population</v>
+      </c>
+      <c r="G1" s="5" t="str">
+        <v>land_area</v>
+      </c>
+      <c r="H1" s="5" t="str">
+        <v>density</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1613,8 +1600,20 @@
       <c r="C2">
         <v>22.83</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E2" t="str">
+        <v>Manhattan</v>
+      </c>
+      <c r="F2" s="5">
+        <v>1694251</v>
+      </c>
+      <c r="G2" s="5">
+        <v>22.83</v>
+      </c>
+      <c r="H2" s="5">
+        <v>74211.607533946561</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1624,8 +1623,20 @@
       <c r="C3">
         <v>69.37</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E3" t="str">
+        <v>Brooklyn</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2736074</v>
+      </c>
+      <c r="G3" s="5">
+        <v>69.37</v>
+      </c>
+      <c r="H3" s="5">
+        <v>39441.747152947959</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1635,8 +1646,20 @@
       <c r="C4">
         <v>108.53</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E4" t="str">
+        <v>Queens</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2405464</v>
+      </c>
+      <c r="G4" s="5">
+        <v>108.53</v>
+      </c>
+      <c r="H4" s="5">
+        <v>22164.046807334376</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1646,8 +1669,20 @@
       <c r="C5">
         <v>42.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E5" t="str">
+        <v>Bronx</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1472654</v>
+      </c>
+      <c r="G5" s="5">
+        <v>42.1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>34979.904988123511</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1657,40 +1692,47 @@
       <c r="C6">
         <v>58.37</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E6" t="str">
+        <v>Staten Island</v>
+      </c>
+      <c r="F6" s="5">
+        <v>495747</v>
+      </c>
+      <c r="G6" s="5">
+        <v>58.37</v>
+      </c>
+      <c r="H6" s="5">
+        <v>8493.1814288161731</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E8" t="str" cm="1">
-        <f t="array" aca="1" ref="E8:E13" ca="1">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
+        <f t="array" ref="E8:E13">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
         <v>population</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E9">
-        <f ca="1"/>
         <v>1694251</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E10">
-        <f ca="1"/>
         <v>2736074</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E11">
-        <f ca="1"/>
         <v>2405464</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E12">
-        <f ca="1"/>
         <v>1472654</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="E13">
-        <f ca="1"/>
         <v>495747</v>
       </c>
     </row>
@@ -1705,7 +1747,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G201"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1716,7 +1758,7 @@
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -1739,7 +1781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -1762,7 +1804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1785,7 +1827,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1808,7 +1850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1831,7 +1873,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1854,7 +1896,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -1877,7 +1919,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -1900,7 +1942,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1923,7 +1965,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>35</v>
       </c>
@@ -1946,7 +1988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -1969,7 +2011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>38</v>
       </c>
@@ -1992,7 +2034,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -2015,7 +2057,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -2038,7 +2080,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -2061,7 +2103,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -2084,7 +2126,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -2107,7 +2149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>47</v>
       </c>
@@ -2130,7 +2172,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>48</v>
       </c>
@@ -2153,7 +2195,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>49</v>
       </c>
@@ -2176,7 +2218,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>51</v>
       </c>
@@ -2199,7 +2241,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -2222,7 +2264,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -2245,7 +2287,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2268,7 +2310,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -2291,7 +2333,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2314,7 +2356,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -2337,7 +2379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>61</v>
       </c>
@@ -2360,7 +2402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>62</v>
       </c>
@@ -2383,7 +2425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -2406,7 +2448,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -2429,7 +2471,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>66</v>
       </c>
@@ -2452,7 +2494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -2475,7 +2517,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>68</v>
       </c>
@@ -2498,7 +2540,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -2521,7 +2563,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -2544,7 +2586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -2567,7 +2609,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -2590,7 +2632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>74</v>
       </c>
@@ -2613,7 +2655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -2636,7 +2678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -2659,7 +2701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>78</v>
       </c>
@@ -2682,7 +2724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>79</v>
       </c>
@@ -2705,7 +2747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>80</v>
       </c>
@@ -2728,7 +2770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>81</v>
       </c>
@@ -2751,7 +2793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>82</v>
       </c>
@@ -2774,7 +2816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>83</v>
       </c>
@@ -2797,7 +2839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>84</v>
       </c>
@@ -2820,7 +2862,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>85</v>
       </c>
@@ -2843,7 +2885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>86</v>
       </c>
@@ -2866,7 +2908,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>87</v>
       </c>
@@ -2889,7 +2931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>88</v>
       </c>
@@ -2912,7 +2954,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>89</v>
       </c>
@@ -2935,7 +2977,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>90</v>
       </c>
@@ -2958,7 +3000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>91</v>
       </c>
@@ -2981,7 +3023,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -3004,7 +3046,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>93</v>
       </c>
@@ -3027,7 +3069,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>94</v>
       </c>
@@ -3050,7 +3092,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>95</v>
       </c>
@@ -3073,7 +3115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>96</v>
       </c>
@@ -3096,7 +3138,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>97</v>
       </c>
@@ -3119,7 +3161,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>98</v>
       </c>
@@ -3142,7 +3184,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>99</v>
       </c>
@@ -3165,7 +3207,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>100</v>
       </c>
@@ -3188,7 +3230,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>101</v>
       </c>
@@ -3211,7 +3253,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>102</v>
       </c>
@@ -3231,7 +3273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>103</v>
       </c>
@@ -3254,7 +3296,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>104</v>
       </c>
@@ -3277,7 +3319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>105</v>
       </c>
@@ -3300,7 +3342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>106</v>
       </c>
@@ -3323,7 +3365,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>107</v>
       </c>
@@ -3346,7 +3388,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>108</v>
       </c>
@@ -3369,7 +3411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>109</v>
       </c>
@@ -3392,7 +3434,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>110</v>
       </c>
@@ -3415,7 +3457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>111</v>
       </c>
@@ -3438,7 +3480,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -3461,7 +3503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>113</v>
       </c>
@@ -3484,7 +3526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>114</v>
       </c>
@@ -3507,7 +3549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>115</v>
       </c>
@@ -3530,7 +3572,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>116</v>
       </c>
@@ -3553,7 +3595,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>117</v>
       </c>
@@ -3576,7 +3618,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>118</v>
       </c>
@@ -3599,7 +3641,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>119</v>
       </c>
@@ -3622,7 +3664,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>120</v>
       </c>
@@ -3645,7 +3687,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>121</v>
       </c>
@@ -3668,7 +3710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>122</v>
       </c>
@@ -3691,7 +3733,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>123</v>
       </c>
@@ -3714,7 +3756,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>124</v>
       </c>
@@ -3737,7 +3779,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>125</v>
       </c>
@@ -3760,7 +3802,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>126</v>
       </c>
@@ -3783,7 +3825,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>127</v>
       </c>
@@ -3806,7 +3848,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>128</v>
       </c>
@@ -3829,7 +3871,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>129</v>
       </c>
@@ -3852,7 +3894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>130</v>
       </c>
@@ -3875,7 +3917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>131</v>
       </c>
@@ -3898,7 +3940,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>132</v>
       </c>
@@ -3921,7 +3963,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>133</v>
       </c>
@@ -3944,7 +3986,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>134</v>
       </c>
@@ -3967,7 +4009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>135</v>
       </c>
@@ -3990,7 +4032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>136</v>
       </c>
@@ -4013,7 +4055,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>137</v>
       </c>
@@ -4036,7 +4078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>138</v>
       </c>
@@ -4059,7 +4101,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>139</v>
       </c>
@@ -4082,7 +4124,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>140</v>
       </c>
@@ -4105,7 +4147,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>141</v>
       </c>
@@ -4128,7 +4170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>142</v>
       </c>
@@ -4151,7 +4193,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>143</v>
       </c>
@@ -4174,7 +4216,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>144</v>
       </c>
@@ -4197,7 +4239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>145</v>
       </c>
@@ -4220,7 +4262,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>146</v>
       </c>
@@ -4243,7 +4285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>147</v>
       </c>
@@ -4266,7 +4308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>148</v>
       </c>
@@ -4289,7 +4331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>149</v>
       </c>
@@ -4312,7 +4354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>150</v>
       </c>
@@ -4335,7 +4377,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>151</v>
       </c>
@@ -4358,7 +4400,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>152</v>
       </c>
@@ -4381,7 +4423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>153</v>
       </c>
@@ -4404,7 +4446,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>154</v>
       </c>
@@ -4427,7 +4469,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>155</v>
       </c>
@@ -4450,7 +4492,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>156</v>
       </c>
@@ -4473,7 +4515,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>157</v>
       </c>
@@ -4496,7 +4538,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>158</v>
       </c>
@@ -4519,7 +4561,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>159</v>
       </c>
@@ -4542,7 +4584,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>160</v>
       </c>
@@ -4565,7 +4607,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>161</v>
       </c>
@@ -4588,7 +4630,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>162</v>
       </c>
@@ -4611,7 +4653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>163</v>
       </c>
@@ -4634,7 +4676,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>164</v>
       </c>
@@ -4654,7 +4696,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>165</v>
       </c>
@@ -4677,7 +4719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>166</v>
       </c>
@@ -4700,7 +4742,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>167</v>
       </c>
@@ -4723,7 +4765,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>168</v>
       </c>
@@ -4746,7 +4788,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>169</v>
       </c>
@@ -4769,7 +4811,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>170</v>
       </c>
@@ -4792,7 +4834,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>171</v>
       </c>
@@ -4815,7 +4857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>172</v>
       </c>
@@ -4838,7 +4880,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>173</v>
       </c>
@@ -4861,7 +4903,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>174</v>
       </c>
@@ -4884,7 +4926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>175</v>
       </c>
@@ -4907,7 +4949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>176</v>
       </c>
@@ -4930,7 +4972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>177</v>
       </c>
@@ -4953,7 +4995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>178</v>
       </c>
@@ -4976,7 +5018,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>179</v>
       </c>
@@ -4999,7 +5041,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>180</v>
       </c>
@@ -5022,7 +5064,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>181</v>
       </c>
@@ -5045,7 +5087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>182</v>
       </c>
@@ -5068,7 +5110,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>183</v>
       </c>
@@ -5091,7 +5133,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>184</v>
       </c>
@@ -5114,7 +5156,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>185</v>
       </c>
@@ -5134,7 +5176,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>186</v>
       </c>
@@ -5157,7 +5199,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>187</v>
       </c>
@@ -5180,7 +5222,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>188</v>
       </c>
@@ -5203,7 +5245,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>189</v>
       </c>
@@ -5226,7 +5268,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>190</v>
       </c>
@@ -5249,7 +5291,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>191</v>
       </c>
@@ -5272,7 +5314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>192</v>
       </c>
@@ -5292,7 +5334,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>193</v>
       </c>
@@ -5315,7 +5357,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>194</v>
       </c>
@@ -5338,7 +5380,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>195</v>
       </c>
@@ -5361,7 +5403,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>196</v>
       </c>
@@ -5384,7 +5426,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>197</v>
       </c>
@@ -5407,7 +5449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>198</v>
       </c>
@@ -5430,7 +5472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>199</v>
       </c>
@@ -5453,7 +5495,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>200</v>
       </c>
@@ -5473,7 +5515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>201</v>
       </c>
@@ -5496,7 +5538,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>202</v>
       </c>
@@ -5519,7 +5561,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>203</v>
       </c>
@@ -5542,7 +5584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>204</v>
       </c>
@@ -5565,7 +5607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>205</v>
       </c>
@@ -5588,7 +5630,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>206</v>
       </c>
@@ -5611,7 +5653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>207</v>
       </c>
@@ -5634,7 +5676,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>208</v>
       </c>
@@ -5657,7 +5699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>209</v>
       </c>
@@ -5677,7 +5719,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>210</v>
       </c>
@@ -5700,7 +5742,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>211</v>
       </c>
@@ -5723,7 +5765,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>212</v>
       </c>
@@ -5746,7 +5788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>213</v>
       </c>
@@ -5769,7 +5811,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>214</v>
       </c>
@@ -5792,7 +5834,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>215</v>
       </c>
@@ -5815,7 +5857,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>216</v>
       </c>
@@ -5838,7 +5880,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>217</v>
       </c>
@@ -5861,7 +5903,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>218</v>
       </c>
@@ -5884,7 +5926,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>219</v>
       </c>
@@ -5907,7 +5949,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>220</v>
       </c>
@@ -5930,7 +5972,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>221</v>
       </c>
@@ -5953,7 +5995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>222</v>
       </c>
@@ -5976,7 +6018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>223</v>
       </c>
@@ -5999,7 +6041,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>224</v>
       </c>
@@ -6022,7 +6064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>225</v>
       </c>
@@ -6045,7 +6087,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>226</v>
       </c>
@@ -6068,7 +6110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>227</v>
       </c>
@@ -6091,7 +6133,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>228</v>
       </c>
@@ -6114,7 +6156,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>229</v>
       </c>
@@ -6137,7 +6179,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>230</v>
       </c>
@@ -6160,7 +6202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
         <v>231</v>
       </c>
@@ -6183,7 +6225,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
         <v>232</v>
       </c>
@@ -6206,7 +6248,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
         <v>233</v>
       </c>
@@ -6229,7 +6271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
         <v>234</v>
       </c>
@@ -6252,7 +6294,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
         <v>235</v>
       </c>
@@ -6275,7 +6317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>236</v>
       </c>
@@ -6298,7 +6340,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
         <v>237</v>
       </c>
@@ -6331,3334 +6373,2577 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E979612-8BD7-40EA-9D5A-2165C0273E84}">
-  <dimension ref="A1:H189"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:H184"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.41015625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.29296875" customWidth="1"/>
-    <col min="4" max="4" width="12.41015625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.17578125" customWidth="1"/>
-    <col min="6" max="6" width="11.9375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.265625" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.19921875" customWidth="1"/>
+    <col min="6" max="6" width="11.9296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.9375" customWidth="1"/>
+    <col min="8" max="8" width="13.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A1" t="e" cm="1" vm="2">
-        <f t="array" aca="1" ref="A1" ca="1">_xlfn._xlws.PY(1,1,sales[#All])</f>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" t="e" cm="1" vm="1">
+        <f t="array" ref="A1">_xlfn._xlws.PY(1,1,sales[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="str" cm="1">
-        <f t="array" aca="1" ref="A3:G8" ca="1">_xlfn._xlws.PY(2,0)</f>
+        <f t="array" ref="A3:G8">_xlfn._xlws.PY(2,0)</f>
         <v>order_id</v>
       </c>
       <c r="B3" t="str">
-        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="C3" t="str">
-        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="D3" t="str">
-        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="E3" t="str">
-        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="F3" t="str">
-        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="G3" t="str">
-        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
-        <f ca="1"/>
         <v>ORD-0001</v>
       </c>
       <c r="B4" t="str">
-        <f ca="1"/>
         <v>Desk</v>
       </c>
       <c r="C4" t="str">
-        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="D4">
-        <f ca="1"/>
         <v>68.760000000000005</v>
       </c>
       <c r="E4">
-        <f ca="1"/>
         <v>5</v>
       </c>
       <c r="F4">
-        <f ca="1"/>
         <v>37</v>
       </c>
       <c r="G4" t="str">
-        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
-        <f ca="1"/>
         <v>ORD-0002</v>
       </c>
       <c r="B5" t="str">
-        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="C5" t="str">
-        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="D5">
-        <f ca="1"/>
         <v>115.2</v>
       </c>
       <c r="E5">
-        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="F5">
-        <f ca="1"/>
         <v>24</v>
       </c>
       <c r="G5" t="str">
-        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
-        <f ca="1"/>
         <v>ORD-0003</v>
       </c>
       <c r="B6" t="str">
-        <f ca="1"/>
         <v>Lamp</v>
       </c>
       <c r="C6" t="str">
-        <f ca="1"/>
         <v>Furniture</v>
       </c>
       <c r="D6">
-        <f ca="1"/>
         <v>69.900000000000006</v>
       </c>
       <c r="E6">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="F6">
-        <f ca="1"/>
         <v>63</v>
       </c>
       <c r="G6" t="str">
-        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
-        <f ca="1"/>
         <v>ORD-0004</v>
       </c>
       <c r="B7" t="str">
-        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="C7" t="str">
-        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="D7">
-        <f ca="1"/>
         <v>15.35</v>
       </c>
       <c r="E7">
-        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="F7">
-        <f ca="1"/>
         <v>32</v>
       </c>
       <c r="G7" t="str">
-        <f ca="1"/>
         <v>Germany</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
-        <f ca="1"/>
         <v>ORD-0005</v>
       </c>
       <c r="B8" t="str">
-        <f ca="1"/>
         <v>Tablet</v>
       </c>
       <c r="C8" t="str">
-        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="D8">
-        <f ca="1"/>
         <v>479.68</v>
       </c>
       <c r="E8">
-        <f ca="1"/>
         <v>6</v>
       </c>
       <c r="F8">
-        <f ca="1"/>
         <v>28</v>
       </c>
       <c r="G8" t="str">
-        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="str" cm="1">
-        <f t="array" aca="1" ref="A10:H15" ca="1">_xlfn._xlws.PY(3,0)</f>
+        <f t="array" ref="A10:H15">_xlfn._xlws.PY(3,0)</f>
         <v/>
       </c>
       <c r="B10" t="str">
-        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C10" t="str">
-        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D10" t="str">
-        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E10" t="str">
-        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F10" t="str">
-        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G10" t="str">
-        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H10" t="str">
-        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11">
-        <f ca="1"/>
         <v>195</v>
       </c>
       <c r="B11" t="str">
-        <f ca="1"/>
         <v>ORD-0196</v>
       </c>
       <c r="C11" t="str">
-        <f ca="1"/>
         <v>Headphones</v>
       </c>
       <c r="D11" t="str">
-        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E11">
-        <f ca="1"/>
         <v>162.49</v>
       </c>
       <c r="F11">
-        <f ca="1"/>
         <v>2</v>
       </c>
       <c r="G11">
-        <f ca="1"/>
         <v>22</v>
       </c>
       <c r="H11" t="str">
-        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12">
-        <f ca="1"/>
         <v>196</v>
       </c>
       <c r="B12" t="str">
-        <f ca="1"/>
         <v>ORD-0197</v>
       </c>
       <c r="C12" t="str">
-        <f ca="1"/>
         <v>Monitor</v>
       </c>
       <c r="D12" t="str">
-        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E12">
-        <f ca="1"/>
         <v>277.98</v>
       </c>
       <c r="F12">
-        <f ca="1"/>
         <v>4</v>
       </c>
       <c r="G12">
-        <f ca="1"/>
         <v>54</v>
       </c>
       <c r="H12" t="str">
-        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13">
-        <f ca="1"/>
         <v>197</v>
       </c>
       <c r="B13" t="str">
-        <f ca="1"/>
         <v>ORD-0198</v>
       </c>
       <c r="C13" t="str">
-        <f ca="1"/>
         <v>Printer Paper</v>
       </c>
       <c r="D13" t="str">
-        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E13">
-        <f ca="1"/>
         <v>21.06</v>
       </c>
       <c r="F13">
-        <f ca="1"/>
         <v>1</v>
       </c>
       <c r="G13">
-        <f ca="1"/>
         <v>49</v>
       </c>
       <c r="H13" t="str">
-        <f ca="1"/>
         <v>United States</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14">
-        <f ca="1"/>
         <v>198</v>
       </c>
       <c r="B14" t="str">
-        <f ca="1"/>
         <v>ORD-0199</v>
       </c>
       <c r="C14" t="str">
-        <f ca="1"/>
         <v>Notebook</v>
       </c>
       <c r="D14" t="str">
-        <f ca="1"/>
         <v>Office Supplies</v>
       </c>
       <c r="E14">
-        <f ca="1"/>
         <v>22.61</v>
       </c>
       <c r="F14">
-        <f ca="1"/>
         <v>7</v>
       </c>
       <c r="G14">
-        <f ca="1"/>
         <v>62</v>
       </c>
       <c r="H14" t="str">
-        <f ca="1"/>
         <v>United Kingdom</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15">
-        <f ca="1"/>
         <v>199</v>
       </c>
       <c r="B15" t="str">
-        <f ca="1"/>
         <v>ORD-0200</v>
       </c>
       <c r="C15" t="str">
-        <f ca="1"/>
         <v>Headphones</v>
       </c>
       <c r="D15" t="str">
-        <f ca="1"/>
         <v>Electronics</v>
       </c>
       <c r="E15">
-        <f ca="1"/>
         <v>106.64</v>
       </c>
       <c r="F15">
-        <f ca="1"/>
         <v>10</v>
       </c>
       <c r="G15">
-        <f ca="1"/>
         <v>51</v>
       </c>
       <c r="H15" t="str">
-        <f ca="1"/>
         <v>Canada</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="str" cm="1">
-        <f t="array" aca="1" ref="A17:H22" ca="1">_xlfn._xlws.PY(4,0)</f>
+        <f t="array" ref="A17:H22">_xlfn._xlws.PY(4,0)</f>
         <v/>
       </c>
       <c r="B17" t="str">
-        <f ca="1"/>
         <v>order_id</v>
       </c>
       <c r="C17" t="str">
-        <f ca="1"/>
         <v>product</v>
       </c>
       <c r="D17" t="str">
-        <f ca="1"/>
         <v>category</v>
       </c>
       <c r="E17" t="str">
-        <f ca="1"/>
         <v>unit_price</v>
       </c>
       <c r="F17" t="str">
-        <f ca="1"/>
         <v>quantity</v>
       </c>
       <c r="G17" t="str">
-        <f ca="1"/>
         <v>customer_age</v>
       </c>
       <c r="H17" t="str">
-        <f ca="1"/>
         <v>country</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18">
-        <f ca="1"/>
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="B18" t="str">
-        <f ca="1"/>
-        <v>ORD-0113</v>
+        <v>ORD-0001</v>
       </c>
       <c r="C18" t="str">
-        <f ca="1"/>
+        <v>Desk</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E18">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>37</v>
+      </c>
+      <c r="H18" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>75</v>
+      </c>
+      <c r="B19" t="str">
+        <v>ORD-0076</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Pens</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E19">
+        <v>15.18</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19">
+        <v>40</v>
+      </c>
+      <c r="H19" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>25</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ORD-0026</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Filing Cabinet</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E20">
+        <v>140.75</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>26</v>
+      </c>
+      <c r="H20" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>120</v>
+      </c>
+      <c r="B21" t="str">
+        <v>ORD-0121</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Stapler</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E21">
+        <v>5.86</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>49</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>130</v>
+      </c>
+      <c r="B22" t="str">
+        <v>ORD-0131</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Keyboard</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E22">
+        <v>218.8</v>
+      </c>
+      <c r="F22">
+        <v>4</v>
+      </c>
+      <c r="G22">
+        <v>29</v>
+      </c>
+      <c r="H22" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A24" t="str" cm="1">
+        <f t="array" ref="A24:B30">_xlfn._xlws.PY(5,0)</f>
+        <v>order_id</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25" t="str">
+        <v>product</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A26" t="str">
+        <v>category</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A28" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A29" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="B29">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A30" t="str">
+        <v>country</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A32" t="str" cm="1">
+        <f t="array" ref="A32:B38">_xlfn._xlws.PY(6,0)</f>
+        <v>customer_age</v>
+      </c>
+      <c r="B32">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A33" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A34" t="str">
+        <v>product</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A35" t="str">
+        <v>category</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A36" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A37" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="str">
+        <v>country</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A40" cm="1">
+        <f t="array" ref="A40:A41">_xlfn._xlws.PY(7,0)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A43" t="str" cm="1">
+        <f t="array" ref="A43:D51">_xlfn._xlws.PY(8,0)</f>
+        <v/>
+      </c>
+      <c r="B43" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="C43" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="D43" t="str">
+        <v>customer_age</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A44" t="str">
+        <v>count</v>
+      </c>
+      <c r="B44">
+        <v>200</v>
+      </c>
+      <c r="C44">
+        <v>200</v>
+      </c>
+      <c r="D44">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A45" t="str">
+        <v>mean</v>
+      </c>
+      <c r="B45">
+        <v>211.94830000000002</v>
+      </c>
+      <c r="C45">
+        <v>5.7</v>
+      </c>
+      <c r="D45">
+        <v>43.597938144329895</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A46" t="str">
+        <v>std</v>
+      </c>
+      <c r="B46">
+        <v>215.73323312713649</v>
+      </c>
+      <c r="C46">
+        <v>2.7252771745993041</v>
+      </c>
+      <c r="D46">
+        <v>13.286527356620564</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A47" t="str">
+        <v>min</v>
+      </c>
+      <c r="B47">
+        <v>2.17</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A48" t="str">
+        <v>25%</v>
+      </c>
+      <c r="B48">
+        <v>31.2075</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A49" t="str">
+        <v>50%</v>
+      </c>
+      <c r="B49">
+        <v>111.38</v>
+      </c>
+      <c r="C49">
+        <v>5.5</v>
+      </c>
+      <c r="D49">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A50" t="str">
+        <v>75%</v>
+      </c>
+      <c r="B50">
+        <v>378.83</v>
+      </c>
+      <c r="C50">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>55.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A51" t="str">
+        <v>max</v>
+      </c>
+      <c r="B51">
+        <v>760.69</v>
+      </c>
+      <c r="C51">
+        <v>10</v>
+      </c>
+      <c r="D51">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A53" t="str" cm="1">
+        <f t="array" ref="A53:D61">_xlfn._xlws.PY(9,0)</f>
+        <v/>
+      </c>
+      <c r="B53" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="C53" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="D53" t="str">
+        <v>customer_age</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" t="str">
+        <v>count</v>
+      </c>
+      <c r="B54">
+        <v>200</v>
+      </c>
+      <c r="C54">
+        <v>200</v>
+      </c>
+      <c r="D54">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A55" t="str">
+        <v>mean</v>
+      </c>
+      <c r="B55">
+        <v>211.94830000000002</v>
+      </c>
+      <c r="C55">
+        <v>5.7</v>
+      </c>
+      <c r="D55">
+        <v>43.597938144329895</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A56" t="str">
+        <v>std</v>
+      </c>
+      <c r="B56">
+        <v>215.73323312713649</v>
+      </c>
+      <c r="C56">
+        <v>2.7252771745993041</v>
+      </c>
+      <c r="D56">
+        <v>13.286527356620564</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A57" t="str">
+        <v>min</v>
+      </c>
+      <c r="B57">
+        <v>2.17</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A58" t="str">
+        <v>10%</v>
+      </c>
+      <c r="B58">
+        <v>13.033000000000001</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" t="str">
+        <v>50%</v>
+      </c>
+      <c r="B59">
+        <v>111.38</v>
+      </c>
+      <c r="C59">
+        <v>5.5</v>
+      </c>
+      <c r="D59">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" t="str">
+        <v>90%</v>
+      </c>
+      <c r="B60">
+        <v>512.85599999999999</v>
+      </c>
+      <c r="C60">
+        <v>9.0999999999999943</v>
+      </c>
+      <c r="D60">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A61" t="str">
+        <v>max</v>
+      </c>
+      <c r="B61">
+        <v>760.69</v>
+      </c>
+      <c r="C61">
+        <v>10</v>
+      </c>
+      <c r="D61">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A63" t="str" cm="1">
+        <f t="array" ref="A63:E67">_xlfn._xlws.PY(10,0)</f>
+        <v/>
+      </c>
+      <c r="B63" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C63" t="str">
+        <v>product</v>
+      </c>
+      <c r="D63" t="str">
+        <v>category</v>
+      </c>
+      <c r="E63" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" t="str">
+        <v>count</v>
+      </c>
+      <c r="B64">
+        <v>200</v>
+      </c>
+      <c r="C64">
+        <v>200</v>
+      </c>
+      <c r="D64">
+        <v>200</v>
+      </c>
+      <c r="E64">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A65" t="str">
+        <v>unique</v>
+      </c>
+      <c r="B65">
+        <v>200</v>
+      </c>
+      <c r="C65">
+        <v>15</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A66" t="str">
+        <v>top</v>
+      </c>
+      <c r="B66" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="C66" t="str">
         <v>Notebook</v>
       </c>
-      <c r="D18" t="str">
-        <f ca="1"/>
+      <c r="D66" t="str">
         <v>Office Supplies</v>
       </c>
-      <c r="E18">
-        <f ca="1"/>
-        <v>49.52</v>
-      </c>
-      <c r="F18">
-        <f ca="1"/>
+      <c r="E66" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A67" t="str">
+        <v>freq</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>19</v>
+      </c>
+      <c r="D67">
+        <v>80</v>
+      </c>
+      <c r="E67">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A69" t="str" cm="1">
+        <f t="array" ref="A69:C74">_xlfn._xlws.PY(11,0)</f>
+        <v>product</v>
+      </c>
+      <c r="B69" t="str">
+        <v>category</v>
+      </c>
+      <c r="C69" t="str">
+        <v>unit_price</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A70" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C70">
+        <v>68.760000000000005</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A71" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C71">
+        <v>115.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A72" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C72">
+        <v>69.900000000000006</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A73" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C73">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A74" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C74">
+        <v>479.68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A76" t="str" cm="1">
+        <f t="array" ref="A76:A81">_xlfn._xlws.PY(12,0)</f>
+        <v>country</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A77" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A78" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A79" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A80" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A81" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A84" t="str" cm="1">
+        <f t="array" ref="A84:H89">_xlfn._xlws.PY(13,0)</f>
+        <v/>
+      </c>
+      <c r="B84" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C84" t="str">
+        <v>product</v>
+      </c>
+      <c r="D84" t="str">
+        <v>category</v>
+      </c>
+      <c r="E84" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F84" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G84" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H84" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <v>0</v>
+      </c>
+      <c r="B85" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E85">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="F85">
         <v>5</v>
       </c>
-      <c r="G18">
-        <f ca="1"/>
-        <v>58</v>
-      </c>
-      <c r="H18" t="str">
-        <f ca="1"/>
+      <c r="G85">
+        <v>37</v>
+      </c>
+      <c r="H85" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <v>1</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ORD-0002</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E86">
+        <v>115.2</v>
+      </c>
+      <c r="F86">
+        <v>7</v>
+      </c>
+      <c r="G86">
+        <v>24</v>
+      </c>
+      <c r="H86" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <v>4</v>
+      </c>
+      <c r="B87" t="str">
+        <v>ORD-0005</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E87">
+        <v>479.68</v>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87">
+        <v>28</v>
+      </c>
+      <c r="H87" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <v>11</v>
+      </c>
+      <c r="B88" t="str">
+        <v>ORD-0012</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E88">
+        <v>415.36</v>
+      </c>
+      <c r="F88">
+        <v>6</v>
+      </c>
+      <c r="G88">
+        <v>47</v>
+      </c>
+      <c r="H88" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <v>13</v>
+      </c>
+      <c r="B89" t="str">
+        <v>ORD-0014</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Headphones</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E89">
+        <v>91.32</v>
+      </c>
+      <c r="F89">
+        <v>9</v>
+      </c>
+      <c r="G89">
+        <v>56</v>
+      </c>
+      <c r="H89" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A91" t="str" cm="1">
+        <f t="array" ref="A91:H96">_xlfn._xlws.PY(14,0)</f>
+        <v/>
+      </c>
+      <c r="B91" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C91" t="str">
+        <v>product</v>
+      </c>
+      <c r="D91" t="str">
+        <v>category</v>
+      </c>
+      <c r="E91" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F91" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G91" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H91" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <v>0</v>
+      </c>
+      <c r="B92" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E92">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="F92">
+        <v>5</v>
+      </c>
+      <c r="G92">
+        <v>37</v>
+      </c>
+      <c r="H92" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <v>1</v>
+      </c>
+      <c r="B93" t="str">
+        <v>ORD-0002</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E93">
+        <v>115.2</v>
+      </c>
+      <c r="F93">
+        <v>7</v>
+      </c>
+      <c r="G93">
+        <v>24</v>
+      </c>
+      <c r="H93" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <v>4</v>
+      </c>
+      <c r="B94" t="str">
+        <v>ORD-0005</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E94">
+        <v>479.68</v>
+      </c>
+      <c r="F94">
+        <v>6</v>
+      </c>
+      <c r="G94">
+        <v>28</v>
+      </c>
+      <c r="H94" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <v>11</v>
+      </c>
+      <c r="B95" t="str">
+        <v>ORD-0012</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E95">
+        <v>415.36</v>
+      </c>
+      <c r="F95">
+        <v>6</v>
+      </c>
+      <c r="G95">
+        <v>47</v>
+      </c>
+      <c r="H95" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <v>13</v>
+      </c>
+      <c r="B96" t="str">
+        <v>ORD-0014</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Headphones</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E96">
+        <v>91.32</v>
+      </c>
+      <c r="F96">
+        <v>9</v>
+      </c>
+      <c r="G96">
+        <v>56</v>
+      </c>
+      <c r="H96" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A98" t="str" cm="1">
+        <f t="array" ref="A98:H103">_xlfn._xlws.PY(15,0)</f>
+        <v/>
+      </c>
+      <c r="B98" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C98" t="str">
+        <v>product</v>
+      </c>
+      <c r="D98" t="str">
+        <v>category</v>
+      </c>
+      <c r="E98" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F98" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G98" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H98" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <v>0</v>
+      </c>
+      <c r="B99" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E99">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="F99">
+        <v>5</v>
+      </c>
+      <c r="G99">
+        <v>37</v>
+      </c>
+      <c r="H99" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <v>1</v>
+      </c>
+      <c r="B100" t="str">
+        <v>ORD-0002</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E100">
+        <v>115.2</v>
+      </c>
+      <c r="F100">
+        <v>7</v>
+      </c>
+      <c r="G100">
+        <v>24</v>
+      </c>
+      <c r="H100" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <v>4</v>
+      </c>
+      <c r="B101" t="str">
+        <v>ORD-0005</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E101">
+        <v>479.68</v>
+      </c>
+      <c r="F101">
+        <v>6</v>
+      </c>
+      <c r="G101">
+        <v>28</v>
+      </c>
+      <c r="H101" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A102">
+        <v>11</v>
+      </c>
+      <c r="B102" t="str">
+        <v>ORD-0012</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E102">
+        <v>415.36</v>
+      </c>
+      <c r="F102">
+        <v>6</v>
+      </c>
+      <c r="G102">
+        <v>47</v>
+      </c>
+      <c r="H102" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A103">
+        <v>13</v>
+      </c>
+      <c r="B103" t="str">
+        <v>ORD-0014</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Headphones</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E103">
+        <v>91.32</v>
+      </c>
+      <c r="F103">
+        <v>9</v>
+      </c>
+      <c r="G103">
+        <v>56</v>
+      </c>
+      <c r="H103" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A105" t="str" cm="1">
+        <f t="array" ref="A105:H110">_xlfn._xlws.PY(16,0)</f>
+        <v/>
+      </c>
+      <c r="B105" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C105" t="str">
+        <v>product</v>
+      </c>
+      <c r="D105" t="str">
+        <v>category</v>
+      </c>
+      <c r="E105" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F105" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G105" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H105" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A106">
+        <v>48</v>
+      </c>
+      <c r="B106" t="str">
+        <v>ORD-0049</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Printer Paper</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E106">
+        <v>2.17</v>
+      </c>
+      <c r="F106">
+        <v>3</v>
+      </c>
+      <c r="G106">
+        <v>62</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A107">
+        <v>79</v>
+      </c>
+      <c r="B107" t="str">
+        <v>ORD-0080</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Stapler</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E107">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F107">
+        <v>6</v>
+      </c>
+      <c r="G107">
+        <v>41</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A108">
+        <v>99</v>
+      </c>
+      <c r="B108" t="str">
+        <v>ORD-0100</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E108">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="F108">
+        <v>4</v>
+      </c>
+      <c r="G108">
+        <v>27</v>
+      </c>
+      <c r="H108" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A109">
+        <v>142</v>
+      </c>
+      <c r="B109" t="str">
+        <v>ORD-0143</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E109">
+        <v>3.72</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
+      </c>
+      <c r="G109">
+        <v>37</v>
+      </c>
+      <c r="H109" t="str">
         <v>Germany</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A19">
-        <f ca="1"/>
-        <v>180</v>
-      </c>
-      <c r="B19" t="str">
-        <f ca="1"/>
-        <v>ORD-0181</v>
-      </c>
-      <c r="C19" t="str">
-        <f ca="1"/>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A110">
+        <v>21</v>
+      </c>
+      <c r="B110" t="str">
+        <v>ORD-0022</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Pens</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E110">
+        <v>4.78</v>
+      </c>
+      <c r="F110">
+        <v>10</v>
+      </c>
+      <c r="G110">
+        <v>27</v>
+      </c>
+      <c r="H110" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A113" t="str" cm="1">
+        <f t="array" ref="A113:H118">_xlfn._xlws.PY(17,0)</f>
+        <v/>
+      </c>
+      <c r="B113" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C113" t="str">
+        <v>product</v>
+      </c>
+      <c r="D113" t="str">
+        <v>category</v>
+      </c>
+      <c r="E113" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F113" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G113" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H113" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>ORD-0114</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E114">
+        <v>760.69</v>
+      </c>
+      <c r="F114">
+        <v>4</v>
+      </c>
+      <c r="G114">
+        <v>62</v>
+      </c>
+      <c r="H114" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A115">
+        <v>165</v>
+      </c>
+      <c r="B115" t="str">
+        <v>ORD-0166</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Filing Cabinet</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E115">
+        <v>754.29</v>
+      </c>
+      <c r="F115">
+        <v>5</v>
+      </c>
+      <c r="G115">
+        <v>24</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A116">
+        <v>45</v>
+      </c>
+      <c r="B116" t="str">
+        <v>ORD-0046</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E116">
+        <v>754.2</v>
+      </c>
+      <c r="F116">
+        <v>3</v>
+      </c>
+      <c r="G116">
+        <v>38</v>
+      </c>
+      <c r="H116" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <v>40</v>
+      </c>
+      <c r="B117" t="str">
+        <v>ORD-0041</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Bookshelf</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E117">
+        <v>751.03</v>
+      </c>
+      <c r="F117">
+        <v>4</v>
+      </c>
+      <c r="G117">
+        <v>64</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A118">
+        <v>152</v>
+      </c>
+      <c r="B118" t="str">
+        <v>ORD-0153</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E118">
+        <v>732.96</v>
+      </c>
+      <c r="F118">
+        <v>8</v>
+      </c>
+      <c r="G118">
+        <v>40</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A121" t="str" cm="1">
+        <f t="array" ref="A121:H126">_xlfn._xlws.PY(18,0)</f>
+        <v/>
+      </c>
+      <c r="B121" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C121" t="str">
+        <v>product</v>
+      </c>
+      <c r="D121" t="str">
+        <v>category</v>
+      </c>
+      <c r="E121" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F121" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G121" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H121" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A122">
+        <v>48</v>
+      </c>
+      <c r="B122" t="str">
+        <v>ORD-0049</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Printer Paper</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E122">
+        <v>2.17</v>
+      </c>
+      <c r="F122">
+        <v>3</v>
+      </c>
+      <c r="G122">
+        <v>62</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A123">
+        <v>32</v>
+      </c>
+      <c r="B123" t="str">
+        <v>ORD-0033</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E123">
+        <v>6.7</v>
+      </c>
+      <c r="F123">
+        <v>9</v>
+      </c>
+      <c r="G123">
+        <v>22</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A124">
+        <v>119</v>
+      </c>
+      <c r="B124" t="str">
+        <v>ORD-0120</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Stapler</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E124">
+        <v>7.97</v>
+      </c>
+      <c r="F124">
+        <v>5</v>
+      </c>
+      <c r="G124">
+        <v>47</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A125">
+        <v>181</v>
+      </c>
+      <c r="B125" t="str">
+        <v>ORD-0182</v>
+      </c>
+      <c r="C125" t="str">
         <v>Binder</v>
       </c>
-      <c r="D19" t="str">
-        <f ca="1"/>
+      <c r="D125" t="str">
         <v>Office Supplies</v>
       </c>
-      <c r="E19">
-        <f ca="1"/>
-        <v>41.72</v>
-      </c>
-      <c r="F19">
-        <f ca="1"/>
+      <c r="E125">
+        <v>19.97</v>
+      </c>
+      <c r="F125">
+        <v>3</v>
+      </c>
+      <c r="G125">
+        <v>65</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A126">
+        <v>34</v>
+      </c>
+      <c r="B126" t="str">
+        <v>ORD-0035</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Monitor</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E126">
+        <v>26.02</v>
+      </c>
+      <c r="F126">
         <v>7</v>
       </c>
-      <c r="G19">
-        <f ca="1"/>
-        <v>48</v>
-      </c>
-      <c r="H19" t="str">
-        <f ca="1"/>
+      <c r="G126">
+        <v>38</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A129" t="str" cm="1">
+        <f t="array" ref="A129:H134">_xlfn._xlws.PY(19,0)</f>
+        <v/>
+      </c>
+      <c r="B129" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C129" t="str">
+        <v>product</v>
+      </c>
+      <c r="D129" t="str">
+        <v>category</v>
+      </c>
+      <c r="E129" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F129" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G129" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H129" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A130">
+        <v>113</v>
+      </c>
+      <c r="B130" t="str">
+        <v>ORD-0114</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E130">
+        <v>760.69</v>
+      </c>
+      <c r="F130">
+        <v>4</v>
+      </c>
+      <c r="G130">
+        <v>62</v>
+      </c>
+      <c r="H130" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A131">
+        <v>165</v>
+      </c>
+      <c r="B131" t="str">
+        <v>ORD-0166</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Filing Cabinet</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E131">
+        <v>754.29</v>
+      </c>
+      <c r="F131">
+        <v>5</v>
+      </c>
+      <c r="G131">
+        <v>24</v>
+      </c>
+      <c r="H131" t="str">
         <v>Germany</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A20">
-        <f ca="1"/>
-        <v>82</v>
-      </c>
-      <c r="B20" t="str">
-        <f ca="1"/>
-        <v>ORD-0083</v>
-      </c>
-      <c r="C20" t="str">
-        <f ca="1"/>
-        <v>Chair</v>
-      </c>
-      <c r="D20" t="str">
-        <f ca="1"/>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A132">
+        <v>45</v>
+      </c>
+      <c r="B132" t="str">
+        <v>ORD-0046</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D132" t="str">
         <v>Furniture</v>
       </c>
-      <c r="E20">
-        <f ca="1"/>
-        <v>680.38</v>
-      </c>
-      <c r="F20">
-        <f ca="1"/>
+      <c r="E132">
+        <v>754.2</v>
+      </c>
+      <c r="F132">
         <v>3</v>
       </c>
-      <c r="G20">
-        <f ca="1"/>
-        <v>61</v>
-      </c>
-      <c r="H20" t="str">
-        <f ca="1"/>
+      <c r="G132">
+        <v>38</v>
+      </c>
+      <c r="H132" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A133">
+        <v>40</v>
+      </c>
+      <c r="B133" t="str">
+        <v>ORD-0041</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Bookshelf</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E133">
+        <v>751.03</v>
+      </c>
+      <c r="F133">
+        <v>4</v>
+      </c>
+      <c r="G133">
+        <v>64</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A134">
+        <v>152</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ORD-0153</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E134">
+        <v>732.96</v>
+      </c>
+      <c r="F134">
+        <v>8</v>
+      </c>
+      <c r="G134">
+        <v>40</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A136" t="str" cm="1">
+        <f t="array" ref="A136:B141">_xlfn._xlws.PY(20,0)</f>
+        <v>country</v>
+      </c>
+      <c r="B136" t="str">
+        <v>count</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A137" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B137">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A138" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B138">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A139" t="str">
         <v>United Kingdom</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A21">
-        <f ca="1"/>
-        <v>46</v>
-      </c>
-      <c r="B21" t="str">
-        <f ca="1"/>
-        <v>ORD-0047</v>
-      </c>
-      <c r="C21" t="str">
-        <f ca="1"/>
-        <v>Chair</v>
-      </c>
-      <c r="D21" t="str">
-        <f ca="1"/>
+      <c r="B139">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A140" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B140">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A141" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B141">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A144" t="str" cm="1">
+        <f t="array" ref="A144:B147">_xlfn._xlws.PY(21,0)</f>
+        <v>category</v>
+      </c>
+      <c r="B144" t="str">
+        <v>proportion</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A145" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="B145">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A146" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="B146">
+        <v>0.32500000000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A147" t="str">
         <v>Furniture</v>
       </c>
-      <c r="E21">
-        <f ca="1"/>
-        <v>254.26</v>
-      </c>
-      <c r="F21">
-        <f ca="1"/>
-        <v>10</v>
-      </c>
-      <c r="G21">
-        <f ca="1"/>
-        <v>35</v>
-      </c>
-      <c r="H21" t="str">
-        <f ca="1"/>
+      <c r="B147">
+        <v>0.27500000000000002</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A149" t="str" cm="1">
+        <f t="array" ref="A149:B154">_xlfn._xlws.PY(22,0)</f>
+        <v>country</v>
+      </c>
+      <c r="B149" t="str">
+        <v>unit_price</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A150" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B150">
+        <v>167.16199999999998</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A151" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B151">
+        <v>201.18230769230769</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A152" t="str">
         <v>Germany</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A22">
-        <f ca="1"/>
-        <v>69</v>
-      </c>
-      <c r="B22" t="str">
-        <f ca="1"/>
-        <v>ORD-0070</v>
-      </c>
-      <c r="C22" t="str">
-        <f ca="1"/>
-        <v>Notebook</v>
-      </c>
-      <c r="D22" t="str">
-        <f ca="1"/>
+      <c r="B152">
+        <v>182.58790697674419</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A153" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B153">
+        <v>274.43128205128204</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A154" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B154">
+        <v>209.05701298701297</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A156" t="str" cm="1">
+        <f t="array" ref="A156:B159">_xlfn._xlws.PY(23,0)</f>
+        <v>category</v>
+      </c>
+      <c r="B156" t="str">
+        <v>quantity</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A157" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="B157">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A158" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="B158">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A159" t="str">
         <v>Office Supplies</v>
       </c>
-      <c r="E22">
-        <f ca="1"/>
-        <v>11.33</v>
-      </c>
-      <c r="F22">
-        <f ca="1"/>
-        <v>7</v>
-      </c>
-      <c r="G22">
-        <f ca="1"/>
-        <v>53</v>
-      </c>
-      <c r="H22" t="str">
-        <f ca="1"/>
+      <c r="B159">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A161" t="str" cm="1">
+        <f t="array" ref="A161:C176">_xlfn._xlws.PY(24,0)</f>
+        <v>country</v>
+      </c>
+      <c r="B161" t="str">
+        <v>category</v>
+      </c>
+      <c r="C161" t="str">
+        <v>unit_price</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A162" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C162">
+        <v>270.6516666666667</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A163" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C163">
+        <v>256.68</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A164" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C164">
+        <v>18.91333333333333</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A165" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C165">
+        <v>274.04250000000002</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A166" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C166">
+        <v>529.45000000000005</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A167" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C167">
+        <v>30.088461538461541</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A168" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C168">
+        <v>230.67818181818183</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A169" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C169">
+        <v>350.0864285714286</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A170" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C170">
+        <v>22.922777777777778</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A171" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C171">
+        <v>272.95764705882351</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A172" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C172">
+        <v>529.8054545454545</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A173" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C173">
+        <v>21.334545454545456</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A174" t="str">
         <v>United States</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A24" t="str" cm="1">
-        <f t="array" aca="1" ref="A24:B30" ca="1">_xlfn._xlws.PY(5,0)</f>
-        <v>order_id</v>
-      </c>
-      <c r="B24">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A25" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="B25">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A26" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="B26">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A27" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="B27">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A28" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="B28">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A29" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-      <c r="B29">
-        <f ca="1"/>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A30" t="str">
-        <f ca="1"/>
+      <c r="B174" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C174">
+        <v>296.6995652173913</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A175" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C175">
+        <v>383.92954545454546</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A176" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C176">
+        <v>25.839062500000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A178" t="str" cm="1">
+        <f t="array" ref="A178:D184">_xlfn._xlws.PY(25,0)</f>
+        <v/>
+      </c>
+      <c r="B178" t="str">
+        <v>mean</v>
+      </c>
+      <c r="C178" t="str">
+        <v>min</v>
+      </c>
+      <c r="D178" t="str">
+        <v>max</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A179" t="str">
         <v>country</v>
       </c>
-      <c r="B30">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A32" t="str" cm="1">
-        <f t="array" aca="1" ref="A32:B38" ca="1">_xlfn._xlws.PY(6,0)</f>
-        <v>customer_age</v>
-      </c>
-      <c r="B32">
-        <f ca="1"/>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A33" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="B33">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A34" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="B34">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A35" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="B35">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A36" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="B36">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A37" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="B37">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A38" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-      <c r="B38">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A40" cm="1">
-        <f t="array" aca="1" ref="A40:A41" ca="1">_xlfn._xlws.PY(7,0)</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A41">
-        <f ca="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A43" t="str" cm="1">
-        <f t="array" aca="1" ref="A43:D51" ca="1">_xlfn._xlws.PY(8,0)</f>
+      <c r="B179" t="str">
         <v/>
       </c>
-      <c r="B43" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="C43" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="D43" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A44" t="str">
-        <f ca="1"/>
-        <v>count</v>
-      </c>
-      <c r="B44">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-      <c r="C44">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-      <c r="D44">
-        <f ca="1"/>
-        <v>194</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A45" t="str">
-        <f ca="1"/>
-        <v>mean</v>
-      </c>
-      <c r="B45">
-        <f ca="1"/>
-        <v>211.94830000000002</v>
-      </c>
-      <c r="C45">
-        <f ca="1"/>
-        <v>5.7</v>
-      </c>
-      <c r="D45">
-        <f ca="1"/>
-        <v>43.597938144329895</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A46" t="str">
-        <f ca="1"/>
-        <v>std</v>
-      </c>
-      <c r="B46">
-        <f ca="1"/>
-        <v>215.73323312713649</v>
-      </c>
-      <c r="C46">
-        <f ca="1"/>
-        <v>2.7252771745993041</v>
-      </c>
-      <c r="D46">
-        <f ca="1"/>
-        <v>13.286527356620564</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A47" t="str">
-        <f ca="1"/>
-        <v>min</v>
-      </c>
-      <c r="B47">
-        <f ca="1"/>
+      <c r="C179" t="str">
+        <v/>
+      </c>
+      <c r="D179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A180" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B180">
+        <v>167.16199999999998</v>
+      </c>
+      <c r="C180">
         <v>2.17</v>
       </c>
-      <c r="C47">
-        <f ca="1"/>
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <f ca="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A48" t="str">
-        <f ca="1"/>
-        <v>25%</v>
-      </c>
-      <c r="B48">
-        <f ca="1"/>
-        <v>31.2075</v>
-      </c>
-      <c r="C48">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="D48">
-        <f ca="1"/>
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A49" t="str">
-        <f ca="1"/>
-        <v>50%</v>
-      </c>
-      <c r="B49">
-        <f ca="1"/>
-        <v>111.38</v>
-      </c>
-      <c r="C49">
-        <f ca="1"/>
-        <v>5.5</v>
-      </c>
-      <c r="D49">
-        <f ca="1"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A50" t="str">
-        <f ca="1"/>
-        <v>75%</v>
-      </c>
-      <c r="B50">
-        <f ca="1"/>
-        <v>378.83</v>
-      </c>
-      <c r="C50">
-        <f ca="1"/>
-        <v>8</v>
-      </c>
-      <c r="D50">
-        <f ca="1"/>
-        <v>55.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A51" t="str">
-        <f ca="1"/>
-        <v>max</v>
-      </c>
-      <c r="B51">
-        <f ca="1"/>
-        <v>760.69</v>
-      </c>
-      <c r="C51">
-        <f ca="1"/>
-        <v>10</v>
-      </c>
-      <c r="D51">
-        <f ca="1"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A53" t="str" cm="1">
-        <f t="array" aca="1" ref="A53:D61" ca="1">_xlfn._xlws.PY(9,0)</f>
-        <v/>
-      </c>
-      <c r="B53" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="C53" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="D53" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A54" t="str">
-        <f ca="1"/>
-        <v>count</v>
-      </c>
-      <c r="B54">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-      <c r="C54">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-      <c r="D54">
-        <f ca="1"/>
-        <v>194</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A55" t="str">
-        <f ca="1"/>
-        <v>mean</v>
-      </c>
-      <c r="B55">
-        <f ca="1"/>
-        <v>211.94830000000002</v>
-      </c>
-      <c r="C55">
-        <f ca="1"/>
-        <v>5.7</v>
-      </c>
-      <c r="D55">
-        <f ca="1"/>
-        <v>43.597938144329895</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A56" t="str">
-        <f ca="1"/>
-        <v>std</v>
-      </c>
-      <c r="B56">
-        <f ca="1"/>
-        <v>215.73323312713649</v>
-      </c>
-      <c r="C56">
-        <f ca="1"/>
-        <v>2.7252771745993041</v>
-      </c>
-      <c r="D56">
-        <f ca="1"/>
-        <v>13.286527356620564</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A57" t="str">
-        <f ca="1"/>
-        <v>min</v>
-      </c>
-      <c r="B57">
-        <f ca="1"/>
-        <v>2.17</v>
-      </c>
-      <c r="C57">
-        <f ca="1"/>
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <f ca="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A58" t="str">
-        <f ca="1"/>
-        <v>10%</v>
-      </c>
-      <c r="B58">
-        <f ca="1"/>
-        <v>13.033000000000001</v>
-      </c>
-      <c r="C58">
-        <f ca="1"/>
-        <v>2</v>
-      </c>
-      <c r="D58">
-        <f ca="1"/>
-        <v>25.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A59" t="str">
-        <f ca="1"/>
-        <v>50%</v>
-      </c>
-      <c r="B59">
-        <f ca="1"/>
-        <v>111.38</v>
-      </c>
-      <c r="C59">
-        <f ca="1"/>
-        <v>5.5</v>
-      </c>
-      <c r="D59">
-        <f ca="1"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A60" t="str">
-        <f ca="1"/>
-        <v>90%</v>
-      </c>
-      <c r="B60">
-        <f ca="1"/>
-        <v>512.85599999999999</v>
-      </c>
-      <c r="C60">
-        <f ca="1"/>
-        <v>9.0999999999999943</v>
-      </c>
-      <c r="D60">
-        <f ca="1"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A61" t="str">
-        <f ca="1"/>
-        <v>max</v>
-      </c>
-      <c r="B61">
-        <f ca="1"/>
-        <v>760.69</v>
-      </c>
-      <c r="C61">
-        <f ca="1"/>
-        <v>10</v>
-      </c>
-      <c r="D61">
-        <f ca="1"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A63" t="str" cm="1">
-        <f t="array" aca="1" ref="A63:E67" ca="1">_xlfn._xlws.PY(10,0)</f>
-        <v/>
-      </c>
-      <c r="B63" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="C63" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="D63" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="E63" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A64" t="str">
-        <f ca="1"/>
-        <v>count</v>
-      </c>
-      <c r="B64">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-      <c r="C64">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-      <c r="D64">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-      <c r="E64">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A65" t="str">
-        <f ca="1"/>
-        <v>unique</v>
-      </c>
-      <c r="B65">
-        <f ca="1"/>
-        <v>200</v>
-      </c>
-      <c r="C65">
-        <f ca="1"/>
-        <v>15</v>
-      </c>
-      <c r="D65">
-        <f ca="1"/>
-        <v>3</v>
-      </c>
-      <c r="E65">
-        <f ca="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A66" t="str">
-        <f ca="1"/>
-        <v>top</v>
-      </c>
-      <c r="B66" t="str">
-        <f ca="1"/>
-        <v>ORD-0001</v>
-      </c>
-      <c r="C66" t="str">
-        <f ca="1"/>
-        <v>Notebook</v>
-      </c>
-      <c r="D66" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E66" t="str">
-        <f ca="1"/>
+      <c r="D180">
+        <v>486.65</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A181" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B181">
+        <v>201.18230769230769</v>
+      </c>
+      <c r="C181">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="D181">
+        <v>732.96</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A182" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B182">
+        <v>182.58790697674419</v>
+      </c>
+      <c r="C182">
+        <v>3.72</v>
+      </c>
+      <c r="D182">
+        <v>754.29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A183" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B183">
+        <v>274.43128205128204</v>
+      </c>
+      <c r="C183">
+        <v>7.32</v>
+      </c>
+      <c r="D183">
+        <v>689.59</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A184" t="str">
         <v>United States</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A67" t="str">
-        <f ca="1"/>
-        <v>freq</v>
-      </c>
-      <c r="B67">
-        <f ca="1"/>
-        <v>1</v>
-      </c>
-      <c r="C67">
-        <f ca="1"/>
-        <v>19</v>
-      </c>
-      <c r="D67">
-        <f ca="1"/>
-        <v>80</v>
-      </c>
-      <c r="E67">
-        <f ca="1"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A69" t="str" cm="1">
-        <f t="array" aca="1" ref="A69:C74" ca="1">_xlfn._xlws.PY(11,0)</f>
-        <v>product</v>
-      </c>
-      <c r="B69" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="C69" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A70" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="B70" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="C70">
-        <f ca="1"/>
-        <v>68.760000000000005</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A71" t="str">
-        <f ca="1"/>
-        <v>Lamp</v>
-      </c>
-      <c r="B71" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="C71">
-        <f ca="1"/>
-        <v>115.2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A72" t="str">
-        <f ca="1"/>
-        <v>Lamp</v>
-      </c>
-      <c r="B72" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="C72">
-        <f ca="1"/>
-        <v>69.900000000000006</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A73" t="str">
-        <f ca="1"/>
-        <v>Notebook</v>
-      </c>
-      <c r="B73" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="C73">
-        <f ca="1"/>
-        <v>15.35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A74" t="str">
-        <f ca="1"/>
-        <v>Tablet</v>
-      </c>
-      <c r="B74" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="C74">
-        <f ca="1"/>
-        <v>479.68</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A76" t="str" cm="1">
-        <f t="array" aca="1" ref="A76:A81" ca="1">_xlfn._xlws.PY(12,0)</f>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A77" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A78" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A79" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A80" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A81" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A84" t="str" cm="1">
-        <f t="array" aca="1" ref="A84:H89" ca="1">_xlfn._xlws.PY(13,0)</f>
-        <v/>
-      </c>
-      <c r="B84" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="C84" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="D84" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="E84" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="F84" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="G84" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-      <c r="H84" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A85">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-      <c r="B85" t="str">
-        <f ca="1"/>
-        <v>ORD-0001</v>
-      </c>
-      <c r="C85" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D85" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E85">
-        <f ca="1"/>
-        <v>68.760000000000005</v>
-      </c>
-      <c r="F85">
-        <f ca="1"/>
-        <v>5</v>
-      </c>
-      <c r="G85">
-        <f ca="1"/>
-        <v>37</v>
-      </c>
-      <c r="H85" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A86">
-        <f ca="1"/>
-        <v>1</v>
-      </c>
-      <c r="B86" t="str">
-        <f ca="1"/>
-        <v>ORD-0002</v>
-      </c>
-      <c r="C86" t="str">
-        <f ca="1"/>
-        <v>Lamp</v>
-      </c>
-      <c r="D86" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E86">
-        <f ca="1"/>
-        <v>115.2</v>
-      </c>
-      <c r="F86">
-        <f ca="1"/>
-        <v>7</v>
-      </c>
-      <c r="G86">
-        <f ca="1"/>
-        <v>24</v>
-      </c>
-      <c r="H86" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A87">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="B87" t="str">
-        <f ca="1"/>
-        <v>ORD-0005</v>
-      </c>
-      <c r="C87" t="str">
-        <f ca="1"/>
-        <v>Tablet</v>
-      </c>
-      <c r="D87" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E87">
-        <f ca="1"/>
-        <v>479.68</v>
-      </c>
-      <c r="F87">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
-      <c r="G87">
-        <f ca="1"/>
-        <v>28</v>
-      </c>
-      <c r="H87" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A88">
-        <f ca="1"/>
-        <v>11</v>
-      </c>
-      <c r="B88" t="str">
-        <f ca="1"/>
-        <v>ORD-0012</v>
-      </c>
-      <c r="C88" t="str">
-        <f ca="1"/>
-        <v>Tablet</v>
-      </c>
-      <c r="D88" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E88">
-        <f ca="1"/>
-        <v>415.36</v>
-      </c>
-      <c r="F88">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
-      <c r="G88">
-        <f ca="1"/>
-        <v>47</v>
-      </c>
-      <c r="H88" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A89">
-        <f ca="1"/>
-        <v>13</v>
-      </c>
-      <c r="B89" t="str">
-        <f ca="1"/>
-        <v>ORD-0014</v>
-      </c>
-      <c r="C89" t="str">
-        <f ca="1"/>
-        <v>Headphones</v>
-      </c>
-      <c r="D89" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E89">
-        <f ca="1"/>
-        <v>91.32</v>
-      </c>
-      <c r="F89">
-        <f ca="1"/>
-        <v>9</v>
-      </c>
-      <c r="G89">
-        <f ca="1"/>
-        <v>56</v>
-      </c>
-      <c r="H89" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A91" t="str" cm="1">
-        <f t="array" aca="1" ref="A91:H96" ca="1">_xlfn._xlws.PY(14,0)</f>
-        <v/>
-      </c>
-      <c r="B91" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="C91" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="D91" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="E91" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="F91" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="G91" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-      <c r="H91" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A92">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-      <c r="B92" t="str">
-        <f ca="1"/>
-        <v>ORD-0001</v>
-      </c>
-      <c r="C92" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D92" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E92">
-        <f ca="1"/>
-        <v>68.760000000000005</v>
-      </c>
-      <c r="F92">
-        <f ca="1"/>
-        <v>5</v>
-      </c>
-      <c r="G92">
-        <f ca="1"/>
-        <v>37</v>
-      </c>
-      <c r="H92" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A93">
-        <f ca="1"/>
-        <v>1</v>
-      </c>
-      <c r="B93" t="str">
-        <f ca="1"/>
-        <v>ORD-0002</v>
-      </c>
-      <c r="C93" t="str">
-        <f ca="1"/>
-        <v>Lamp</v>
-      </c>
-      <c r="D93" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E93">
-        <f ca="1"/>
-        <v>115.2</v>
-      </c>
-      <c r="F93">
-        <f ca="1"/>
-        <v>7</v>
-      </c>
-      <c r="G93">
-        <f ca="1"/>
-        <v>24</v>
-      </c>
-      <c r="H93" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A94">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="B94" t="str">
-        <f ca="1"/>
-        <v>ORD-0005</v>
-      </c>
-      <c r="C94" t="str">
-        <f ca="1"/>
-        <v>Tablet</v>
-      </c>
-      <c r="D94" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E94">
-        <f ca="1"/>
-        <v>479.68</v>
-      </c>
-      <c r="F94">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
-      <c r="G94">
-        <f ca="1"/>
-        <v>28</v>
-      </c>
-      <c r="H94" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A95">
-        <f ca="1"/>
-        <v>11</v>
-      </c>
-      <c r="B95" t="str">
-        <f ca="1"/>
-        <v>ORD-0012</v>
-      </c>
-      <c r="C95" t="str">
-        <f ca="1"/>
-        <v>Tablet</v>
-      </c>
-      <c r="D95" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E95">
-        <f ca="1"/>
-        <v>415.36</v>
-      </c>
-      <c r="F95">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
-      <c r="G95">
-        <f ca="1"/>
-        <v>47</v>
-      </c>
-      <c r="H95" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A96">
-        <f ca="1"/>
-        <v>13</v>
-      </c>
-      <c r="B96" t="str">
-        <f ca="1"/>
-        <v>ORD-0014</v>
-      </c>
-      <c r="C96" t="str">
-        <f ca="1"/>
-        <v>Headphones</v>
-      </c>
-      <c r="D96" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E96">
-        <f ca="1"/>
-        <v>91.32</v>
-      </c>
-      <c r="F96">
-        <f ca="1"/>
-        <v>9</v>
-      </c>
-      <c r="G96">
-        <f ca="1"/>
-        <v>56</v>
-      </c>
-      <c r="H96" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A98" t="str" cm="1">
-        <f t="array" aca="1" ref="A98:H103" ca="1">_xlfn._xlws.PY(15,0)</f>
-        <v/>
-      </c>
-      <c r="B98" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="C98" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="D98" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="E98" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="F98" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="G98" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-      <c r="H98" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A99">
-        <f ca="1"/>
-        <v>0</v>
-      </c>
-      <c r="B99" t="str">
-        <f ca="1"/>
-        <v>ORD-0001</v>
-      </c>
-      <c r="C99" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D99" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E99">
-        <f ca="1"/>
-        <v>68.760000000000005</v>
-      </c>
-      <c r="F99">
-        <f ca="1"/>
-        <v>5</v>
-      </c>
-      <c r="G99">
-        <f ca="1"/>
-        <v>37</v>
-      </c>
-      <c r="H99" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A100">
-        <f ca="1"/>
-        <v>1</v>
-      </c>
-      <c r="B100" t="str">
-        <f ca="1"/>
-        <v>ORD-0002</v>
-      </c>
-      <c r="C100" t="str">
-        <f ca="1"/>
-        <v>Lamp</v>
-      </c>
-      <c r="D100" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E100">
-        <f ca="1"/>
-        <v>115.2</v>
-      </c>
-      <c r="F100">
-        <f ca="1"/>
-        <v>7</v>
-      </c>
-      <c r="G100">
-        <f ca="1"/>
-        <v>24</v>
-      </c>
-      <c r="H100" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A101">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="B101" t="str">
-        <f ca="1"/>
-        <v>ORD-0005</v>
-      </c>
-      <c r="C101" t="str">
-        <f ca="1"/>
-        <v>Tablet</v>
-      </c>
-      <c r="D101" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E101">
-        <f ca="1"/>
-        <v>479.68</v>
-      </c>
-      <c r="F101">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
-      <c r="G101">
-        <f ca="1"/>
-        <v>28</v>
-      </c>
-      <c r="H101" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A102">
-        <f ca="1"/>
-        <v>11</v>
-      </c>
-      <c r="B102" t="str">
-        <f ca="1"/>
-        <v>ORD-0012</v>
-      </c>
-      <c r="C102" t="str">
-        <f ca="1"/>
-        <v>Tablet</v>
-      </c>
-      <c r="D102" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E102">
-        <f ca="1"/>
-        <v>415.36</v>
-      </c>
-      <c r="F102">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
-      <c r="G102">
-        <f ca="1"/>
-        <v>47</v>
-      </c>
-      <c r="H102" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A103">
-        <f ca="1"/>
-        <v>13</v>
-      </c>
-      <c r="B103" t="str">
-        <f ca="1"/>
-        <v>ORD-0014</v>
-      </c>
-      <c r="C103" t="str">
-        <f ca="1"/>
-        <v>Headphones</v>
-      </c>
-      <c r="D103" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E103">
-        <f ca="1"/>
-        <v>91.32</v>
-      </c>
-      <c r="F103">
-        <f ca="1"/>
-        <v>9</v>
-      </c>
-      <c r="G103">
-        <f ca="1"/>
-        <v>56</v>
-      </c>
-      <c r="H103" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A105" t="str" cm="1">
-        <f t="array" aca="1" ref="A105:H110" ca="1">_xlfn._xlws.PY(16,0)</f>
-        <v/>
-      </c>
-      <c r="B105" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="C105" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="D105" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="E105" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="F105" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="G105" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-      <c r="H105" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A106">
-        <f ca="1"/>
-        <v>48</v>
-      </c>
-      <c r="B106" t="str">
-        <f ca="1"/>
-        <v>ORD-0049</v>
-      </c>
-      <c r="C106" t="str">
-        <f ca="1"/>
-        <v>Printer Paper</v>
-      </c>
-      <c r="D106" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E106">
-        <f ca="1"/>
-        <v>2.17</v>
-      </c>
-      <c r="F106">
-        <f ca="1"/>
-        <v>3</v>
-      </c>
-      <c r="G106">
-        <f ca="1"/>
-        <v>62</v>
-      </c>
-      <c r="H106" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A107">
-        <f ca="1"/>
-        <v>79</v>
-      </c>
-      <c r="B107" t="str">
-        <f ca="1"/>
-        <v>ORD-0080</v>
-      </c>
-      <c r="C107" t="str">
-        <f ca="1"/>
-        <v>Stapler</v>
-      </c>
-      <c r="D107" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E107">
-        <f ca="1"/>
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="F107">
-        <f ca="1"/>
-        <v>6</v>
-      </c>
-      <c r="G107">
-        <f ca="1"/>
-        <v>41</v>
-      </c>
-      <c r="H107" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A108">
-        <f ca="1"/>
-        <v>99</v>
-      </c>
-      <c r="B108" t="str">
-        <f ca="1"/>
-        <v>ORD-0100</v>
-      </c>
-      <c r="C108" t="str">
-        <f ca="1"/>
-        <v>Notebook</v>
-      </c>
-      <c r="D108" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E108">
-        <f ca="1"/>
+      <c r="B184">
+        <v>209.05701298701297</v>
+      </c>
+      <c r="C184">
         <v>2.4900000000000002</v>
       </c>
-      <c r="F108">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="G108">
-        <f ca="1"/>
-        <v>27</v>
-      </c>
-      <c r="H108" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A109">
-        <f ca="1"/>
-        <v>142</v>
-      </c>
-      <c r="B109" t="str">
-        <f ca="1"/>
-        <v>ORD-0143</v>
-      </c>
-      <c r="C109" t="str">
-        <f ca="1"/>
-        <v>Notebook</v>
-      </c>
-      <c r="D109" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E109">
-        <f ca="1"/>
-        <v>3.72</v>
-      </c>
-      <c r="F109">
-        <f ca="1"/>
-        <v>2</v>
-      </c>
-      <c r="G109">
-        <f ca="1"/>
-        <v>37</v>
-      </c>
-      <c r="H109" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A110">
-        <f ca="1"/>
-        <v>21</v>
-      </c>
-      <c r="B110" t="str">
-        <f ca="1"/>
-        <v>ORD-0022</v>
-      </c>
-      <c r="C110" t="str">
-        <f ca="1"/>
-        <v>Pens</v>
-      </c>
-      <c r="D110" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E110">
-        <f ca="1"/>
-        <v>4.78</v>
-      </c>
-      <c r="F110">
-        <f ca="1"/>
-        <v>10</v>
-      </c>
-      <c r="G110">
-        <f ca="1"/>
-        <v>27</v>
-      </c>
-      <c r="H110" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A113" t="str" cm="1">
-        <f t="array" aca="1" ref="A113:H118" ca="1">_xlfn._xlws.PY(17,0)</f>
-        <v/>
-      </c>
-      <c r="B113" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="C113" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="D113" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="E113" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="F113" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="G113" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-      <c r="H113" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A114">
-        <f ca="1"/>
-        <v>113</v>
-      </c>
-      <c r="B114" t="str">
-        <f ca="1"/>
-        <v>ORD-0114</v>
-      </c>
-      <c r="C114" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D114" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E114">
-        <f ca="1"/>
-        <v>760.69</v>
-      </c>
-      <c r="F114">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="G114">
-        <f ca="1"/>
-        <v>62</v>
-      </c>
-      <c r="H114" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A115">
-        <f ca="1"/>
-        <v>165</v>
-      </c>
-      <c r="B115" t="str">
-        <f ca="1"/>
-        <v>ORD-0166</v>
-      </c>
-      <c r="C115" t="str">
-        <f ca="1"/>
-        <v>Filing Cabinet</v>
-      </c>
-      <c r="D115" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E115">
-        <f ca="1"/>
-        <v>754.29</v>
-      </c>
-      <c r="F115">
-        <f ca="1"/>
-        <v>5</v>
-      </c>
-      <c r="G115">
-        <f ca="1"/>
-        <v>24</v>
-      </c>
-      <c r="H115" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A116">
-        <f ca="1"/>
-        <v>45</v>
-      </c>
-      <c r="B116" t="str">
-        <f ca="1"/>
-        <v>ORD-0046</v>
-      </c>
-      <c r="C116" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D116" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E116">
-        <f ca="1"/>
-        <v>754.2</v>
-      </c>
-      <c r="F116">
-        <f ca="1"/>
-        <v>3</v>
-      </c>
-      <c r="G116">
-        <f ca="1"/>
-        <v>38</v>
-      </c>
-      <c r="H116" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A117">
-        <f ca="1"/>
-        <v>40</v>
-      </c>
-      <c r="B117" t="str">
-        <f ca="1"/>
-        <v>ORD-0041</v>
-      </c>
-      <c r="C117" t="str">
-        <f ca="1"/>
-        <v>Bookshelf</v>
-      </c>
-      <c r="D117" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E117">
-        <f ca="1"/>
-        <v>751.03</v>
-      </c>
-      <c r="F117">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="G117">
-        <f ca="1"/>
-        <v>64</v>
-      </c>
-      <c r="H117" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A118">
-        <f ca="1"/>
-        <v>152</v>
-      </c>
-      <c r="B118" t="str">
-        <f ca="1"/>
-        <v>ORD-0153</v>
-      </c>
-      <c r="C118" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D118" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E118">
-        <f ca="1"/>
-        <v>732.96</v>
-      </c>
-      <c r="F118">
-        <f ca="1"/>
-        <v>8</v>
-      </c>
-      <c r="G118">
-        <f ca="1"/>
-        <v>40</v>
-      </c>
-      <c r="H118" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A121" t="str" cm="1">
-        <f t="array" aca="1" ref="A121:H126" ca="1">_xlfn._xlws.PY(18,0)</f>
-        <v/>
-      </c>
-      <c r="B121" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="C121" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="D121" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="E121" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="F121" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="G121" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-      <c r="H121" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A122">
-        <f ca="1"/>
-        <v>48</v>
-      </c>
-      <c r="B122" t="str">
-        <f ca="1"/>
-        <v>ORD-0049</v>
-      </c>
-      <c r="C122" t="str">
-        <f ca="1"/>
-        <v>Printer Paper</v>
-      </c>
-      <c r="D122" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E122">
-        <f ca="1"/>
-        <v>2.17</v>
-      </c>
-      <c r="F122">
-        <f ca="1"/>
-        <v>3</v>
-      </c>
-      <c r="G122">
-        <f ca="1"/>
-        <v>62</v>
-      </c>
-      <c r="H122" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A123">
-        <f ca="1"/>
-        <v>32</v>
-      </c>
-      <c r="B123" t="str">
-        <f ca="1"/>
-        <v>ORD-0033</v>
-      </c>
-      <c r="C123" t="str">
-        <f ca="1"/>
-        <v>Notebook</v>
-      </c>
-      <c r="D123" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E123">
-        <f ca="1"/>
-        <v>6.7</v>
-      </c>
-      <c r="F123">
-        <f ca="1"/>
-        <v>9</v>
-      </c>
-      <c r="G123">
-        <f ca="1"/>
-        <v>22</v>
-      </c>
-      <c r="H123" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A124">
-        <f ca="1"/>
-        <v>119</v>
-      </c>
-      <c r="B124" t="str">
-        <f ca="1"/>
-        <v>ORD-0120</v>
-      </c>
-      <c r="C124" t="str">
-        <f ca="1"/>
-        <v>Stapler</v>
-      </c>
-      <c r="D124" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E124">
-        <f ca="1"/>
-        <v>7.97</v>
-      </c>
-      <c r="F124">
-        <f ca="1"/>
-        <v>5</v>
-      </c>
-      <c r="G124">
-        <f ca="1"/>
-        <v>47</v>
-      </c>
-      <c r="H124" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A125">
-        <f ca="1"/>
-        <v>181</v>
-      </c>
-      <c r="B125" t="str">
-        <f ca="1"/>
-        <v>ORD-0182</v>
-      </c>
-      <c r="C125" t="str">
-        <f ca="1"/>
-        <v>Binder</v>
-      </c>
-      <c r="D125" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="E125">
-        <f ca="1"/>
-        <v>19.97</v>
-      </c>
-      <c r="F125">
-        <f ca="1"/>
-        <v>3</v>
-      </c>
-      <c r="G125">
-        <f ca="1"/>
-        <v>65</v>
-      </c>
-      <c r="H125" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A126">
-        <f ca="1"/>
-        <v>34</v>
-      </c>
-      <c r="B126" t="str">
-        <f ca="1"/>
-        <v>ORD-0035</v>
-      </c>
-      <c r="C126" t="str">
-        <f ca="1"/>
-        <v>Monitor</v>
-      </c>
-      <c r="D126" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="E126">
-        <f ca="1"/>
-        <v>26.02</v>
-      </c>
-      <c r="F126">
-        <f ca="1"/>
-        <v>7</v>
-      </c>
-      <c r="G126">
-        <f ca="1"/>
-        <v>38</v>
-      </c>
-      <c r="H126" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A129" t="str" cm="1">
-        <f t="array" aca="1" ref="A129:H134" ca="1">_xlfn._xlws.PY(19,0)</f>
-        <v/>
-      </c>
-      <c r="B129" t="str">
-        <f ca="1"/>
-        <v>order_id</v>
-      </c>
-      <c r="C129" t="str">
-        <f ca="1"/>
-        <v>product</v>
-      </c>
-      <c r="D129" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="E129" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-      <c r="F129" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-      <c r="G129" t="str">
-        <f ca="1"/>
-        <v>customer_age</v>
-      </c>
-      <c r="H129" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A130">
-        <f ca="1"/>
-        <v>113</v>
-      </c>
-      <c r="B130" t="str">
-        <f ca="1"/>
-        <v>ORD-0114</v>
-      </c>
-      <c r="C130" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D130" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E130">
-        <f ca="1"/>
-        <v>760.69</v>
-      </c>
-      <c r="F130">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="G130">
-        <f ca="1"/>
-        <v>62</v>
-      </c>
-      <c r="H130" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A131">
-        <f ca="1"/>
-        <v>165</v>
-      </c>
-      <c r="B131" t="str">
-        <f ca="1"/>
-        <v>ORD-0166</v>
-      </c>
-      <c r="C131" t="str">
-        <f ca="1"/>
-        <v>Filing Cabinet</v>
-      </c>
-      <c r="D131" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E131">
-        <f ca="1"/>
-        <v>754.29</v>
-      </c>
-      <c r="F131">
-        <f ca="1"/>
-        <v>5</v>
-      </c>
-      <c r="G131">
-        <f ca="1"/>
-        <v>24</v>
-      </c>
-      <c r="H131" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A132">
-        <f ca="1"/>
-        <v>45</v>
-      </c>
-      <c r="B132" t="str">
-        <f ca="1"/>
-        <v>ORD-0046</v>
-      </c>
-      <c r="C132" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D132" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E132">
-        <f ca="1"/>
-        <v>754.2</v>
-      </c>
-      <c r="F132">
-        <f ca="1"/>
-        <v>3</v>
-      </c>
-      <c r="G132">
-        <f ca="1"/>
-        <v>38</v>
-      </c>
-      <c r="H132" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A133">
-        <f ca="1"/>
-        <v>40</v>
-      </c>
-      <c r="B133" t="str">
-        <f ca="1"/>
-        <v>ORD-0041</v>
-      </c>
-      <c r="C133" t="str">
-        <f ca="1"/>
-        <v>Bookshelf</v>
-      </c>
-      <c r="D133" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E133">
-        <f ca="1"/>
-        <v>751.03</v>
-      </c>
-      <c r="F133">
-        <f ca="1"/>
-        <v>4</v>
-      </c>
-      <c r="G133">
-        <f ca="1"/>
-        <v>64</v>
-      </c>
-      <c r="H133" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A134">
-        <f ca="1"/>
-        <v>152</v>
-      </c>
-      <c r="B134" t="str">
-        <f ca="1"/>
-        <v>ORD-0153</v>
-      </c>
-      <c r="C134" t="str">
-        <f ca="1"/>
-        <v>Desk</v>
-      </c>
-      <c r="D134" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="E134">
-        <f ca="1"/>
-        <v>732.96</v>
-      </c>
-      <c r="F134">
-        <f ca="1"/>
-        <v>8</v>
-      </c>
-      <c r="G134">
-        <f ca="1"/>
-        <v>40</v>
-      </c>
-      <c r="H134" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A136" t="str" cm="1">
-        <f t="array" aca="1" ref="A136:B141" ca="1">_xlfn._xlws.PY(20,0)</f>
-        <v>country</v>
-      </c>
-      <c r="B136" t="str">
-        <f ca="1"/>
-        <v>count</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A137" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-      <c r="B137">
-        <f ca="1"/>
-        <v>77</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A138" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-      <c r="B138">
-        <f ca="1"/>
-        <v>43</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A139" t="str">
-        <f ca="1"/>
-        <v>United Kingdom</v>
-      </c>
-      <c r="B139">
-        <f ca="1"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A140" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-      <c r="B140">
-        <f ca="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A141" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-      <c r="B141">
-        <f ca="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A144" t="str" cm="1">
-        <f t="array" aca="1" ref="A144:B147" ca="1">_xlfn._xlws.PY(21,0)</f>
-        <v>category</v>
-      </c>
-      <c r="B144" t="str">
-        <f ca="1"/>
-        <v>count</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A145" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="B145">
-        <f ca="1"/>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A146" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="B146">
-        <f ca="1"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A147" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="B147">
-        <f ca="1"/>
-        <v>55</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A149" t="str" cm="1">
-        <f t="array" aca="1" ref="A149:B152" ca="1">_xlfn._xlws.PY(22,0)</f>
-        <v>category</v>
-      </c>
-      <c r="B149" t="str">
-        <f ca="1"/>
-        <v>proportion</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A150" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="B150">
-        <f ca="1"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A151" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="B151">
-        <f ca="1"/>
-        <v>0.32500000000000001</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A152" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="B152">
-        <f ca="1"/>
-        <v>0.27500000000000002</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A154" t="str" cm="1">
-        <f t="array" aca="1" ref="A154:B159" ca="1">_xlfn._xlws.PY(23,0)</f>
-        <v>country</v>
-      </c>
-      <c r="B154" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A155" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-      <c r="B155">
-        <f ca="1"/>
-        <v>167.16199999999998</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A156" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-      <c r="B156">
-        <f ca="1"/>
-        <v>201.18230769230769</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A157" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-      <c r="B157">
-        <f ca="1"/>
-        <v>182.58790697674419</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A158" t="str">
-        <f ca="1"/>
-        <v>United Kingdom</v>
-      </c>
-      <c r="B158">
-        <f ca="1"/>
-        <v>274.43128205128204</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.5">
-      <c r="A159" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-      <c r="B159">
-        <f ca="1"/>
-        <v>209.05701298701297</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A161" t="str" cm="1">
-        <f t="array" aca="1" ref="A161:B164" ca="1">_xlfn._xlws.PY(24,0)</f>
-        <v>category</v>
-      </c>
-      <c r="B161" t="str">
-        <f ca="1"/>
-        <v>quantity</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A162" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="B162">
-        <f ca="1"/>
-        <v>362</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A163" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="B163">
-        <f ca="1"/>
-        <v>288</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A164" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="B164">
-        <f ca="1"/>
-        <v>490</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A166" t="str" cm="1">
-        <f t="array" aca="1" ref="A166:C181" ca="1">_xlfn._xlws.PY(25,0)</f>
-        <v>country</v>
-      </c>
-      <c r="B166" t="str">
-        <f ca="1"/>
-        <v>category</v>
-      </c>
-      <c r="C166" t="str">
-        <f ca="1"/>
-        <v>unit_price</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A167" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-      <c r="B167" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="C167">
-        <f ca="1"/>
-        <v>270.6516666666667</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A168" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-      <c r="B168" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="C168">
-        <f ca="1"/>
-        <v>256.68</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A169" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-      <c r="B169" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="C169">
-        <f ca="1"/>
-        <v>18.91333333333333</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A170" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-      <c r="B170" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="C170">
-        <f ca="1"/>
-        <v>274.04250000000002</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A171" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-      <c r="B171" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="C171">
-        <f ca="1"/>
-        <v>529.45000000000005</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A172" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-      <c r="B172" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="C172">
-        <f ca="1"/>
-        <v>30.088461538461541</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A173" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-      <c r="B173" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="C173">
-        <f ca="1"/>
-        <v>230.67818181818183</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A174" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-      <c r="B174" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="C174">
-        <f ca="1"/>
-        <v>350.0864285714286</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A175" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-      <c r="B175" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="C175">
-        <f ca="1"/>
-        <v>22.922777777777778</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.5">
-      <c r="A176" t="str">
-        <f ca="1"/>
-        <v>United Kingdom</v>
-      </c>
-      <c r="B176" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="C176">
-        <f ca="1"/>
-        <v>272.95764705882351</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A177" t="str">
-        <f ca="1"/>
-        <v>United Kingdom</v>
-      </c>
-      <c r="B177" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="C177">
-        <f ca="1"/>
-        <v>529.8054545454545</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A178" t="str">
-        <f ca="1"/>
-        <v>United Kingdom</v>
-      </c>
-      <c r="B178" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="C178">
-        <f ca="1"/>
-        <v>21.334545454545456</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A179" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-      <c r="B179" t="str">
-        <f ca="1"/>
-        <v>Electronics</v>
-      </c>
-      <c r="C179">
-        <f ca="1"/>
-        <v>296.6995652173913</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A180" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-      <c r="B180" t="str">
-        <f ca="1"/>
-        <v>Furniture</v>
-      </c>
-      <c r="C180">
-        <f ca="1"/>
-        <v>383.92954545454546</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A181" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-      <c r="B181" t="str">
-        <f ca="1"/>
-        <v>Office Supplies</v>
-      </c>
-      <c r="C181">
-        <f ca="1"/>
-        <v>25.839062500000001</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A183" t="str" cm="1">
-        <f t="array" aca="1" ref="A183:D189" ca="1">_xlfn._xlws.PY(26,0)</f>
-        <v/>
-      </c>
-      <c r="B183" t="str">
-        <f ca="1"/>
-        <v>mean</v>
-      </c>
-      <c r="C183" t="str">
-        <f ca="1"/>
-        <v>min</v>
-      </c>
-      <c r="D183" t="str">
-        <f ca="1"/>
-        <v>max</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A184" t="str">
-        <f ca="1"/>
-        <v>country</v>
-      </c>
-      <c r="B184" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="C184" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="D184" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A185" t="str">
-        <f ca="1"/>
-        <v>Australia</v>
-      </c>
-      <c r="B185">
-        <f ca="1"/>
-        <v>167.16199999999998</v>
-      </c>
-      <c r="C185">
-        <f ca="1"/>
-        <v>2.17</v>
-      </c>
-      <c r="D185">
-        <f ca="1"/>
-        <v>486.65</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A186" t="str">
-        <f ca="1"/>
-        <v>Canada</v>
-      </c>
-      <c r="B186">
-        <f ca="1"/>
-        <v>201.18230769230769</v>
-      </c>
-      <c r="C186">
-        <f ca="1"/>
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="D186">
-        <f ca="1"/>
-        <v>732.96</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A187" t="str">
-        <f ca="1"/>
-        <v>Germany</v>
-      </c>
-      <c r="B187">
-        <f ca="1"/>
-        <v>182.58790697674419</v>
-      </c>
-      <c r="C187">
-        <f ca="1"/>
-        <v>3.72</v>
-      </c>
-      <c r="D187">
-        <f ca="1"/>
-        <v>754.29</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A188" t="str">
-        <f ca="1"/>
-        <v>United Kingdom</v>
-      </c>
-      <c r="B188">
-        <f ca="1"/>
-        <v>274.43128205128204</v>
-      </c>
-      <c r="C188">
-        <f ca="1"/>
-        <v>7.32</v>
-      </c>
-      <c r="D188">
-        <f ca="1"/>
-        <v>689.59</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.5">
-      <c r="A189" t="str">
-        <f ca="1"/>
-        <v>United States</v>
-      </c>
-      <c r="B189">
-        <f ca="1"/>
-        <v>209.05701298701297</v>
-      </c>
-      <c r="C189">
-        <f ca="1"/>
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="D189">
-        <f ca="1"/>
+      <c r="D184">
         <v>760.69</v>
       </c>
     </row>

--- a/ch_02_pandas/ch_02_solution.xlsx
+++ b/ch_02_pandas/ch_02_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02_pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{207B83A7-FAB8-4D24-B601-926ABE3E5B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321BC6CD-AD96-44FF-8FED-E1A9921EBC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nyc" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
+          <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
@@ -202,9 +202,6 @@
     <t>Queens</t>
   </si>
   <si>
-    <t>Bronx</t>
-  </si>
-  <si>
     <t>Staten Island</t>
   </si>
   <si>
@@ -896,6 +893,9 @@
   </si>
   <si>
     <t>ORD-0200</t>
+  </si>
+  <si>
+    <t>The Bronx</t>
   </si>
 </sst>
 </file>
@@ -964,6 +964,9 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -979,9 +982,6 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <font>
@@ -1053,192 +1053,22 @@
 </rvTypesInfo>
 </file>
 
-<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
-  <a r="12" c="8">
-    <v t="s"/>
-    <v t="s">order_id</v>
-    <v t="s">product</v>
-    <v t="s">category</v>
-    <v t="s">unit_price</v>
-    <v t="s">quantity</v>
-    <v t="s">customer_age</v>
-    <v t="s">country</v>
-    <v>0</v>
-    <v t="s">ORD-0001</v>
-    <v t="s">Desk</v>
-    <v t="s">Furniture</v>
-    <v>68.760000000000005</v>
-    <v>5</v>
-    <v>37</v>
-    <v t="s">United States</v>
-    <v>1</v>
-    <v t="s">ORD-0002</v>
-    <v t="s">Lamp</v>
-    <v t="s">Furniture</v>
-    <v>115.2</v>
-    <v>7</v>
-    <v>24</v>
-    <v t="s">United States</v>
-    <v>2</v>
-    <v t="s">ORD-0003</v>
-    <v t="s">Lamp</v>
-    <v t="s">Furniture</v>
-    <v>69.900000000000006</v>
-    <v>4</v>
-    <v>63</v>
-    <v t="s">Germany</v>
-    <v>3</v>
-    <v t="s">ORD-0004</v>
-    <v t="s">Notebook</v>
-    <v t="s">Office Supplies</v>
-    <v>15.35</v>
-    <v>1</v>
-    <v>32</v>
-    <v t="s">Germany</v>
-    <v>4</v>
-    <v t="s">ORD-0005</v>
-    <v t="s">Tablet</v>
-    <v t="s">Electronics</v>
-    <v>479.68</v>
-    <v>6</v>
-    <v>28</v>
-    <v t="s">United States</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v t="s">...</v>
-    <v>195</v>
-    <v t="s">ORD-0196</v>
-    <v t="s">Headphones</v>
-    <v t="s">Electronics</v>
-    <v>162.49</v>
-    <v>2</v>
-    <v>22</v>
-    <v t="s">United Kingdom</v>
-    <v>196</v>
-    <v t="s">ORD-0197</v>
-    <v t="s">Monitor</v>
-    <v t="s">Electronics</v>
-    <v>277.98</v>
-    <v>4</v>
-    <v>54</v>
-    <v t="s">United Kingdom</v>
-    <v>197</v>
-    <v t="s">ORD-0198</v>
-    <v t="s">Printer Paper</v>
-    <v t="s">Office Supplies</v>
-    <v>21.06</v>
-    <v>1</v>
-    <v>49</v>
-    <v t="s">United States</v>
-    <v>198</v>
-    <v t="s">ORD-0199</v>
-    <v t="s">Notebook</v>
-    <v t="s">Office Supplies</v>
-    <v>22.61</v>
-    <v>7</v>
-    <v>62</v>
-    <v t="s">United Kingdom</v>
-    <v>199</v>
-    <v t="s">ORD-0200</v>
-    <v t="s">Headphones</v>
-    <v t="s">Electronics</v>
-    <v>106.64</v>
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
     <v>10</v>
-    <v>51</v>
-    <v t="s">Canada</v>
-  </a>
-</arrayData>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
-  <rv s="0">
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <v>DataFrame</v>
-    <v>1</v>
-    <v>0</v>
-  </rv>
-  <rv s="2">
-    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
-    <v>DataFrame</v>
-    <v xml:space="preserve">     order_id        product         category  unit_price  quantity  \
-0    ORD-0001           Desk        Furniture       68.76         5   
-1    ORD-0002           Lamp        Furniture      115.20         7   
-2    ORD-0003           Lamp        Fur...</v>
-    <v>1</v>
-    <v>2</v>
+    <v>9</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
-  <s t="_array">
-    <k n="array" t="a"/>
-  </s>
-  <s t="_entity">
-    <k n="_DisplayString" t="s"/>
-    <k n="_ViewInfo" t="spb"/>
-    <k n="arrayPreview" t="r"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="preview" t="r"/>
-    <k n="_Provider" t="spb"/>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="subType" t="i"/>
   </s>
 </rvStructures>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
-<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="3">
-    <spb s="0">
-      <v>200</v>
-      <v>7</v>
-      <v>DataFrame</v>
-      <v>arrayPreview</v>
-      <v>1</v>
-    </spb>
-    <spb s="1">
-      <v>0</v>
-    </spb>
-    <spb s="2">
-      <v>https://www.anaconda.com/excel</v>
-      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
-      <v>Python provided by Anaconda</v>
-    </spb>
-  </spbData>
-</supportingPropertyBags>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="3">
-  <s>
-    <k n="drw" t="i"/>
-    <k n="dcol" t="i"/>
-    <k n="name" t="s"/>
-    <k n="array" t="s"/>
-    <k n="headers" t="b"/>
-  </s>
-  <s>
-    <k n="ArrayCardInfo" t="spb"/>
-  </s>
-  <s>
-    <k n="link" t="s"/>
-    <k n="logo" t="s"/>
-    <k n="name" t="s"/>
-  </s>
-</spbStructures>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1246,7 +1076,7 @@
   <autoFilter ref="A1:C6" xr:uid="{A099DEF9-7300-4421-80EE-149706CE1CEA}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{4060128F-DD32-4555-9DB9-CA443A160D2A}" name="borough"/>
-    <tableColumn id="2" xr3:uid="{32E7E197-F690-4580-9F10-846DD215807D}" name="population" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{32E7E197-F690-4580-9F10-846DD215807D}" name="population" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{4D8417DA-D82A-4787-B91D-F9A344C39103}" name="land_area"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1254,7 +1084,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}" name="sales" displayName="sales" ref="A1:G201" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}" name="sales" displayName="sales" ref="A1:G201" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:G201" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{054A5DBB-1F62-4FF0-893D-CA3913FFC271}" name="order_id"/>
@@ -1554,7 +1384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1576,92 +1406,50 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="str" cm="1">
-        <f t="array" ref="E1:H6">_xlfn._xlws.PY(0,0,nyc_pop[#All])</f>
-        <v>borough</v>
-      </c>
-      <c r="F1" s="5" t="str">
-        <v>population</v>
-      </c>
-      <c r="G1" s="5" t="str">
-        <v>land_area</v>
-      </c>
-      <c r="H1" s="5" t="str">
-        <v>density</v>
-      </c>
+      <c r="E1" t="e" cm="1" vm="1">
+        <f t="array" ref="E1">_xlfn._xlws.PY(0,0,nyc_pop[#All])</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="4">
-        <v>1694251</v>
+        <v>2736074</v>
       </c>
       <c r="C2">
-        <v>22.83</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Manhattan</v>
-      </c>
-      <c r="F2" s="5">
-        <v>1694251</v>
-      </c>
-      <c r="G2" s="5">
-        <v>22.83</v>
-      </c>
-      <c r="H2" s="5">
-        <v>74211.607533946561</v>
+        <v>69.37</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="4">
-        <v>2736074</v>
+        <v>2405464</v>
       </c>
       <c r="C3">
-        <v>69.37</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Brooklyn</v>
-      </c>
-      <c r="F3" s="5">
-        <v>2736074</v>
-      </c>
-      <c r="G3" s="5">
-        <v>69.37</v>
-      </c>
-      <c r="H3" s="5">
-        <v>39441.747152947959</v>
+        <v>108.53</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>2405464</v>
+        <v>1694251</v>
       </c>
       <c r="C4">
-        <v>108.53</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Queens</v>
-      </c>
-      <c r="F4" s="5">
-        <v>2405464</v>
-      </c>
-      <c r="G4" s="5">
-        <v>108.53</v>
-      </c>
-      <c r="H4" s="5">
-        <v>22164.046807334376</v>
+        <v>22.83</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>237</v>
       </c>
       <c r="B5" s="4">
         <v>1472654</v>
@@ -1669,22 +1457,10 @@
       <c r="C5">
         <v>42.1</v>
       </c>
-      <c r="E5" t="str">
-        <v>Bronx</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1472654</v>
-      </c>
-      <c r="G5" s="5">
-        <v>42.1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>34979.904988123511</v>
-      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="4">
         <v>495747</v>
@@ -1692,48 +1468,11 @@
       <c r="C6">
         <v>58.37</v>
       </c>
-      <c r="E6" t="str">
-        <v>Staten Island</v>
-      </c>
-      <c r="F6" s="5">
-        <v>495747</v>
-      </c>
-      <c r="G6" s="5">
-        <v>58.37</v>
-      </c>
-      <c r="H6" s="5">
-        <v>8493.1814288161731</v>
-      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E8" t="str" cm="1">
-        <f t="array" ref="E8:E13">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
-        <v>population</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E9">
-        <v>1694251</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E10">
-        <v>2736074</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E11">
-        <v>2405464</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E12">
-        <v>1472654</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E13">
-        <v>495747</v>
+      <c r="E8" t="e" cm="1">
+        <f t="array" ref="E8">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
@@ -1760,36 +1499,36 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
       </c>
       <c r="D2">
         <v>68.760000000000005</v>
@@ -1801,18 +1540,18 @@
         <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3">
         <v>115.2</v>
@@ -1824,18 +1563,18 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>69.900000000000006</v>
@@ -1847,18 +1586,18 @@
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>15.35</v>
@@ -1870,18 +1609,18 @@
         <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6">
         <v>479.68</v>
@@ -1893,18 +1632,18 @@
         <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>14.7</v>
@@ -1916,18 +1655,18 @@
         <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>28.5</v>
@@ -1939,18 +1678,18 @@
         <v>45</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9">
         <v>392.21</v>
@@ -1962,18 +1701,18 @@
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="B10" t="s">
-        <v>36</v>
-      </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>9.81</v>
@@ -1985,18 +1724,18 @@
         <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
         <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>17</v>
       </c>
       <c r="D11">
         <v>506.85</v>
@@ -2008,18 +1747,18 @@
         <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>49.5</v>
@@ -2031,18 +1770,18 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13">
         <v>415.36</v>
@@ -2054,18 +1793,18 @@
         <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>209.47</v>
@@ -2077,18 +1816,18 @@
         <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15">
         <v>91.32</v>
@@ -2100,18 +1839,18 @@
         <v>56</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>321.5</v>
@@ -2123,18 +1862,18 @@
         <v>54</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17">
         <v>323.04000000000002</v>
@@ -2146,18 +1885,18 @@
         <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18">
         <v>14.07</v>
@@ -2169,18 +1908,18 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19">
         <v>626.45000000000005</v>
@@ -2192,18 +1931,18 @@
         <v>29</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20">
         <v>486.65</v>
@@ -2215,18 +1954,18 @@
         <v>54</v>
       </c>
       <c r="G20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <v>31.23</v>
@@ -2238,18 +1977,18 @@
         <v>45</v>
       </c>
       <c r="G21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
         <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>17</v>
       </c>
       <c r="D22">
         <v>499.21</v>
@@ -2261,18 +2000,18 @@
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
         <v>53</v>
       </c>
-      <c r="B23" t="s">
-        <v>54</v>
-      </c>
       <c r="C23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D23">
         <v>4.78</v>
@@ -2284,18 +2023,18 @@
         <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" t="s">
         <v>55</v>
       </c>
-      <c r="B24" t="s">
-        <v>56</v>
-      </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24">
         <v>388.77</v>
@@ -2307,18 +2046,18 @@
         <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25">
         <v>43.88</v>
@@ -2330,18 +2069,18 @@
         <v>35</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s">
         <v>58</v>
       </c>
-      <c r="B26" t="s">
-        <v>59</v>
-      </c>
       <c r="C26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D26">
         <v>584.71</v>
@@ -2353,18 +2092,18 @@
         <v>64</v>
       </c>
       <c r="G26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27">
         <v>140.75</v>
@@ -2376,18 +2115,18 @@
         <v>26</v>
       </c>
       <c r="G27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28">
         <v>129.6</v>
@@ -2399,18 +2138,18 @@
         <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29">
         <v>58.66</v>
@@ -2422,18 +2161,18 @@
         <v>39</v>
       </c>
       <c r="G29" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D30">
         <v>298.7</v>
@@ -2445,18 +2184,18 @@
         <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" t="s">
         <v>64</v>
       </c>
-      <c r="B31" t="s">
-        <v>65</v>
-      </c>
       <c r="C31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31">
         <v>193.29</v>
@@ -2468,18 +2207,18 @@
         <v>51</v>
       </c>
       <c r="G31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" t="s">
         <v>16</v>
-      </c>
-      <c r="C32" t="s">
-        <v>17</v>
       </c>
       <c r="D32">
         <v>95.46</v>
@@ -2491,18 +2230,18 @@
         <v>28</v>
       </c>
       <c r="G32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33">
         <v>22.25</v>
@@ -2514,18 +2253,18 @@
         <v>51</v>
       </c>
       <c r="G33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D34">
         <v>6.7</v>
@@ -2537,18 +2276,18 @@
         <v>22</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35">
         <v>218.05</v>
@@ -2560,18 +2299,18 @@
         <v>35</v>
       </c>
       <c r="G35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36">
         <v>26.02</v>
@@ -2583,18 +2322,18 @@
         <v>38</v>
       </c>
       <c r="G36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" t="s">
         <v>71</v>
       </c>
-      <c r="B37" t="s">
-        <v>72</v>
-      </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D37">
         <v>35.44</v>
@@ -2606,18 +2345,18 @@
         <v>64</v>
       </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D38">
         <v>48.5</v>
@@ -2629,18 +2368,18 @@
         <v>56</v>
       </c>
       <c r="G38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39">
         <v>251.47</v>
@@ -2652,18 +2391,18 @@
         <v>32</v>
       </c>
       <c r="G39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
         <v>75</v>
       </c>
-      <c r="B40" t="s">
-        <v>76</v>
-      </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D40">
         <v>307.64</v>
@@ -2675,18 +2414,18 @@
         <v>47</v>
       </c>
       <c r="G40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D41">
         <v>307.39999999999998</v>
@@ -2698,18 +2437,18 @@
         <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42">
         <v>751.03</v>
@@ -2721,18 +2460,18 @@
         <v>64</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D43">
         <v>34.24</v>
@@ -2744,18 +2483,18 @@
         <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D44">
         <v>242.69</v>
@@ -2767,18 +2506,18 @@
         <v>28</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D45">
         <v>46.8</v>
@@ -2790,18 +2529,18 @@
         <v>37</v>
       </c>
       <c r="G45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D46">
         <v>508.76</v>
@@ -2813,18 +2552,18 @@
         <v>22</v>
       </c>
       <c r="G46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" t="s">
         <v>16</v>
-      </c>
-      <c r="C47" t="s">
-        <v>17</v>
       </c>
       <c r="D47">
         <v>754.2</v>
@@ -2836,18 +2575,18 @@
         <v>38</v>
       </c>
       <c r="G47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D48">
         <v>254.26</v>
@@ -2859,18 +2598,18 @@
         <v>35</v>
       </c>
       <c r="G48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49">
         <v>429.06</v>
@@ -2882,18 +2621,18 @@
         <v>25</v>
       </c>
       <c r="G49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D50">
         <v>2.17</v>
@@ -2905,18 +2644,18 @@
         <v>62</v>
       </c>
       <c r="G50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D51">
         <v>35.869999999999997</v>
@@ -2928,18 +2667,18 @@
         <v>22</v>
       </c>
       <c r="G51" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D52">
         <v>459.19</v>
@@ -2951,18 +2690,18 @@
         <v>59</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D53">
         <v>198.21</v>
@@ -2974,18 +2713,18 @@
         <v>44</v>
       </c>
       <c r="G53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D54">
         <v>395.56</v>
@@ -2997,18 +2736,18 @@
         <v>61</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D55">
         <v>488.7</v>
@@ -3020,18 +2759,18 @@
         <v>48</v>
       </c>
       <c r="G55" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D56">
         <v>40.51</v>
@@ -3043,18 +2782,18 @@
         <v>39</v>
       </c>
       <c r="G56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57">
         <v>43.21</v>
@@ -3066,18 +2805,18 @@
         <v>34</v>
       </c>
       <c r="G57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D58">
         <v>12.7</v>
@@ -3089,18 +2828,18 @@
         <v>47</v>
       </c>
       <c r="G58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D59">
         <v>32.79</v>
@@ -3112,18 +2851,18 @@
         <v>65</v>
       </c>
       <c r="G59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D60">
         <v>441.59</v>
@@ -3135,18 +2874,18 @@
         <v>33</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61">
         <v>308.37</v>
@@ -3158,18 +2897,18 @@
         <v>42</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D62">
         <v>452.26</v>
@@ -3181,18 +2920,18 @@
         <v>38</v>
       </c>
       <c r="G62" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D63">
         <v>565.14</v>
@@ -3204,18 +2943,18 @@
         <v>45</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D64">
         <v>17.07</v>
@@ -3227,18 +2966,18 @@
         <v>41</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D65">
         <v>35.47</v>
@@ -3250,18 +2989,18 @@
         <v>30</v>
       </c>
       <c r="G65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D66">
         <v>31.54</v>
@@ -3270,18 +3009,18 @@
         <v>5</v>
       </c>
       <c r="G66" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D67">
         <v>22.63</v>
@@ -3293,18 +3032,18 @@
         <v>60</v>
       </c>
       <c r="G67" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B68" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D68">
         <v>26.54</v>
@@ -3316,18 +3055,18 @@
         <v>64</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D69">
         <v>301.39</v>
@@ -3339,18 +3078,18 @@
         <v>65</v>
       </c>
       <c r="G69" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D70">
         <v>46.95</v>
@@ -3362,18 +3101,18 @@
         <v>61</v>
       </c>
       <c r="G70" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D71">
         <v>11.33</v>
@@ -3385,18 +3124,18 @@
         <v>53</v>
       </c>
       <c r="G71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B72" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" t="s">
         <v>16</v>
-      </c>
-      <c r="C72" t="s">
-        <v>17</v>
       </c>
       <c r="D72">
         <v>719.49</v>
@@ -3408,18 +3147,18 @@
         <v>49</v>
       </c>
       <c r="G72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D73">
         <v>398.41</v>
@@ -3431,18 +3170,18 @@
         <v>37</v>
       </c>
       <c r="G73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D74">
         <v>342.1</v>
@@ -3454,18 +3193,18 @@
         <v>60</v>
       </c>
       <c r="G74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D75">
         <v>41.12</v>
@@ -3477,18 +3216,18 @@
         <v>49</v>
       </c>
       <c r="G75" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D76">
         <v>238.78</v>
@@ -3500,18 +3239,18 @@
         <v>62</v>
       </c>
       <c r="G76" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B77" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D77">
         <v>15.18</v>
@@ -3523,18 +3262,18 @@
         <v>40</v>
       </c>
       <c r="G77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B78" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" t="s">
         <v>16</v>
-      </c>
-      <c r="C78" t="s">
-        <v>17</v>
       </c>
       <c r="D78">
         <v>153.78</v>
@@ -3546,18 +3285,18 @@
         <v>46</v>
       </c>
       <c r="G78" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C79" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D79">
         <v>218.61</v>
@@ -3569,18 +3308,18 @@
         <v>51</v>
       </c>
       <c r="G79" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D80">
         <v>45.43</v>
@@ -3592,18 +3331,18 @@
         <v>23</v>
       </c>
       <c r="G80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B81" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D81">
         <v>2.2799999999999998</v>
@@ -3615,18 +3354,18 @@
         <v>41</v>
       </c>
       <c r="G81" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D82">
         <v>37.880000000000003</v>
@@ -3638,18 +3377,18 @@
         <v>60</v>
       </c>
       <c r="G82" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C83" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D83">
         <v>25.31</v>
@@ -3661,18 +3400,18 @@
         <v>43</v>
       </c>
       <c r="G83" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D84">
         <v>680.38</v>
@@ -3684,18 +3423,18 @@
         <v>61</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D85">
         <v>547.25</v>
@@ -3707,18 +3446,18 @@
         <v>63</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D86">
         <v>148.57</v>
@@ -3730,18 +3469,18 @@
         <v>35</v>
       </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B87" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D87">
         <v>38.1</v>
@@ -3753,18 +3492,18 @@
         <v>38</v>
       </c>
       <c r="G87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D88">
         <v>89.06</v>
@@ -3776,18 +3515,18 @@
         <v>36</v>
       </c>
       <c r="G88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" t="s">
         <v>16</v>
-      </c>
-      <c r="C89" t="s">
-        <v>17</v>
       </c>
       <c r="D89">
         <v>615.66999999999996</v>
@@ -3799,18 +3538,18 @@
         <v>34</v>
       </c>
       <c r="G89" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D90">
         <v>249.94</v>
@@ -3822,18 +3561,18 @@
         <v>58</v>
       </c>
       <c r="G90" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B91" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C91" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D91">
         <v>10.050000000000001</v>
@@ -3845,18 +3584,18 @@
         <v>29</v>
       </c>
       <c r="G91" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D92">
         <v>29.78</v>
@@ -3868,18 +3607,18 @@
         <v>58</v>
       </c>
       <c r="G92" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D93">
         <v>5.65</v>
@@ -3891,18 +3630,18 @@
         <v>28</v>
       </c>
       <c r="G93" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D94">
         <v>654.15</v>
@@ -3914,18 +3653,18 @@
         <v>24</v>
       </c>
       <c r="G94" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D95">
         <v>26.29</v>
@@ -3937,18 +3676,18 @@
         <v>22</v>
       </c>
       <c r="G95" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D96">
         <v>481.37</v>
@@ -3960,18 +3699,18 @@
         <v>31</v>
       </c>
       <c r="G96" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D97">
         <v>511.93</v>
@@ -3983,18 +3722,18 @@
         <v>52</v>
       </c>
       <c r="G97" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D98">
         <v>291.73</v>
@@ -4006,18 +3745,18 @@
         <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D99">
         <v>31.3</v>
@@ -4029,18 +3768,18 @@
         <v>43</v>
       </c>
       <c r="G99" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D100">
         <v>125.76</v>
@@ -4052,18 +3791,18 @@
         <v>43</v>
       </c>
       <c r="G100" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D101">
         <v>2.4900000000000002</v>
@@ -4075,18 +3814,18 @@
         <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B102" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D102">
         <v>567.96</v>
@@ -4098,18 +3837,18 @@
         <v>50</v>
       </c>
       <c r="G102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D103">
         <v>353.6</v>
@@ -4121,18 +3860,18 @@
         <v>64</v>
       </c>
       <c r="G103" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B104" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D104">
         <v>369.13</v>
@@ -4144,18 +3883,18 @@
         <v>43</v>
       </c>
       <c r="G104" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D105">
         <v>13.07</v>
@@ -4167,18 +3906,18 @@
         <v>42</v>
       </c>
       <c r="G105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B106" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D106">
         <v>193.66</v>
@@ -4190,18 +3929,18 @@
         <v>39</v>
       </c>
       <c r="G106" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D107">
         <v>262.25</v>
@@ -4213,18 +3952,18 @@
         <v>34</v>
       </c>
       <c r="G107" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B108" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D108">
         <v>35.979999999999997</v>
@@ -4236,18 +3975,18 @@
         <v>39</v>
       </c>
       <c r="G108" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C109" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D109">
         <v>32.619999999999997</v>
@@ -4259,18 +3998,18 @@
         <v>28</v>
       </c>
       <c r="G109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B110" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D110">
         <v>23.14</v>
@@ -4282,18 +4021,18 @@
         <v>25</v>
       </c>
       <c r="G110" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B111" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C111" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D111">
         <v>215.34</v>
@@ -4305,18 +4044,18 @@
         <v>58</v>
       </c>
       <c r="G111" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B112" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D112">
         <v>475.83</v>
@@ -4328,18 +4067,18 @@
         <v>37</v>
       </c>
       <c r="G112" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D113">
         <v>643.05999999999995</v>
@@ -4351,18 +4090,18 @@
         <v>55</v>
       </c>
       <c r="G113" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B114" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D114">
         <v>49.52</v>
@@ -4374,18 +4113,18 @@
         <v>58</v>
       </c>
       <c r="G114" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" t="s">
         <v>16</v>
-      </c>
-      <c r="C115" t="s">
-        <v>17</v>
       </c>
       <c r="D115">
         <v>760.69</v>
@@ -4397,18 +4136,18 @@
         <v>62</v>
       </c>
       <c r="G115" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B116" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C116" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D116">
         <v>107.56</v>
@@ -4420,18 +4159,18 @@
         <v>32</v>
       </c>
       <c r="G116" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B117" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C117" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D117">
         <v>268.44</v>
@@ -4443,18 +4182,18 @@
         <v>40</v>
       </c>
       <c r="G117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B118" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C118" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D118">
         <v>34.99</v>
@@ -4466,18 +4205,18 @@
         <v>62</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B119" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C119" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D119">
         <v>79.52</v>
@@ -4489,18 +4228,18 @@
         <v>63</v>
       </c>
       <c r="G119" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C120" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D120">
         <v>53.33</v>
@@ -4512,18 +4251,18 @@
         <v>60</v>
       </c>
       <c r="G120" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C121" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D121">
         <v>7.97</v>
@@ -4535,18 +4274,18 @@
         <v>47</v>
       </c>
       <c r="G121" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C122" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D122">
         <v>5.86</v>
@@ -4558,18 +4297,18 @@
         <v>49</v>
       </c>
       <c r="G122" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B123" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D123">
         <v>133.74</v>
@@ -4581,18 +4320,18 @@
         <v>59</v>
       </c>
       <c r="G123" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B124" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C124" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D124">
         <v>482.19</v>
@@ -4604,18 +4343,18 @@
         <v>52</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B125" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D125">
         <v>49.85</v>
@@ -4627,18 +4366,18 @@
         <v>62</v>
       </c>
       <c r="G125" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C126" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D126">
         <v>21.6</v>
@@ -4650,18 +4389,18 @@
         <v>64</v>
       </c>
       <c r="G126" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B127" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D127">
         <v>15.83</v>
@@ -4673,18 +4412,18 @@
         <v>57</v>
       </c>
       <c r="G127" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B128" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C128" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D128">
         <v>7.56</v>
@@ -4693,18 +4432,18 @@
         <v>7</v>
       </c>
       <c r="G128" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B129" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D129">
         <v>359.94</v>
@@ -4716,18 +4455,18 @@
         <v>55</v>
       </c>
       <c r="G129" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B130" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C130" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D130">
         <v>619.99</v>
@@ -4739,18 +4478,18 @@
         <v>39</v>
       </c>
       <c r="G130" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B131" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C131" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D131">
         <v>7.83</v>
@@ -4762,18 +4501,18 @@
         <v>37</v>
       </c>
       <c r="G131" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D132">
         <v>218.8</v>
@@ -4785,18 +4524,18 @@
         <v>29</v>
       </c>
       <c r="G132" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B133" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C133" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D133">
         <v>468.01</v>
@@ -4808,18 +4547,18 @@
         <v>54</v>
       </c>
       <c r="G133" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B134" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C134" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D134">
         <v>13.7</v>
@@ -4831,18 +4570,18 @@
         <v>31</v>
       </c>
       <c r="G134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B135" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C135" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D135">
         <v>698.02</v>
@@ -4854,18 +4593,18 @@
         <v>48</v>
       </c>
       <c r="G135" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B136" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D136">
         <v>15.58</v>
@@ -4877,18 +4616,18 @@
         <v>59</v>
       </c>
       <c r="G136" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B137" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C137" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D137">
         <v>280.83</v>
@@ -4900,18 +4639,18 @@
         <v>43</v>
       </c>
       <c r="G137" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B138" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C138" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D138">
         <v>43.74</v>
@@ -4923,18 +4662,18 @@
         <v>58</v>
       </c>
       <c r="G138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B139" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C139" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D139">
         <v>17.27</v>
@@ -4946,18 +4685,18 @@
         <v>46</v>
       </c>
       <c r="G139" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B140" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C140" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D140">
         <v>421.5</v>
@@ -4969,18 +4708,18 @@
         <v>30</v>
       </c>
       <c r="G140" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B141" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C141" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D141">
         <v>72.36</v>
@@ -4992,18 +4731,18 @@
         <v>22</v>
       </c>
       <c r="G141" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B142" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C142" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D142">
         <v>106.12</v>
@@ -5015,18 +4754,18 @@
         <v>43</v>
       </c>
       <c r="G142" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B143" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D143">
         <v>429.86</v>
@@ -5038,18 +4777,18 @@
         <v>46</v>
       </c>
       <c r="G143" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C144" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D144">
         <v>3.72</v>
@@ -5061,18 +4800,18 @@
         <v>37</v>
       </c>
       <c r="G144" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B145" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D145">
         <v>231.14</v>
@@ -5084,18 +4823,18 @@
         <v>62</v>
       </c>
       <c r="G145" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B146" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D146">
         <v>454.13</v>
@@ -5107,18 +4846,18 @@
         <v>42</v>
       </c>
       <c r="G146" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B147" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C147" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D147">
         <v>8.99</v>
@@ -5130,18 +4869,18 @@
         <v>48</v>
       </c>
       <c r="G147" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B148" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C148" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D148">
         <v>62.51</v>
@@ -5153,18 +4892,18 @@
         <v>61</v>
       </c>
       <c r="G148" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B149" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C149" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D149">
         <v>224.14</v>
@@ -5173,18 +4912,18 @@
         <v>5</v>
       </c>
       <c r="G149" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B150" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C150" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D150">
         <v>34.53</v>
@@ -5196,18 +4935,18 @@
         <v>26</v>
       </c>
       <c r="G150" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B151" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C151" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D151">
         <v>529.20000000000005</v>
@@ -5219,18 +4958,18 @@
         <v>38</v>
       </c>
       <c r="G151" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B152" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C152" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D152">
         <v>7.12</v>
@@ -5242,18 +4981,18 @@
         <v>58</v>
       </c>
       <c r="G152" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B153" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C153" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D153">
         <v>66.45</v>
@@ -5265,18 +5004,18 @@
         <v>39</v>
       </c>
       <c r="G153" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B154" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154" t="s">
         <v>16</v>
-      </c>
-      <c r="C154" t="s">
-        <v>17</v>
       </c>
       <c r="D154">
         <v>732.96</v>
@@ -5288,18 +5027,18 @@
         <v>40</v>
       </c>
       <c r="G154" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B155" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C155" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D155">
         <v>32.56</v>
@@ -5311,18 +5050,18 @@
         <v>38</v>
       </c>
       <c r="G155" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B156" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C156" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D156">
         <v>521.19000000000005</v>
@@ -5331,18 +5070,18 @@
         <v>1</v>
       </c>
       <c r="G156" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B157" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C157" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D157">
         <v>6.33</v>
@@ -5354,18 +5093,18 @@
         <v>42</v>
       </c>
       <c r="G157" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B158" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C158" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D158">
         <v>441.32</v>
@@ -5377,18 +5116,18 @@
         <v>55</v>
       </c>
       <c r="G158" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B159" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C159" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D159">
         <v>459.17</v>
@@ -5400,18 +5139,18 @@
         <v>40</v>
       </c>
       <c r="G159" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B160" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C160" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D160">
         <v>482.37</v>
@@ -5423,18 +5162,18 @@
         <v>36</v>
       </c>
       <c r="G160" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B161" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C161" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D161">
         <v>19.559999999999999</v>
@@ -5446,18 +5185,18 @@
         <v>22</v>
       </c>
       <c r="G161" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B162" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D162">
         <v>30.06</v>
@@ -5469,18 +5208,18 @@
         <v>28</v>
       </c>
       <c r="G162" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B163" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C163" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D163">
         <v>296</v>
@@ -5492,18 +5231,18 @@
         <v>36</v>
       </c>
       <c r="G163" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B164" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C164" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D164">
         <v>33.159999999999997</v>
@@ -5512,18 +5251,18 @@
         <v>2</v>
       </c>
       <c r="G164" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B165" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C165" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D165">
         <v>6.67</v>
@@ -5535,18 +5274,18 @@
         <v>30</v>
       </c>
       <c r="G165" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B166" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C166" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D166">
         <v>364.35</v>
@@ -5558,18 +5297,18 @@
         <v>48</v>
       </c>
       <c r="G166" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B167" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C167" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D167">
         <v>754.29</v>
@@ -5581,18 +5320,18 @@
         <v>24</v>
       </c>
       <c r="G167" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B168" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C168" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D168">
         <v>43.06</v>
@@ -5604,18 +5343,18 @@
         <v>65</v>
       </c>
       <c r="G168" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B169" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C169" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D169">
         <v>95.41</v>
@@ -5627,18 +5366,18 @@
         <v>34</v>
       </c>
       <c r="G169" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B170" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C170" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D170">
         <v>33.81</v>
@@ -5650,18 +5389,18 @@
         <v>23</v>
       </c>
       <c r="G170" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B171" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C171" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D171">
         <v>122.47</v>
@@ -5673,18 +5412,18 @@
         <v>35</v>
       </c>
       <c r="G171" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B172" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D172">
         <v>392.83</v>
@@ -5696,18 +5435,18 @@
         <v>22</v>
       </c>
       <c r="G172" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B173" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D173">
         <v>144.06</v>
@@ -5716,18 +5455,18 @@
         <v>3</v>
       </c>
       <c r="G173" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B174" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C174" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D174">
         <v>400.24</v>
@@ -5739,18 +5478,18 @@
         <v>59</v>
       </c>
       <c r="G174" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B175" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C175" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D175">
         <v>377.32</v>
@@ -5762,18 +5501,18 @@
         <v>29</v>
       </c>
       <c r="G175" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B176" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C176" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D176">
         <v>30.5</v>
@@ -5785,18 +5524,18 @@
         <v>54</v>
       </c>
       <c r="G176" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B177" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C177" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D177">
         <v>276.22000000000003</v>
@@ -5808,18 +5547,18 @@
         <v>25</v>
       </c>
       <c r="G177" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B178" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C178" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D178">
         <v>25.53</v>
@@ -5831,18 +5570,18 @@
         <v>26</v>
       </c>
       <c r="G178" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B179" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C179" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D179">
         <v>84.94</v>
@@ -5854,18 +5593,18 @@
         <v>62</v>
       </c>
       <c r="G179" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B180" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C180" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D180">
         <v>27.47</v>
@@ -5877,18 +5616,18 @@
         <v>54</v>
       </c>
       <c r="G180" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" t="s">
         <v>16</v>
-      </c>
-      <c r="C181" t="s">
-        <v>17</v>
       </c>
       <c r="D181">
         <v>689.59</v>
@@ -5900,18 +5639,18 @@
         <v>35</v>
       </c>
       <c r="G181" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B182" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C182" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D182">
         <v>41.72</v>
@@ -5923,18 +5662,18 @@
         <v>48</v>
       </c>
       <c r="G182" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B183" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C183" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D183">
         <v>19.97</v>
@@ -5946,18 +5685,18 @@
         <v>65</v>
       </c>
       <c r="G183" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B184" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C184" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D184">
         <v>230.14</v>
@@ -5969,18 +5708,18 @@
         <v>30</v>
       </c>
       <c r="G184" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B185" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C185" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D185">
         <v>297.23</v>
@@ -5992,18 +5731,18 @@
         <v>48</v>
       </c>
       <c r="G185" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B186" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C186" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D186">
         <v>48.48</v>
@@ -6015,18 +5754,18 @@
         <v>41</v>
       </c>
       <c r="G186" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B187" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C187" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D187">
         <v>336.95</v>
@@ -6038,18 +5777,18 @@
         <v>28</v>
       </c>
       <c r="G187" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C188" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D188">
         <v>297.7</v>
@@ -6061,18 +5800,18 @@
         <v>57</v>
       </c>
       <c r="G188" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B189" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C189" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D189">
         <v>69.69</v>
@@ -6084,18 +5823,18 @@
         <v>23</v>
       </c>
       <c r="G189" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B190" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C190" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D190">
         <v>18.850000000000001</v>
@@ -6107,18 +5846,18 @@
         <v>31</v>
       </c>
       <c r="G190" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B191" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C191" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D191">
         <v>68.58</v>
@@ -6130,18 +5869,18 @@
         <v>35</v>
       </c>
       <c r="G191" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B192" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D192">
         <v>173.03</v>
@@ -6153,18 +5892,18 @@
         <v>58</v>
       </c>
       <c r="G192" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B193" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C193" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D193">
         <v>383.36</v>
@@ -6176,18 +5915,18 @@
         <v>65</v>
       </c>
       <c r="G193" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B194" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C194" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D194">
         <v>31.14</v>
@@ -6199,18 +5938,18 @@
         <v>39</v>
       </c>
       <c r="G194" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A195" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B195" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C195" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D195">
         <v>7.32</v>
@@ -6222,18 +5961,18 @@
         <v>53</v>
       </c>
       <c r="G195" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A196" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B196" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C196" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D196">
         <v>492.61</v>
@@ -6245,18 +5984,18 @@
         <v>22</v>
       </c>
       <c r="G196" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A197" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B197" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C197" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D197">
         <v>162.49</v>
@@ -6268,18 +6007,18 @@
         <v>22</v>
       </c>
       <c r="G197" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A198" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B198" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C198" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D198">
         <v>277.98</v>
@@ -6291,18 +6030,18 @@
         <v>54</v>
       </c>
       <c r="G198" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A199" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B199" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C199" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D199">
         <v>21.06</v>
@@ -6314,18 +6053,18 @@
         <v>49</v>
       </c>
       <c r="G199" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B200" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C200" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D200">
         <v>22.61</v>
@@ -6337,18 +6076,18 @@
         <v>62</v>
       </c>
       <c r="G200" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A201" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B201" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C201" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D201">
         <v>106.64</v>
@@ -6360,7 +6099,7 @@
         <v>51</v>
       </c>
       <c r="G201" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6373,7 +6112,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E979612-8BD7-40EA-9D5A-2165C0273E84}">
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:A178"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="23.73046875" bestFit="1" customWidth="1"/>
@@ -6386,2565 +6125,154 @@
     <col min="8" max="8" width="13.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="e" cm="1" vm="1">
         <f t="array" ref="A1">_xlfn._xlws.PY(1,1,sales[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="str" cm="1">
-        <f t="array" ref="A3:G8">_xlfn._xlws.PY(2,0)</f>
-        <v>order_id</v>
-      </c>
-      <c r="B3" t="str">
-        <v>product</v>
-      </c>
-      <c r="C3" t="str">
-        <v>category</v>
-      </c>
-      <c r="D3" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="E3" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="F3" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="G3" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="str">
-        <v>ORD-0001</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="D4">
-        <v>68.760000000000005</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>37</v>
-      </c>
-      <c r="G4" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="str">
-        <v>ORD-0002</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Lamp</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="D5">
-        <v>115.2</v>
-      </c>
-      <c r="E5">
-        <v>7</v>
-      </c>
-      <c r="F5">
-        <v>24</v>
-      </c>
-      <c r="G5" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="str">
-        <v>ORD-0003</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Lamp</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="D6">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>63</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7" t="str">
-        <v>ORD-0004</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Notebook</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="D7">
-        <v>15.35</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>32</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8" t="str">
-        <v>ORD-0005</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="D8">
-        <v>479.68</v>
-      </c>
-      <c r="E8">
-        <v>6</v>
-      </c>
-      <c r="F8">
-        <v>28</v>
-      </c>
-      <c r="G8" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A10" t="str" cm="1">
-        <f t="array" ref="A10:H15">_xlfn._xlws.PY(3,0)</f>
-        <v/>
-      </c>
-      <c r="B10" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C10" t="str">
-        <v>product</v>
-      </c>
-      <c r="D10" t="str">
-        <v>category</v>
-      </c>
-      <c r="E10" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F10" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G10" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H10" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A11">
-        <v>195</v>
-      </c>
-      <c r="B11" t="str">
-        <v>ORD-0196</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E11">
-        <v>162.49</v>
-      </c>
-      <c r="F11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>22</v>
-      </c>
-      <c r="H11" t="str">
-        <v>United Kingdom</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>196</v>
-      </c>
-      <c r="B12" t="str">
-        <v>ORD-0197</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E12">
-        <v>277.98</v>
-      </c>
-      <c r="F12">
-        <v>4</v>
-      </c>
-      <c r="G12">
-        <v>54</v>
-      </c>
-      <c r="H12" t="str">
-        <v>United Kingdom</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>197</v>
-      </c>
-      <c r="B13" t="str">
-        <v>ORD-0198</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Printer Paper</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E13">
-        <v>21.06</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>49</v>
-      </c>
-      <c r="H13" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <v>198</v>
-      </c>
-      <c r="B14" t="str">
-        <v>ORD-0199</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Notebook</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E14">
-        <v>22.61</v>
-      </c>
-      <c r="F14">
-        <v>7</v>
-      </c>
-      <c r="G14">
-        <v>62</v>
-      </c>
-      <c r="H14" t="str">
-        <v>United Kingdom</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A15">
-        <v>199</v>
-      </c>
-      <c r="B15" t="str">
-        <v>ORD-0200</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E15">
-        <v>106.64</v>
-      </c>
-      <c r="F15">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>51</v>
-      </c>
-      <c r="H15" t="str">
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17" t="str" cm="1">
-        <f t="array" ref="A17:H22">_xlfn._xlws.PY(4,0)</f>
-        <v/>
-      </c>
-      <c r="B17" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C17" t="str">
-        <v>product</v>
-      </c>
-      <c r="D17" t="str">
-        <v>category</v>
-      </c>
-      <c r="E17" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F17" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G17" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H17" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A18">
-        <v>0</v>
-      </c>
-      <c r="B18" t="str">
-        <v>ORD-0001</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E18">
-        <v>68.760000000000005</v>
-      </c>
-      <c r="F18">
-        <v>5</v>
-      </c>
-      <c r="G18">
-        <v>37</v>
-      </c>
-      <c r="H18" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19">
-        <v>75</v>
-      </c>
-      <c r="B19" t="str">
-        <v>ORD-0076</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Pens</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E19">
-        <v>15.18</v>
-      </c>
-      <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>40</v>
-      </c>
-      <c r="H19" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A20">
-        <v>25</v>
-      </c>
-      <c r="B20" t="str">
-        <v>ORD-0026</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Filing Cabinet</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E20">
-        <v>140.75</v>
-      </c>
-      <c r="F20">
-        <v>4</v>
-      </c>
-      <c r="G20">
-        <v>26</v>
-      </c>
-      <c r="H20" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21">
-        <v>120</v>
-      </c>
-      <c r="B21" t="str">
-        <v>ORD-0121</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Stapler</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E21">
-        <v>5.86</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>49</v>
-      </c>
-      <c r="H21" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22">
-        <v>130</v>
-      </c>
-      <c r="B22" t="str">
-        <v>ORD-0131</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Keyboard</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E22">
-        <v>218.8</v>
-      </c>
-      <c r="F22">
-        <v>4</v>
-      </c>
-      <c r="G22">
-        <v>29</v>
-      </c>
-      <c r="H22" t="str">
-        <v>United Kingdom</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" t="str" cm="1">
-        <f t="array" ref="A24:B30">_xlfn._xlws.PY(5,0)</f>
-        <v>order_id</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" t="str">
-        <v>product</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A26" t="str">
-        <v>category</v>
-      </c>
-      <c r="B26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A27" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A28" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="B28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A29" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="B29">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A30" t="str">
-        <v>country</v>
-      </c>
-      <c r="B30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A32" t="str" cm="1">
-        <f t="array" ref="A32:B38">_xlfn._xlws.PY(6,0)</f>
-        <v>customer_age</v>
-      </c>
-      <c r="B32">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A33" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A34" t="str">
-        <v>product</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A35" t="str">
-        <v>category</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A36" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A37" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A38" t="str">
-        <v>country</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A40" cm="1">
-        <f t="array" ref="A40:A41">_xlfn._xlws.PY(7,0)</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A41">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A43" t="str" cm="1">
-        <f t="array" ref="A43:D51">_xlfn._xlws.PY(8,0)</f>
-        <v/>
-      </c>
-      <c r="B43" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="C43" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="D43" t="str">
-        <v>customer_age</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A44" t="str">
-        <v>count</v>
-      </c>
-      <c r="B44">
-        <v>200</v>
-      </c>
-      <c r="C44">
-        <v>200</v>
-      </c>
-      <c r="D44">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A45" t="str">
-        <v>mean</v>
-      </c>
-      <c r="B45">
-        <v>211.94830000000002</v>
-      </c>
-      <c r="C45">
-        <v>5.7</v>
-      </c>
-      <c r="D45">
-        <v>43.597938144329895</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A46" t="str">
-        <v>std</v>
-      </c>
-      <c r="B46">
-        <v>215.73323312713649</v>
-      </c>
-      <c r="C46">
-        <v>2.7252771745993041</v>
-      </c>
-      <c r="D46">
-        <v>13.286527356620564</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A47" t="str">
-        <v>min</v>
-      </c>
-      <c r="B47">
-        <v>2.17</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A48" t="str">
-        <v>25%</v>
-      </c>
-      <c r="B48">
-        <v>31.2075</v>
-      </c>
-      <c r="C48">
-        <v>4</v>
-      </c>
-      <c r="D48">
-        <v>33.25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A49" t="str">
-        <v>50%</v>
-      </c>
-      <c r="B49">
-        <v>111.38</v>
-      </c>
-      <c r="C49">
-        <v>5.5</v>
-      </c>
-      <c r="D49">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A50" t="str">
-        <v>75%</v>
-      </c>
-      <c r="B50">
-        <v>378.83</v>
-      </c>
-      <c r="C50">
-        <v>8</v>
-      </c>
-      <c r="D50">
-        <v>55.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A51" t="str">
-        <v>max</v>
-      </c>
-      <c r="B51">
-        <v>760.69</v>
-      </c>
-      <c r="C51">
-        <v>10</v>
-      </c>
-      <c r="D51">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A53" t="str" cm="1">
-        <f t="array" ref="A53:D61">_xlfn._xlws.PY(9,0)</f>
-        <v/>
-      </c>
-      <c r="B53" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="C53" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="D53" t="str">
-        <v>customer_age</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A54" t="str">
-        <v>count</v>
-      </c>
-      <c r="B54">
-        <v>200</v>
-      </c>
-      <c r="C54">
-        <v>200</v>
-      </c>
-      <c r="D54">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A55" t="str">
-        <v>mean</v>
-      </c>
-      <c r="B55">
-        <v>211.94830000000002</v>
-      </c>
-      <c r="C55">
-        <v>5.7</v>
-      </c>
-      <c r="D55">
-        <v>43.597938144329895</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A56" t="str">
-        <v>std</v>
-      </c>
-      <c r="B56">
-        <v>215.73323312713649</v>
-      </c>
-      <c r="C56">
-        <v>2.7252771745993041</v>
-      </c>
-      <c r="D56">
-        <v>13.286527356620564</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A57" t="str">
-        <v>min</v>
-      </c>
-      <c r="B57">
-        <v>2.17</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A58" t="str">
-        <v>10%</v>
-      </c>
-      <c r="B58">
-        <v>13.033000000000001</v>
-      </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="D58">
-        <v>25.3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" t="str">
-        <v>50%</v>
-      </c>
-      <c r="B59">
-        <v>111.38</v>
-      </c>
-      <c r="C59">
-        <v>5.5</v>
-      </c>
-      <c r="D59">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A60" t="str">
-        <v>90%</v>
-      </c>
-      <c r="B60">
-        <v>512.85599999999999</v>
-      </c>
-      <c r="C60">
-        <v>9.0999999999999943</v>
-      </c>
-      <c r="D60">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A61" t="str">
-        <v>max</v>
-      </c>
-      <c r="B61">
-        <v>760.69</v>
-      </c>
-      <c r="C61">
-        <v>10</v>
-      </c>
-      <c r="D61">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A63" t="str" cm="1">
-        <f t="array" ref="A63:E67">_xlfn._xlws.PY(10,0)</f>
-        <v/>
-      </c>
-      <c r="B63" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C63" t="str">
-        <v>product</v>
-      </c>
-      <c r="D63" t="str">
-        <v>category</v>
-      </c>
-      <c r="E63" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A64" t="str">
-        <v>count</v>
-      </c>
-      <c r="B64">
-        <v>200</v>
-      </c>
-      <c r="C64">
-        <v>200</v>
-      </c>
-      <c r="D64">
-        <v>200</v>
-      </c>
-      <c r="E64">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A65" t="str">
-        <v>unique</v>
-      </c>
-      <c r="B65">
-        <v>200</v>
-      </c>
-      <c r="C65">
-        <v>15</v>
-      </c>
-      <c r="D65">
-        <v>3</v>
-      </c>
-      <c r="E65">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A66" t="str">
-        <v>top</v>
-      </c>
-      <c r="B66" t="str">
-        <v>ORD-0001</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Notebook</v>
-      </c>
-      <c r="D66" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E66" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A67" t="str">
-        <v>freq</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="C67">
-        <v>19</v>
-      </c>
-      <c r="D67">
-        <v>80</v>
-      </c>
-      <c r="E67">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A69" t="str" cm="1">
-        <f t="array" ref="A69:C74">_xlfn._xlws.PY(11,0)</f>
-        <v>product</v>
-      </c>
-      <c r="B69" t="str">
-        <v>category</v>
-      </c>
-      <c r="C69" t="str">
-        <v>unit_price</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A70" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="B70" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="C70">
-        <v>68.760000000000005</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A71" t="str">
-        <v>Lamp</v>
-      </c>
-      <c r="B71" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="C71">
-        <v>115.2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A72" t="str">
-        <v>Lamp</v>
-      </c>
-      <c r="B72" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="C72">
-        <v>69.900000000000006</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A73" t="str">
-        <v>Notebook</v>
-      </c>
-      <c r="B73" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="C73">
-        <v>15.35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A74" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="B74" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="C74">
-        <v>479.68</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A76" t="str" cm="1">
-        <f t="array" ref="A76:A81">_xlfn._xlws.PY(12,0)</f>
-        <v>country</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A77" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A78" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A79" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A80" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A81" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A84" t="str" cm="1">
-        <f t="array" ref="A84:H89">_xlfn._xlws.PY(13,0)</f>
-        <v/>
-      </c>
-      <c r="B84" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C84" t="str">
-        <v>product</v>
-      </c>
-      <c r="D84" t="str">
-        <v>category</v>
-      </c>
-      <c r="E84" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F84" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G84" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H84" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A85">
-        <v>0</v>
-      </c>
-      <c r="B85" t="str">
-        <v>ORD-0001</v>
-      </c>
-      <c r="C85" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D85" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E85">
-        <v>68.760000000000005</v>
-      </c>
-      <c r="F85">
-        <v>5</v>
-      </c>
-      <c r="G85">
-        <v>37</v>
-      </c>
-      <c r="H85" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A86">
-        <v>1</v>
-      </c>
-      <c r="B86" t="str">
-        <v>ORD-0002</v>
-      </c>
-      <c r="C86" t="str">
-        <v>Lamp</v>
-      </c>
-      <c r="D86" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E86">
-        <v>115.2</v>
-      </c>
-      <c r="F86">
-        <v>7</v>
-      </c>
-      <c r="G86">
-        <v>24</v>
-      </c>
-      <c r="H86" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A87">
-        <v>4</v>
-      </c>
-      <c r="B87" t="str">
-        <v>ORD-0005</v>
-      </c>
-      <c r="C87" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D87" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E87">
-        <v>479.68</v>
-      </c>
-      <c r="F87">
-        <v>6</v>
-      </c>
-      <c r="G87">
-        <v>28</v>
-      </c>
-      <c r="H87" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A88">
-        <v>11</v>
-      </c>
-      <c r="B88" t="str">
-        <v>ORD-0012</v>
-      </c>
-      <c r="C88" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D88" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E88">
-        <v>415.36</v>
-      </c>
-      <c r="F88">
-        <v>6</v>
-      </c>
-      <c r="G88">
-        <v>47</v>
-      </c>
-      <c r="H88" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A89">
-        <v>13</v>
-      </c>
-      <c r="B89" t="str">
-        <v>ORD-0014</v>
-      </c>
-      <c r="C89" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="D89" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E89">
-        <v>91.32</v>
-      </c>
-      <c r="F89">
-        <v>9</v>
-      </c>
-      <c r="G89">
-        <v>56</v>
-      </c>
-      <c r="H89" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A91" t="str" cm="1">
-        <f t="array" ref="A91:H96">_xlfn._xlws.PY(14,0)</f>
-        <v/>
-      </c>
-      <c r="B91" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C91" t="str">
-        <v>product</v>
-      </c>
-      <c r="D91" t="str">
-        <v>category</v>
-      </c>
-      <c r="E91" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F91" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G91" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H91" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A92">
-        <v>0</v>
-      </c>
-      <c r="B92" t="str">
-        <v>ORD-0001</v>
-      </c>
-      <c r="C92" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D92" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E92">
-        <v>68.760000000000005</v>
-      </c>
-      <c r="F92">
-        <v>5</v>
-      </c>
-      <c r="G92">
-        <v>37</v>
-      </c>
-      <c r="H92" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A93">
-        <v>1</v>
-      </c>
-      <c r="B93" t="str">
-        <v>ORD-0002</v>
-      </c>
-      <c r="C93" t="str">
-        <v>Lamp</v>
-      </c>
-      <c r="D93" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E93">
-        <v>115.2</v>
-      </c>
-      <c r="F93">
-        <v>7</v>
-      </c>
-      <c r="G93">
-        <v>24</v>
-      </c>
-      <c r="H93" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A94">
-        <v>4</v>
-      </c>
-      <c r="B94" t="str">
-        <v>ORD-0005</v>
-      </c>
-      <c r="C94" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D94" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E94">
-        <v>479.68</v>
-      </c>
-      <c r="F94">
-        <v>6</v>
-      </c>
-      <c r="G94">
-        <v>28</v>
-      </c>
-      <c r="H94" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A95">
-        <v>11</v>
-      </c>
-      <c r="B95" t="str">
-        <v>ORD-0012</v>
-      </c>
-      <c r="C95" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D95" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E95">
-        <v>415.36</v>
-      </c>
-      <c r="F95">
-        <v>6</v>
-      </c>
-      <c r="G95">
-        <v>47</v>
-      </c>
-      <c r="H95" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A96">
-        <v>13</v>
-      </c>
-      <c r="B96" t="str">
-        <v>ORD-0014</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="D96" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E96">
-        <v>91.32</v>
-      </c>
-      <c r="F96">
-        <v>9</v>
-      </c>
-      <c r="G96">
-        <v>56</v>
-      </c>
-      <c r="H96" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A98" t="str" cm="1">
-        <f t="array" ref="A98:H103">_xlfn._xlws.PY(15,0)</f>
-        <v/>
-      </c>
-      <c r="B98" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C98" t="str">
-        <v>product</v>
-      </c>
-      <c r="D98" t="str">
-        <v>category</v>
-      </c>
-      <c r="E98" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F98" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G98" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H98" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A99">
-        <v>0</v>
-      </c>
-      <c r="B99" t="str">
-        <v>ORD-0001</v>
-      </c>
-      <c r="C99" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D99" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E99">
-        <v>68.760000000000005</v>
-      </c>
-      <c r="F99">
-        <v>5</v>
-      </c>
-      <c r="G99">
-        <v>37</v>
-      </c>
-      <c r="H99" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A100">
-        <v>1</v>
-      </c>
-      <c r="B100" t="str">
-        <v>ORD-0002</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Lamp</v>
-      </c>
-      <c r="D100" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E100">
-        <v>115.2</v>
-      </c>
-      <c r="F100">
-        <v>7</v>
-      </c>
-      <c r="G100">
-        <v>24</v>
-      </c>
-      <c r="H100" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A101">
-        <v>4</v>
-      </c>
-      <c r="B101" t="str">
-        <v>ORD-0005</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D101" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E101">
-        <v>479.68</v>
-      </c>
-      <c r="F101">
-        <v>6</v>
-      </c>
-      <c r="G101">
-        <v>28</v>
-      </c>
-      <c r="H101" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A102">
-        <v>11</v>
-      </c>
-      <c r="B102" t="str">
-        <v>ORD-0012</v>
-      </c>
-      <c r="C102" t="str">
-        <v>Tablet</v>
-      </c>
-      <c r="D102" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E102">
-        <v>415.36</v>
-      </c>
-      <c r="F102">
-        <v>6</v>
-      </c>
-      <c r="G102">
-        <v>47</v>
-      </c>
-      <c r="H102" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A103">
-        <v>13</v>
-      </c>
-      <c r="B103" t="str">
-        <v>ORD-0014</v>
-      </c>
-      <c r="C103" t="str">
-        <v>Headphones</v>
-      </c>
-      <c r="D103" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E103">
-        <v>91.32</v>
-      </c>
-      <c r="F103">
-        <v>9</v>
-      </c>
-      <c r="G103">
-        <v>56</v>
-      </c>
-      <c r="H103" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A105" t="str" cm="1">
-        <f t="array" ref="A105:H110">_xlfn._xlws.PY(16,0)</f>
-        <v/>
-      </c>
-      <c r="B105" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C105" t="str">
-        <v>product</v>
-      </c>
-      <c r="D105" t="str">
-        <v>category</v>
-      </c>
-      <c r="E105" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F105" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G105" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H105" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A106">
-        <v>48</v>
-      </c>
-      <c r="B106" t="str">
-        <v>ORD-0049</v>
-      </c>
-      <c r="C106" t="str">
-        <v>Printer Paper</v>
-      </c>
-      <c r="D106" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E106">
-        <v>2.17</v>
-      </c>
-      <c r="F106">
-        <v>3</v>
-      </c>
-      <c r="G106">
-        <v>62</v>
-      </c>
-      <c r="H106" t="str">
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A107">
-        <v>79</v>
-      </c>
-      <c r="B107" t="str">
-        <v>ORD-0080</v>
-      </c>
-      <c r="C107" t="str">
-        <v>Stapler</v>
-      </c>
-      <c r="D107" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E107">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="F107">
-        <v>6</v>
-      </c>
-      <c r="G107">
-        <v>41</v>
-      </c>
-      <c r="H107" t="str">
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A108">
-        <v>99</v>
-      </c>
-      <c r="B108" t="str">
-        <v>ORD-0100</v>
-      </c>
-      <c r="C108" t="str">
-        <v>Notebook</v>
-      </c>
-      <c r="D108" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E108">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="F108">
-        <v>4</v>
-      </c>
-      <c r="G108">
-        <v>27</v>
-      </c>
-      <c r="H108" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A109">
-        <v>142</v>
-      </c>
-      <c r="B109" t="str">
-        <v>ORD-0143</v>
-      </c>
-      <c r="C109" t="str">
-        <v>Notebook</v>
-      </c>
-      <c r="D109" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E109">
-        <v>3.72</v>
-      </c>
-      <c r="F109">
-        <v>2</v>
-      </c>
-      <c r="G109">
-        <v>37</v>
-      </c>
-      <c r="H109" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A110">
-        <v>21</v>
-      </c>
-      <c r="B110" t="str">
-        <v>ORD-0022</v>
-      </c>
-      <c r="C110" t="str">
-        <v>Pens</v>
-      </c>
-      <c r="D110" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E110">
-        <v>4.78</v>
-      </c>
-      <c r="F110">
-        <v>10</v>
-      </c>
-      <c r="G110">
-        <v>27</v>
-      </c>
-      <c r="H110" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A113" t="str" cm="1">
-        <f t="array" ref="A113:H118">_xlfn._xlws.PY(17,0)</f>
-        <v/>
-      </c>
-      <c r="B113" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C113" t="str">
-        <v>product</v>
-      </c>
-      <c r="D113" t="str">
-        <v>category</v>
-      </c>
-      <c r="E113" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F113" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G113" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H113" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A114">
-        <v>113</v>
-      </c>
-      <c r="B114" t="str">
-        <v>ORD-0114</v>
-      </c>
-      <c r="C114" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D114" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E114">
-        <v>760.69</v>
-      </c>
-      <c r="F114">
-        <v>4</v>
-      </c>
-      <c r="G114">
-        <v>62</v>
-      </c>
-      <c r="H114" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A115">
-        <v>165</v>
-      </c>
-      <c r="B115" t="str">
-        <v>ORD-0166</v>
-      </c>
-      <c r="C115" t="str">
-        <v>Filing Cabinet</v>
-      </c>
-      <c r="D115" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E115">
-        <v>754.29</v>
-      </c>
-      <c r="F115">
-        <v>5</v>
-      </c>
-      <c r="G115">
-        <v>24</v>
-      </c>
-      <c r="H115" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A116">
-        <v>45</v>
-      </c>
-      <c r="B116" t="str">
-        <v>ORD-0046</v>
-      </c>
-      <c r="C116" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D116" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E116">
-        <v>754.2</v>
-      </c>
-      <c r="F116">
-        <v>3</v>
-      </c>
-      <c r="G116">
-        <v>38</v>
-      </c>
-      <c r="H116" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A117">
-        <v>40</v>
-      </c>
-      <c r="B117" t="str">
-        <v>ORD-0041</v>
-      </c>
-      <c r="C117" t="str">
-        <v>Bookshelf</v>
-      </c>
-      <c r="D117" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E117">
-        <v>751.03</v>
-      </c>
-      <c r="F117">
-        <v>4</v>
-      </c>
-      <c r="G117">
-        <v>64</v>
-      </c>
-      <c r="H117" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A118">
-        <v>152</v>
-      </c>
-      <c r="B118" t="str">
-        <v>ORD-0153</v>
-      </c>
-      <c r="C118" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D118" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E118">
-        <v>732.96</v>
-      </c>
-      <c r="F118">
-        <v>8</v>
-      </c>
-      <c r="G118">
-        <v>40</v>
-      </c>
-      <c r="H118" t="str">
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A121" t="str" cm="1">
-        <f t="array" ref="A121:H126">_xlfn._xlws.PY(18,0)</f>
-        <v/>
-      </c>
-      <c r="B121" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C121" t="str">
-        <v>product</v>
-      </c>
-      <c r="D121" t="str">
-        <v>category</v>
-      </c>
-      <c r="E121" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F121" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G121" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H121" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A122">
-        <v>48</v>
-      </c>
-      <c r="B122" t="str">
-        <v>ORD-0049</v>
-      </c>
-      <c r="C122" t="str">
-        <v>Printer Paper</v>
-      </c>
-      <c r="D122" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E122">
-        <v>2.17</v>
-      </c>
-      <c r="F122">
-        <v>3</v>
-      </c>
-      <c r="G122">
-        <v>62</v>
-      </c>
-      <c r="H122" t="str">
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A123">
-        <v>32</v>
-      </c>
-      <c r="B123" t="str">
-        <v>ORD-0033</v>
-      </c>
-      <c r="C123" t="str">
-        <v>Notebook</v>
-      </c>
-      <c r="D123" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E123">
-        <v>6.7</v>
-      </c>
-      <c r="F123">
-        <v>9</v>
-      </c>
-      <c r="G123">
-        <v>22</v>
-      </c>
-      <c r="H123" t="str">
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A124">
-        <v>119</v>
-      </c>
-      <c r="B124" t="str">
-        <v>ORD-0120</v>
-      </c>
-      <c r="C124" t="str">
-        <v>Stapler</v>
-      </c>
-      <c r="D124" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E124">
-        <v>7.97</v>
-      </c>
-      <c r="F124">
-        <v>5</v>
-      </c>
-      <c r="G124">
-        <v>47</v>
-      </c>
-      <c r="H124" t="str">
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A125">
-        <v>181</v>
-      </c>
-      <c r="B125" t="str">
-        <v>ORD-0182</v>
-      </c>
-      <c r="C125" t="str">
-        <v>Binder</v>
-      </c>
-      <c r="D125" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="E125">
-        <v>19.97</v>
-      </c>
-      <c r="F125">
-        <v>3</v>
-      </c>
-      <c r="G125">
-        <v>65</v>
-      </c>
-      <c r="H125" t="str">
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A126">
-        <v>34</v>
-      </c>
-      <c r="B126" t="str">
-        <v>ORD-0035</v>
-      </c>
-      <c r="C126" t="str">
-        <v>Monitor</v>
-      </c>
-      <c r="D126" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="E126">
-        <v>26.02</v>
-      </c>
-      <c r="F126">
-        <v>7</v>
-      </c>
-      <c r="G126">
-        <v>38</v>
-      </c>
-      <c r="H126" t="str">
-        <v>Australia</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A129" t="str" cm="1">
-        <f t="array" ref="A129:H134">_xlfn._xlws.PY(19,0)</f>
-        <v/>
-      </c>
-      <c r="B129" t="str">
-        <v>order_id</v>
-      </c>
-      <c r="C129" t="str">
-        <v>product</v>
-      </c>
-      <c r="D129" t="str">
-        <v>category</v>
-      </c>
-      <c r="E129" t="str">
-        <v>unit_price</v>
-      </c>
-      <c r="F129" t="str">
-        <v>quantity</v>
-      </c>
-      <c r="G129" t="str">
-        <v>customer_age</v>
-      </c>
-      <c r="H129" t="str">
-        <v>country</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A130">
-        <v>113</v>
-      </c>
-      <c r="B130" t="str">
-        <v>ORD-0114</v>
-      </c>
-      <c r="C130" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D130" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E130">
-        <v>760.69</v>
-      </c>
-      <c r="F130">
-        <v>4</v>
-      </c>
-      <c r="G130">
-        <v>62</v>
-      </c>
-      <c r="H130" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A131">
-        <v>165</v>
-      </c>
-      <c r="B131" t="str">
-        <v>ORD-0166</v>
-      </c>
-      <c r="C131" t="str">
-        <v>Filing Cabinet</v>
-      </c>
-      <c r="D131" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E131">
-        <v>754.29</v>
-      </c>
-      <c r="F131">
-        <v>5</v>
-      </c>
-      <c r="G131">
-        <v>24</v>
-      </c>
-      <c r="H131" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A132">
-        <v>45</v>
-      </c>
-      <c r="B132" t="str">
-        <v>ORD-0046</v>
-      </c>
-      <c r="C132" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D132" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E132">
-        <v>754.2</v>
-      </c>
-      <c r="F132">
-        <v>3</v>
-      </c>
-      <c r="G132">
-        <v>38</v>
-      </c>
-      <c r="H132" t="str">
-        <v>United States</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A133">
-        <v>40</v>
-      </c>
-      <c r="B133" t="str">
-        <v>ORD-0041</v>
-      </c>
-      <c r="C133" t="str">
-        <v>Bookshelf</v>
-      </c>
-      <c r="D133" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E133">
-        <v>751.03</v>
-      </c>
-      <c r="F133">
-        <v>4</v>
-      </c>
-      <c r="G133">
-        <v>64</v>
-      </c>
-      <c r="H133" t="str">
-        <v>Germany</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A134">
-        <v>152</v>
-      </c>
-      <c r="B134" t="str">
-        <v>ORD-0153</v>
-      </c>
-      <c r="C134" t="str">
-        <v>Desk</v>
-      </c>
-      <c r="D134" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="E134">
-        <v>732.96</v>
-      </c>
-      <c r="F134">
-        <v>8</v>
-      </c>
-      <c r="G134">
-        <v>40</v>
-      </c>
-      <c r="H134" t="str">
-        <v>Canada</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A136" t="str" cm="1">
-        <f t="array" ref="A136:B141">_xlfn._xlws.PY(20,0)</f>
-        <v>country</v>
-      </c>
-      <c r="B136" t="str">
-        <v>count</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A137" t="str">
-        <v>United States</v>
-      </c>
-      <c r="B137">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A138" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B138">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A139" t="str">
-        <v>United Kingdom</v>
-      </c>
-      <c r="B139">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A140" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="B140">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A141" t="str">
-        <v>Australia</v>
-      </c>
-      <c r="B141">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A144" t="str" cm="1">
-        <f t="array" ref="A144:B147">_xlfn._xlws.PY(21,0)</f>
-        <v>category</v>
-      </c>
-      <c r="B144" t="str">
-        <v>proportion</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A145" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="B145">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A146" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="B146">
-        <v>0.32500000000000001</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A147" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="B147">
-        <v>0.27500000000000002</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A149" t="str" cm="1">
-        <f t="array" ref="A149:B154">_xlfn._xlws.PY(22,0)</f>
-        <v>country</v>
-      </c>
-      <c r="B149" t="str">
-        <v>unit_price</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A150" t="str">
-        <v>Australia</v>
-      </c>
-      <c r="B150">
-        <v>167.16199999999998</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A151" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="B151">
-        <v>201.18230769230769</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A152" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B152">
-        <v>182.58790697674419</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A153" t="str">
-        <v>United Kingdom</v>
-      </c>
-      <c r="B153">
-        <v>274.43128205128204</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A154" t="str">
-        <v>United States</v>
-      </c>
-      <c r="B154">
-        <v>209.05701298701297</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A156" t="str" cm="1">
-        <f t="array" ref="A156:B159">_xlfn._xlws.PY(23,0)</f>
-        <v>category</v>
-      </c>
-      <c r="B156" t="str">
-        <v>quantity</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A157" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="B157">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A158" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="B158">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A159" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="B159">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A161" t="str" cm="1">
-        <f t="array" ref="A161:C176">_xlfn._xlws.PY(24,0)</f>
-        <v>country</v>
-      </c>
-      <c r="B161" t="str">
-        <v>category</v>
-      </c>
-      <c r="C161" t="str">
-        <v>unit_price</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A162" t="str">
-        <v>Australia</v>
-      </c>
-      <c r="B162" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="C162">
-        <v>270.6516666666667</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A163" t="str">
-        <v>Australia</v>
-      </c>
-      <c r="B163" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="C163">
-        <v>256.68</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A164" t="str">
-        <v>Australia</v>
-      </c>
-      <c r="B164" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="C164">
-        <v>18.91333333333333</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A165" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="B165" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="C165">
-        <v>274.04250000000002</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A166" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="B166" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="C166">
-        <v>529.45000000000005</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A167" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="B167" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="C167">
-        <v>30.088461538461541</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A168" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B168" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="C168">
-        <v>230.67818181818183</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A169" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B169" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="C169">
-        <v>350.0864285714286</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A170" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B170" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="C170">
-        <v>22.922777777777778</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A171" t="str">
-        <v>United Kingdom</v>
-      </c>
-      <c r="B171" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="C171">
-        <v>272.95764705882351</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A172" t="str">
-        <v>United Kingdom</v>
-      </c>
-      <c r="B172" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="C172">
-        <v>529.8054545454545</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A173" t="str">
-        <v>United Kingdom</v>
-      </c>
-      <c r="B173" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="C173">
-        <v>21.334545454545456</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A174" t="str">
-        <v>United States</v>
-      </c>
-      <c r="B174" t="str">
-        <v>Electronics</v>
-      </c>
-      <c r="C174">
-        <v>296.6995652173913</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A175" t="str">
-        <v>United States</v>
-      </c>
-      <c r="B175" t="str">
-        <v>Furniture</v>
-      </c>
-      <c r="C175">
-        <v>383.92954545454546</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A176" t="str">
-        <v>United States</v>
-      </c>
-      <c r="B176" t="str">
-        <v>Office Supplies</v>
-      </c>
-      <c r="C176">
-        <v>25.839062500000001</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A178" t="str" cm="1">
-        <f t="array" ref="A178:D184">_xlfn._xlws.PY(25,0)</f>
-        <v/>
-      </c>
-      <c r="B178" t="str">
-        <v>mean</v>
-      </c>
-      <c r="C178" t="str">
-        <v>min</v>
-      </c>
-      <c r="D178" t="str">
-        <v>max</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A179" t="str">
-        <v>country</v>
-      </c>
-      <c r="B179" t="str">
-        <v/>
-      </c>
-      <c r="C179" t="str">
-        <v/>
-      </c>
-      <c r="D179" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A180" t="str">
-        <v>Australia</v>
-      </c>
-      <c r="B180">
-        <v>167.16199999999998</v>
-      </c>
-      <c r="C180">
-        <v>2.17</v>
-      </c>
-      <c r="D180">
-        <v>486.65</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A181" t="str">
-        <v>Canada</v>
-      </c>
-      <c r="B181">
-        <v>201.18230769230769</v>
-      </c>
-      <c r="C181">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="D181">
-        <v>732.96</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A182" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B182">
-        <v>182.58790697674419</v>
-      </c>
-      <c r="C182">
-        <v>3.72</v>
-      </c>
-      <c r="D182">
-        <v>754.29</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A183" t="str">
-        <v>United Kingdom</v>
-      </c>
-      <c r="B183">
-        <v>274.43128205128204</v>
-      </c>
-      <c r="C183">
-        <v>7.32</v>
-      </c>
-      <c r="D183">
-        <v>689.59</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A184" t="str">
-        <v>United States</v>
-      </c>
-      <c r="B184">
-        <v>209.05701298701297</v>
-      </c>
-      <c r="C184">
-        <v>2.4900000000000002</v>
-      </c>
-      <c r="D184">
-        <v>760.69</v>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A3" t="e" cm="1" vm="1">
+        <f t="array" ref="A3">_xlfn._xlws.PY(2,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A10" t="e" cm="1" vm="1">
+        <f t="array" ref="A10">_xlfn._xlws.PY(3,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A17" t="e" cm="1" vm="1">
+        <f t="array" ref="A17">_xlfn._xlws.PY(4,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A24" t="e" cm="1" vm="1">
+        <f t="array" ref="A24">_xlfn._xlws.PY(5,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A32" t="e" cm="1" vm="1">
+        <f t="array" ref="A32">_xlfn._xlws.PY(6,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" t="e" cm="1" vm="1">
+        <f t="array" ref="A40">_xlfn._xlws.PY(7,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" t="e" cm="1" vm="1">
+        <f t="array" ref="A43">_xlfn._xlws.PY(8,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" t="e" cm="1" vm="1">
+        <f t="array" ref="A53">_xlfn._xlws.PY(9,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A63" t="e" cm="1" vm="1">
+        <f t="array" ref="A63">_xlfn._xlws.PY(10,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A69" t="e" cm="1" vm="1">
+        <f t="array" ref="A69">_xlfn._xlws.PY(11,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A76" t="e" cm="1" vm="1">
+        <f t="array" ref="A76">_xlfn._xlws.PY(12,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A84" t="e" cm="1" vm="1">
+        <f t="array" ref="A84">_xlfn._xlws.PY(13,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A91" t="e" cm="1" vm="1">
+        <f t="array" ref="A91">_xlfn._xlws.PY(14,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A98" t="e" cm="1" vm="1">
+        <f t="array" ref="A98">_xlfn._xlws.PY(15,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A105" t="e" cm="1" vm="1">
+        <f t="array" ref="A105">_xlfn._xlws.PY(16,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A113" t="e" cm="1" vm="1">
+        <f t="array" ref="A113">_xlfn._xlws.PY(17,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A121" t="e" cm="1" vm="1">
+        <f t="array" ref="A121">_xlfn._xlws.PY(18,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A129" t="e" cm="1" vm="1">
+        <f t="array" ref="A129">_xlfn._xlws.PY(19,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A136" t="e" cm="1" vm="1">
+        <f t="array" ref="A136">_xlfn._xlws.PY(20,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A144" t="e" cm="1" vm="1">
+        <f t="array" ref="A144">_xlfn._xlws.PY(21,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A149" t="e" cm="1" vm="1">
+        <f t="array" ref="A149">_xlfn._xlws.PY(22,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A156" t="e" cm="1" vm="1">
+        <f t="array" ref="A156">_xlfn._xlws.PY(23,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A161" t="e" cm="1" vm="1">
+        <f t="array" ref="A161">_xlfn._xlws.PY(24,0)</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A178" t="e" cm="1" vm="1">
+        <f t="array" ref="A178">_xlfn._xlws.PY(25,0)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/ch_02_pandas/ch_02_solution.xlsx
+++ b/ch_02_pandas/ch_02_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_02_pandas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321BC6CD-AD96-44FF-8FED-E1A9921EBC80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611EEF9E-71F0-45CB-86D0-DAF510D771B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="14586" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nyc" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
+          <xlrd:rvb i="2"/>
         </ext>
       </extLst>
     </bk>
@@ -110,11 +110,11 @@
 sales_df.sample(5)</code>
     </pythonScript>
     <pythonScript>
-      <code># Find %% of missing values in each column
-sales_df.isna().sum() / 100</code>
+      <code xml:space="preserve"># Find %% of missing values in each column
+sales_df.isna().mean() / 100 </code>
     </pythonScript>
     <pythonScript>
-      <code>(sales_df.isna().sum().sort_values(ascending=False)) / 100</code>
+      <code>sales_df.isna().mean().sort_values(ascending=False) * 100</code>
     </pythonScript>
     <pythonScript>
       <code># Get rows and columns of DataFrame
@@ -964,9 +964,6 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -982,6 +979,9 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
       <font>
@@ -1053,22 +1053,192 @@
 </rvTypesInfo>
 </file>
 
+<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
+<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
+  <a r="12" c="8">
+    <v t="s"/>
+    <v t="s">order_id</v>
+    <v t="s">product</v>
+    <v t="s">category</v>
+    <v t="s">unit_price</v>
+    <v t="s">quantity</v>
+    <v t="s">customer_age</v>
+    <v t="s">country</v>
+    <v>0</v>
+    <v t="s">ORD-0001</v>
+    <v t="s">Desk</v>
+    <v t="s">Furniture</v>
+    <v>68.760000000000005</v>
+    <v>5</v>
+    <v>37</v>
+    <v t="s">United States</v>
+    <v>1</v>
+    <v t="s">ORD-0002</v>
+    <v t="s">Lamp</v>
+    <v t="s">Furniture</v>
+    <v>115.2</v>
+    <v>7</v>
+    <v>24</v>
+    <v t="s">United States</v>
+    <v>2</v>
+    <v t="s">ORD-0003</v>
+    <v t="s">Lamp</v>
+    <v t="s">Furniture</v>
+    <v>69.900000000000006</v>
+    <v>4</v>
+    <v>63</v>
+    <v t="s">Germany</v>
+    <v>3</v>
+    <v t="s">ORD-0004</v>
+    <v t="s">Notebook</v>
+    <v t="s">Office Supplies</v>
+    <v>15.35</v>
+    <v>1</v>
+    <v>32</v>
+    <v t="s">Germany</v>
+    <v>4</v>
+    <v t="s">ORD-0005</v>
+    <v t="s">Tablet</v>
+    <v t="s">Electronics</v>
+    <v>479.68</v>
+    <v>6</v>
+    <v>28</v>
+    <v t="s">United States</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v t="s">...</v>
+    <v>195</v>
+    <v t="s">ORD-0196</v>
+    <v t="s">Headphones</v>
+    <v t="s">Electronics</v>
+    <v>162.49</v>
+    <v>2</v>
+    <v>22</v>
+    <v t="s">United Kingdom</v>
+    <v>196</v>
+    <v t="s">ORD-0197</v>
+    <v t="s">Monitor</v>
+    <v t="s">Electronics</v>
+    <v>277.98</v>
+    <v>4</v>
+    <v>54</v>
+    <v t="s">United Kingdom</v>
+    <v>197</v>
+    <v t="s">ORD-0198</v>
+    <v t="s">Printer Paper</v>
+    <v t="s">Office Supplies</v>
+    <v>21.06</v>
+    <v>1</v>
+    <v>49</v>
+    <v t="s">United States</v>
+    <v>198</v>
+    <v t="s">ORD-0199</v>
+    <v t="s">Notebook</v>
+    <v t="s">Office Supplies</v>
+    <v>22.61</v>
+    <v>7</v>
+    <v>62</v>
+    <v t="s">United Kingdom</v>
+    <v>199</v>
+    <v t="s">ORD-0200</v>
+    <v t="s">Headphones</v>
+    <v t="s">Electronics</v>
+    <v>106.64</v>
+    <v>10</v>
+    <v>51</v>
+    <v t="s">Canada</v>
+  </a>
+</arrayData>
+</file>
+
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
-    <v>10</v>
-    <v>9</v>
+    <v>0</v>
+  </rv>
+  <rv s="1">
+    <v>DataFrame</v>
+    <v>1</v>
+    <v>0</v>
+  </rv>
+  <rv s="2">
+    <v>&lt;class 'pandas.core.frame.DataFrame'&gt;</v>
+    <v>DataFrame</v>
+    <v xml:space="preserve">     order_id        product         category  unit_price  quantity  \
+0    ORD-0001           Desk        Furniture       68.76         5   
+1    ORD-0002           Lamp        Furniture      115.20         7   
+2    ORD-0003           Lamp        Fur...</v>
+    <v>1</v>
+    <v>2</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="subType" t="i"/>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+  <s t="_array">
+    <k n="array" t="a"/>
+  </s>
+  <s t="_entity">
+    <k n="_DisplayString" t="s"/>
+    <k n="_ViewInfo" t="spb"/>
+    <k n="arrayPreview" t="r"/>
+  </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="preview" t="r"/>
+    <k n="_Provider" t="spb"/>
   </s>
 </rvStructures>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
+<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
+  <spbData count="3">
+    <spb s="0">
+      <v>200</v>
+      <v>7</v>
+      <v>DataFrame</v>
+      <v>arrayPreview</v>
+      <v>1</v>
+    </spb>
+    <spb s="1">
+      <v>0</v>
+    </spb>
+    <spb s="2">
+      <v>https://www.anaconda.com/excel</v>
+      <v>https://res.cdn.office.net/officepysvc/prod-service/anacondalogo.png</v>
+      <v>Python provided by Anaconda</v>
+    </spb>
+  </spbData>
+</supportingPropertyBags>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="3">
+  <s>
+    <k n="drw" t="i"/>
+    <k n="dcol" t="i"/>
+    <k n="name" t="s"/>
+    <k n="array" t="s"/>
+    <k n="headers" t="b"/>
+  </s>
+  <s>
+    <k n="ArrayCardInfo" t="spb"/>
+  </s>
+  <s>
+    <k n="link" t="s"/>
+    <k n="logo" t="s"/>
+    <k n="name" t="s"/>
+  </s>
+</spbStructures>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1076,7 +1246,7 @@
   <autoFilter ref="A1:C6" xr:uid="{A099DEF9-7300-4421-80EE-149706CE1CEA}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{4060128F-DD32-4555-9DB9-CA443A160D2A}" name="borough"/>
-    <tableColumn id="2" xr3:uid="{32E7E197-F690-4580-9F10-846DD215807D}" name="population" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{32E7E197-F690-4580-9F10-846DD215807D}" name="population" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{4D8417DA-D82A-4787-B91D-F9A344C39103}" name="land_area"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1084,7 +1254,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}" name="sales" displayName="sales" ref="A1:G201" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}" name="sales" displayName="sales" ref="A1:G201" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:G201" xr:uid="{DFD50F0B-C049-417D-9A23-94F4B3CCF18D}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{054A5DBB-1F62-4FF0-893D-CA3913FFC271}" name="order_id"/>
@@ -1384,19 +1554,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="14" style="4" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="11.06640625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="5"/>
+    <col min="5" max="5" width="10.87890625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.64453125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.05859375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="8.9375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1406,15 +1576,21 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="e" cm="1" vm="1">
-        <f t="array" ref="E1">_xlfn._xlws.PY(0,0,nyc_pop[#All])</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="E1" t="str" cm="1">
+        <f t="array" ref="E1:H6">_xlfn._xlws.PY(0,0,nyc_pop[#All])</f>
+        <v>borough</v>
+      </c>
+      <c r="F1" s="5" t="str">
+        <v>population</v>
+      </c>
+      <c r="G1" s="5" t="str">
+        <v>land_area</v>
+      </c>
+      <c r="H1" s="5" t="str">
+        <v>density</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1424,8 +1600,20 @@
       <c r="C2">
         <v>69.37</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="E2" t="str">
+        <v>Brooklyn</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2736074</v>
+      </c>
+      <c r="G2" s="5">
+        <v>69.37</v>
+      </c>
+      <c r="H2" s="5">
+        <v>39441.747152947959</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1435,8 +1623,20 @@
       <c r="C3">
         <v>108.53</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="E3" t="str">
+        <v>Queens</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2405464</v>
+      </c>
+      <c r="G3" s="5">
+        <v>108.53</v>
+      </c>
+      <c r="H3" s="5">
+        <v>22164.046807334376</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1446,8 +1646,20 @@
       <c r="C4">
         <v>22.83</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="E4" t="str">
+        <v>Manhattan</v>
+      </c>
+      <c r="F4" s="5">
+        <v>1694251</v>
+      </c>
+      <c r="G4" s="5">
+        <v>22.83</v>
+      </c>
+      <c r="H4" s="5">
+        <v>74211.607533946561</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>237</v>
       </c>
@@ -1457,8 +1669,20 @@
       <c r="C5">
         <v>42.1</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="E5" t="str">
+        <v>The Bronx</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1472654</v>
+      </c>
+      <c r="G5" s="5">
+        <v>42.1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>34979.904988123511</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1468,11 +1692,48 @@
       <c r="C6">
         <v>58.37</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="E8" t="e" cm="1">
-        <f t="array" ref="E8">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
-        <v>#VALUE!</v>
+      <c r="E6" t="str">
+        <v>Staten Island</v>
+      </c>
+      <c r="F6" s="5">
+        <v>495747</v>
+      </c>
+      <c r="G6" s="5">
+        <v>58.37</v>
+      </c>
+      <c r="H6" s="5">
+        <v>8493.1814288161731</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E8" t="str" cm="1">
+        <f t="array" ref="E8:E13">_xlfn.CHOOSECOLS(_xlfn.ANCHORARRAY(E1), 2)</f>
+        <v>population</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E9">
+        <v>2736074</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E10">
+        <v>2405464</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E11">
+        <v>1694251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E12">
+        <v>1472654</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="E13">
+        <v>495747</v>
       </c>
     </row>
   </sheetData>
@@ -1486,7 +1747,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G201"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -1497,7 +1758,7 @@
     <col min="7" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1520,7 +1781,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1543,7 +1804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1566,7 +1827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1589,7 +1850,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -1612,7 +1873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1635,7 +1896,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1658,7 +1919,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1681,7 +1942,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1704,7 +1965,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -1727,7 +1988,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1750,7 +2011,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1773,7 +2034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1796,7 +2057,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1819,7 +2080,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
         <v>41</v>
       </c>
@@ -1842,7 +2103,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A16" t="s">
         <v>43</v>
       </c>
@@ -1865,7 +2126,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1888,7 +2149,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1911,7 +2172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1934,7 +2195,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1957,7 +2218,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1980,7 +2241,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -2003,7 +2264,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2026,7 +2287,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2049,7 +2310,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2072,7 +2333,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -2095,7 +2356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -2118,7 +2379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -2141,7 +2402,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -2164,7 +2425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A30" t="s">
         <v>62</v>
       </c>
@@ -2187,7 +2448,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -2210,7 +2471,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A32" t="s">
         <v>65</v>
       </c>
@@ -2233,7 +2494,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A33" t="s">
         <v>66</v>
       </c>
@@ -2256,7 +2517,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -2279,7 +2540,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -2302,7 +2563,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -2325,7 +2586,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A37" t="s">
         <v>70</v>
       </c>
@@ -2348,7 +2609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -2371,7 +2632,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -2394,7 +2655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A40" t="s">
         <v>74</v>
       </c>
@@ -2417,7 +2678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -2440,7 +2701,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A42" t="s">
         <v>77</v>
       </c>
@@ -2463,7 +2724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A43" t="s">
         <v>78</v>
       </c>
@@ -2486,7 +2747,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A44" t="s">
         <v>79</v>
       </c>
@@ -2509,7 +2770,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A45" t="s">
         <v>80</v>
       </c>
@@ -2532,7 +2793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A46" t="s">
         <v>81</v>
       </c>
@@ -2555,7 +2816,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A47" t="s">
         <v>82</v>
       </c>
@@ -2578,7 +2839,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A48" t="s">
         <v>83</v>
       </c>
@@ -2601,7 +2862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A49" t="s">
         <v>84</v>
       </c>
@@ -2624,7 +2885,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A50" t="s">
         <v>85</v>
       </c>
@@ -2647,7 +2908,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -2670,7 +2931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A52" t="s">
         <v>87</v>
       </c>
@@ -2693,7 +2954,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A53" t="s">
         <v>88</v>
       </c>
@@ -2716,7 +2977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A54" t="s">
         <v>89</v>
       </c>
@@ -2739,7 +3000,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A55" t="s">
         <v>90</v>
       </c>
@@ -2762,7 +3023,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A56" t="s">
         <v>91</v>
       </c>
@@ -2785,7 +3046,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A57" t="s">
         <v>92</v>
       </c>
@@ -2808,7 +3069,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A58" t="s">
         <v>93</v>
       </c>
@@ -2831,7 +3092,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A59" t="s">
         <v>94</v>
       </c>
@@ -2854,7 +3115,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A60" t="s">
         <v>95</v>
       </c>
@@ -2877,7 +3138,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A61" t="s">
         <v>96</v>
       </c>
@@ -2900,7 +3161,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A62" t="s">
         <v>97</v>
       </c>
@@ -2923,7 +3184,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A63" t="s">
         <v>98</v>
       </c>
@@ -2946,7 +3207,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A64" t="s">
         <v>99</v>
       </c>
@@ -2969,7 +3230,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A65" t="s">
         <v>100</v>
       </c>
@@ -2992,7 +3253,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A66" t="s">
         <v>101</v>
       </c>
@@ -3012,7 +3273,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A67" t="s">
         <v>102</v>
       </c>
@@ -3035,7 +3296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A68" t="s">
         <v>103</v>
       </c>
@@ -3058,7 +3319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A69" t="s">
         <v>104</v>
       </c>
@@ -3081,7 +3342,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A70" t="s">
         <v>105</v>
       </c>
@@ -3104,7 +3365,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A71" t="s">
         <v>106</v>
       </c>
@@ -3127,7 +3388,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A72" t="s">
         <v>107</v>
       </c>
@@ -3150,7 +3411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A73" t="s">
         <v>108</v>
       </c>
@@ -3173,7 +3434,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A74" t="s">
         <v>109</v>
       </c>
@@ -3196,7 +3457,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A75" t="s">
         <v>110</v>
       </c>
@@ -3219,7 +3480,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A76" t="s">
         <v>111</v>
       </c>
@@ -3242,7 +3503,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -3265,7 +3526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A78" t="s">
         <v>113</v>
       </c>
@@ -3288,7 +3549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A79" t="s">
         <v>114</v>
       </c>
@@ -3311,7 +3572,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A80" t="s">
         <v>115</v>
       </c>
@@ -3334,7 +3595,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A81" t="s">
         <v>116</v>
       </c>
@@ -3357,7 +3618,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A82" t="s">
         <v>117</v>
       </c>
@@ -3380,7 +3641,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A83" t="s">
         <v>118</v>
       </c>
@@ -3403,7 +3664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A84" t="s">
         <v>119</v>
       </c>
@@ -3426,7 +3687,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A85" t="s">
         <v>120</v>
       </c>
@@ -3449,7 +3710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A86" t="s">
         <v>121</v>
       </c>
@@ -3472,7 +3733,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A87" t="s">
         <v>122</v>
       </c>
@@ -3495,7 +3756,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A88" t="s">
         <v>123</v>
       </c>
@@ -3518,7 +3779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A89" t="s">
         <v>124</v>
       </c>
@@ -3541,7 +3802,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A90" t="s">
         <v>125</v>
       </c>
@@ -3564,7 +3825,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A91" t="s">
         <v>126</v>
       </c>
@@ -3587,7 +3848,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A92" t="s">
         <v>127</v>
       </c>
@@ -3610,7 +3871,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A93" t="s">
         <v>128</v>
       </c>
@@ -3633,7 +3894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A94" t="s">
         <v>129</v>
       </c>
@@ -3656,7 +3917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A95" t="s">
         <v>130</v>
       </c>
@@ -3679,7 +3940,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A96" t="s">
         <v>131</v>
       </c>
@@ -3702,7 +3963,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A97" t="s">
         <v>132</v>
       </c>
@@ -3725,7 +3986,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A98" t="s">
         <v>133</v>
       </c>
@@ -3748,7 +4009,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A99" t="s">
         <v>134</v>
       </c>
@@ -3771,7 +4032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A100" t="s">
         <v>135</v>
       </c>
@@ -3794,7 +4055,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A101" t="s">
         <v>136</v>
       </c>
@@ -3817,7 +4078,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A102" t="s">
         <v>137</v>
       </c>
@@ -3840,7 +4101,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A103" t="s">
         <v>138</v>
       </c>
@@ -3863,7 +4124,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A104" t="s">
         <v>139</v>
       </c>
@@ -3886,7 +4147,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A105" t="s">
         <v>140</v>
       </c>
@@ -3909,7 +4170,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A106" t="s">
         <v>141</v>
       </c>
@@ -3932,7 +4193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A107" t="s">
         <v>142</v>
       </c>
@@ -3955,7 +4216,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A108" t="s">
         <v>143</v>
       </c>
@@ -3978,7 +4239,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A109" t="s">
         <v>144</v>
       </c>
@@ -4001,7 +4262,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A110" t="s">
         <v>145</v>
       </c>
@@ -4024,7 +4285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A111" t="s">
         <v>146</v>
       </c>
@@ -4047,7 +4308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A112" t="s">
         <v>147</v>
       </c>
@@ -4070,7 +4331,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A113" t="s">
         <v>148</v>
       </c>
@@ -4093,7 +4354,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A114" t="s">
         <v>149</v>
       </c>
@@ -4116,7 +4377,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A115" t="s">
         <v>150</v>
       </c>
@@ -4139,7 +4400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A116" t="s">
         <v>151</v>
       </c>
@@ -4162,7 +4423,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A117" t="s">
         <v>152</v>
       </c>
@@ -4185,7 +4446,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A118" t="s">
         <v>153</v>
       </c>
@@ -4208,7 +4469,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A119" t="s">
         <v>154</v>
       </c>
@@ -4231,7 +4492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A120" t="s">
         <v>155</v>
       </c>
@@ -4254,7 +4515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A121" t="s">
         <v>156</v>
       </c>
@@ -4277,7 +4538,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A122" t="s">
         <v>157</v>
       </c>
@@ -4300,7 +4561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A123" t="s">
         <v>158</v>
       </c>
@@ -4323,7 +4584,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A124" t="s">
         <v>159</v>
       </c>
@@ -4346,7 +4607,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A125" t="s">
         <v>160</v>
       </c>
@@ -4369,7 +4630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A126" t="s">
         <v>161</v>
       </c>
@@ -4392,7 +4653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A127" t="s">
         <v>162</v>
       </c>
@@ -4415,7 +4676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A128" t="s">
         <v>163</v>
       </c>
@@ -4435,7 +4696,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A129" t="s">
         <v>164</v>
       </c>
@@ -4458,7 +4719,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A130" t="s">
         <v>165</v>
       </c>
@@ -4481,7 +4742,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A131" t="s">
         <v>166</v>
       </c>
@@ -4504,7 +4765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A132" t="s">
         <v>167</v>
       </c>
@@ -4527,7 +4788,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A133" t="s">
         <v>168</v>
       </c>
@@ -4550,7 +4811,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A134" t="s">
         <v>169</v>
       </c>
@@ -4573,7 +4834,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A135" t="s">
         <v>170</v>
       </c>
@@ -4596,7 +4857,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A136" t="s">
         <v>171</v>
       </c>
@@ -4619,7 +4880,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A137" t="s">
         <v>172</v>
       </c>
@@ -4642,7 +4903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A138" t="s">
         <v>173</v>
       </c>
@@ -4665,7 +4926,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A139" t="s">
         <v>174</v>
       </c>
@@ -4688,7 +4949,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A140" t="s">
         <v>175</v>
       </c>
@@ -4711,7 +4972,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A141" t="s">
         <v>176</v>
       </c>
@@ -4734,7 +4995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A142" t="s">
         <v>177</v>
       </c>
@@ -4757,7 +5018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A143" t="s">
         <v>178</v>
       </c>
@@ -4780,7 +5041,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A144" t="s">
         <v>179</v>
       </c>
@@ -4803,7 +5064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A145" t="s">
         <v>180</v>
       </c>
@@ -4826,7 +5087,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A146" t="s">
         <v>181</v>
       </c>
@@ -4849,7 +5110,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A147" t="s">
         <v>182</v>
       </c>
@@ -4872,7 +5133,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A148" t="s">
         <v>183</v>
       </c>
@@ -4895,7 +5156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A149" t="s">
         <v>184</v>
       </c>
@@ -4915,7 +5176,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A150" t="s">
         <v>185</v>
       </c>
@@ -4938,7 +5199,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A151" t="s">
         <v>186</v>
       </c>
@@ -4961,7 +5222,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A152" t="s">
         <v>187</v>
       </c>
@@ -4984,7 +5245,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A153" t="s">
         <v>188</v>
       </c>
@@ -5007,7 +5268,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A154" t="s">
         <v>189</v>
       </c>
@@ -5030,7 +5291,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A155" t="s">
         <v>190</v>
       </c>
@@ -5053,7 +5314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A156" t="s">
         <v>191</v>
       </c>
@@ -5073,7 +5334,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A157" t="s">
         <v>192</v>
       </c>
@@ -5096,7 +5357,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A158" t="s">
         <v>193</v>
       </c>
@@ -5119,7 +5380,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A159" t="s">
         <v>194</v>
       </c>
@@ -5142,7 +5403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A160" t="s">
         <v>195</v>
       </c>
@@ -5165,7 +5426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A161" t="s">
         <v>196</v>
       </c>
@@ -5188,7 +5449,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A162" t="s">
         <v>197</v>
       </c>
@@ -5211,7 +5472,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A163" t="s">
         <v>198</v>
       </c>
@@ -5234,7 +5495,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A164" t="s">
         <v>199</v>
       </c>
@@ -5254,7 +5515,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A165" t="s">
         <v>200</v>
       </c>
@@ -5277,7 +5538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A166" t="s">
         <v>201</v>
       </c>
@@ -5300,7 +5561,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A167" t="s">
         <v>202</v>
       </c>
@@ -5323,7 +5584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A168" t="s">
         <v>203</v>
       </c>
@@ -5346,7 +5607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A169" t="s">
         <v>204</v>
       </c>
@@ -5369,7 +5630,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A170" t="s">
         <v>205</v>
       </c>
@@ -5392,7 +5653,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A171" t="s">
         <v>206</v>
       </c>
@@ -5415,7 +5676,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A172" t="s">
         <v>207</v>
       </c>
@@ -5438,7 +5699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A173" t="s">
         <v>208</v>
       </c>
@@ -5458,7 +5719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A174" t="s">
         <v>209</v>
       </c>
@@ -5481,7 +5742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A175" t="s">
         <v>210</v>
       </c>
@@ -5504,7 +5765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A176" t="s">
         <v>211</v>
       </c>
@@ -5527,7 +5788,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A177" t="s">
         <v>212</v>
       </c>
@@ -5550,7 +5811,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A178" t="s">
         <v>213</v>
       </c>
@@ -5573,7 +5834,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A179" t="s">
         <v>214</v>
       </c>
@@ -5596,7 +5857,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A180" t="s">
         <v>215</v>
       </c>
@@ -5619,7 +5880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A181" t="s">
         <v>216</v>
       </c>
@@ -5642,7 +5903,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A182" t="s">
         <v>217</v>
       </c>
@@ -5665,7 +5926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A183" t="s">
         <v>218</v>
       </c>
@@ -5688,7 +5949,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A184" t="s">
         <v>219</v>
       </c>
@@ -5711,7 +5972,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A185" t="s">
         <v>220</v>
       </c>
@@ -5734,7 +5995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A186" t="s">
         <v>221</v>
       </c>
@@ -5757,7 +6018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A187" t="s">
         <v>222</v>
       </c>
@@ -5780,7 +6041,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A188" t="s">
         <v>223</v>
       </c>
@@ -5803,7 +6064,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A189" t="s">
         <v>224</v>
       </c>
@@ -5826,7 +6087,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A190" t="s">
         <v>225</v>
       </c>
@@ -5849,7 +6110,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A191" t="s">
         <v>226</v>
       </c>
@@ -5872,7 +6133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A192" t="s">
         <v>227</v>
       </c>
@@ -5895,7 +6156,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A193" t="s">
         <v>228</v>
       </c>
@@ -5918,7 +6179,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A194" t="s">
         <v>229</v>
       </c>
@@ -5941,7 +6202,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A195" t="s">
         <v>230</v>
       </c>
@@ -5964,7 +6225,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A196" t="s">
         <v>231</v>
       </c>
@@ -5987,7 +6248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A197" t="s">
         <v>232</v>
       </c>
@@ -6010,7 +6271,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A198" t="s">
         <v>233</v>
       </c>
@@ -6033,7 +6294,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A199" t="s">
         <v>234</v>
       </c>
@@ -6056,7 +6317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A200" t="s">
         <v>235</v>
       </c>
@@ -6079,7 +6340,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.5">
       <c r="A201" t="s">
         <v>236</v>
       </c>
@@ -6112,167 +6373,2578 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E979612-8BD7-40EA-9D5A-2165C0273E84}">
-  <dimension ref="A1:A178"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H184"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="23.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.265625" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.19921875" customWidth="1"/>
-    <col min="6" max="6" width="11.9296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.41015625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.234375" customWidth="1"/>
+    <col min="4" max="4" width="12.41015625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.17578125" customWidth="1"/>
+    <col min="6" max="6" width="11.9375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13.9296875" customWidth="1"/>
+    <col min="8" max="8" width="13.9375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A1" t="e" cm="1" vm="1">
         <f t="array" ref="A1">_xlfn._xlws.PY(1,1,sales[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" t="e" cm="1" vm="1">
-        <f t="array" ref="A3">_xlfn._xlws.PY(2,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" t="e" cm="1" vm="1">
-        <f t="array" ref="A10">_xlfn._xlws.PY(3,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" t="e" cm="1" vm="1">
-        <f t="array" ref="A17">_xlfn._xlws.PY(4,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A24" t="e" cm="1" vm="1">
-        <f t="array" ref="A24">_xlfn._xlws.PY(5,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A32" t="e" cm="1" vm="1">
-        <f t="array" ref="A32">_xlfn._xlws.PY(6,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A40" t="e" cm="1" vm="1">
-        <f t="array" ref="A40">_xlfn._xlws.PY(7,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A43" t="e" cm="1" vm="1">
-        <f t="array" ref="A43">_xlfn._xlws.PY(8,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A53" t="e" cm="1" vm="1">
-        <f t="array" ref="A53">_xlfn._xlws.PY(9,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A63" t="e" cm="1" vm="1">
-        <f t="array" ref="A63">_xlfn._xlws.PY(10,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A69" t="e" cm="1" vm="1">
-        <f t="array" ref="A69">_xlfn._xlws.PY(11,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A76" t="e" cm="1" vm="1">
-        <f t="array" ref="A76">_xlfn._xlws.PY(12,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A84" t="e" cm="1" vm="1">
-        <f t="array" ref="A84">_xlfn._xlws.PY(13,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A91" t="e" cm="1" vm="1">
-        <f t="array" ref="A91">_xlfn._xlws.PY(14,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A98" t="e" cm="1" vm="1">
-        <f t="array" ref="A98">_xlfn._xlws.PY(15,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A105" t="e" cm="1" vm="1">
-        <f t="array" ref="A105">_xlfn._xlws.PY(16,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A113" t="e" cm="1" vm="1">
-        <f t="array" ref="A113">_xlfn._xlws.PY(17,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A121" t="e" cm="1" vm="1">
-        <f t="array" ref="A121">_xlfn._xlws.PY(18,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A129" t="e" cm="1" vm="1">
-        <f t="array" ref="A129">_xlfn._xlws.PY(19,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A136" t="e" cm="1" vm="1">
-        <f t="array" ref="A136">_xlfn._xlws.PY(20,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A144" t="e" cm="1" vm="1">
-        <f t="array" ref="A144">_xlfn._xlws.PY(21,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A149" t="e" cm="1" vm="1">
-        <f t="array" ref="A149">_xlfn._xlws.PY(22,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A156" t="e" cm="1" vm="1">
-        <f t="array" ref="A156">_xlfn._xlws.PY(23,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A161" t="e" cm="1" vm="1">
-        <f t="array" ref="A161">_xlfn._xlws.PY(24,0)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A178" t="e" cm="1" vm="1">
-        <f t="array" ref="A178">_xlfn._xlws.PY(25,0)</f>
-        <v>#VALUE!</v>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:G8">_xlfn._xlws.PY(2,0)</f>
+        <v>order_id</v>
+      </c>
+      <c r="B3" t="str">
+        <v>product</v>
+      </c>
+      <c r="C3" t="str">
+        <v>category</v>
+      </c>
+      <c r="D3" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="E3" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="F3" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="G3" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A4" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="D4">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>37</v>
+      </c>
+      <c r="G4" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A5" t="str">
+        <v>ORD-0002</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="D5">
+        <v>115.2</v>
+      </c>
+      <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
+        <v>24</v>
+      </c>
+      <c r="G5" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A6" t="str">
+        <v>ORD-0003</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="D6">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>63</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A7" t="str">
+        <v>ORD-0004</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="D7">
+        <v>15.35</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>32</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A8" t="str">
+        <v>ORD-0005</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="D8">
+        <v>479.68</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>28</v>
+      </c>
+      <c r="G8" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A10" t="str" cm="1">
+        <f t="array" ref="A10:H15">_xlfn._xlws.PY(3,0)</f>
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C10" t="str">
+        <v>product</v>
+      </c>
+      <c r="D10" t="str">
+        <v>category</v>
+      </c>
+      <c r="E10" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F10" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G10" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H10" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A11">
+        <v>195</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ORD-0196</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Headphones</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E11">
+        <v>162.49</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>22</v>
+      </c>
+      <c r="H11" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A12">
+        <v>196</v>
+      </c>
+      <c r="B12" t="str">
+        <v>ORD-0197</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Monitor</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E12">
+        <v>277.98</v>
+      </c>
+      <c r="F12">
+        <v>4</v>
+      </c>
+      <c r="G12">
+        <v>54</v>
+      </c>
+      <c r="H12" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A13">
+        <v>197</v>
+      </c>
+      <c r="B13" t="str">
+        <v>ORD-0198</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Printer Paper</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E13">
+        <v>21.06</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>49</v>
+      </c>
+      <c r="H13" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A14">
+        <v>198</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ORD-0199</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E14">
+        <v>22.61</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>62</v>
+      </c>
+      <c r="H14" t="str">
+        <v>United Kingdom</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A15">
+        <v>199</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ORD-0200</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Headphones</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E15">
+        <v>106.64</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>51</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A17" t="str" cm="1">
+        <f t="array" ref="A17:H22">_xlfn._xlws.PY(4,0)</f>
+        <v/>
+      </c>
+      <c r="B17" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C17" t="str">
+        <v>product</v>
+      </c>
+      <c r="D17" t="str">
+        <v>category</v>
+      </c>
+      <c r="E17" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F17" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G17" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H17" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A18">
+        <v>163</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ORD-0164</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Printer Paper</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E18">
+        <v>6.67</v>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>30</v>
+      </c>
+      <c r="H18" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A19">
+        <v>98</v>
+      </c>
+      <c r="B19" t="str">
+        <v>ORD-0099</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Monitor</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E19">
+        <v>125.76</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>43</v>
+      </c>
+      <c r="H19" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A20">
+        <v>67</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ORD-0068</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E20">
+        <v>301.39</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20">
+        <v>65</v>
+      </c>
+      <c r="H20" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A21">
+        <v>109</v>
+      </c>
+      <c r="B21" t="str">
+        <v>ORD-0110</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Laptop</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E21">
+        <v>215.34</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21">
+        <v>58</v>
+      </c>
+      <c r="H21" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A22">
+        <v>8</v>
+      </c>
+      <c r="B22" t="str">
+        <v>ORD-0009</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Binder</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E22">
+        <v>9.81</v>
+      </c>
+      <c r="F22">
+        <v>6</v>
+      </c>
+      <c r="G22">
+        <v>35</v>
+      </c>
+      <c r="H22" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A24" t="str" cm="1">
+        <f t="array" ref="A24:B30">_xlfn._xlws.PY(5,0)</f>
+        <v>order_id</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A25" t="str">
+        <v>product</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A26" t="str">
+        <v>category</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A27" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A28" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A29" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="B29">
+        <v>2.9999999999999997E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A30" t="str">
+        <v>country</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A32" t="str" cm="1">
+        <f t="array" ref="A32:B38">_xlfn._xlws.PY(6,0)</f>
+        <v>customer_age</v>
+      </c>
+      <c r="B32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A33" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A34" t="str">
+        <v>product</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A35" t="str">
+        <v>category</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A36" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A37" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A38" t="str">
+        <v>country</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A40" cm="1">
+        <f t="array" ref="A40:A41">_xlfn._xlws.PY(7,0)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A43" t="str" cm="1">
+        <f t="array" ref="A43:D51">_xlfn._xlws.PY(8,0)</f>
+        <v/>
+      </c>
+      <c r="B43" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="C43" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="D43" t="str">
+        <v>customer_age</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A44" t="str">
+        <v>count</v>
+      </c>
+      <c r="B44">
+        <v>200</v>
+      </c>
+      <c r="C44">
+        <v>200</v>
+      </c>
+      <c r="D44">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A45" t="str">
+        <v>mean</v>
+      </c>
+      <c r="B45">
+        <v>211.94830000000002</v>
+      </c>
+      <c r="C45">
+        <v>5.7</v>
+      </c>
+      <c r="D45">
+        <v>43.597938144329895</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A46" t="str">
+        <v>std</v>
+      </c>
+      <c r="B46">
+        <v>215.73323312713649</v>
+      </c>
+      <c r="C46">
+        <v>2.7252771745993041</v>
+      </c>
+      <c r="D46">
+        <v>13.286527356620564</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A47" t="str">
+        <v>min</v>
+      </c>
+      <c r="B47">
+        <v>2.17</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A48" t="str">
+        <v>25%</v>
+      </c>
+      <c r="B48">
+        <v>31.2075</v>
+      </c>
+      <c r="C48">
+        <v>4</v>
+      </c>
+      <c r="D48">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A49" t="str">
+        <v>50%</v>
+      </c>
+      <c r="B49">
+        <v>111.38</v>
+      </c>
+      <c r="C49">
+        <v>5.5</v>
+      </c>
+      <c r="D49">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A50" t="str">
+        <v>75%</v>
+      </c>
+      <c r="B50">
+        <v>378.83</v>
+      </c>
+      <c r="C50">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>55.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A51" t="str">
+        <v>max</v>
+      </c>
+      <c r="B51">
+        <v>760.69</v>
+      </c>
+      <c r="C51">
+        <v>10</v>
+      </c>
+      <c r="D51">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A53" t="str" cm="1">
+        <f t="array" ref="A53:D61">_xlfn._xlws.PY(9,0)</f>
+        <v/>
+      </c>
+      <c r="B53" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="C53" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="D53" t="str">
+        <v>customer_age</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A54" t="str">
+        <v>count</v>
+      </c>
+      <c r="B54">
+        <v>200</v>
+      </c>
+      <c r="C54">
+        <v>200</v>
+      </c>
+      <c r="D54">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A55" t="str">
+        <v>mean</v>
+      </c>
+      <c r="B55">
+        <v>211.94830000000002</v>
+      </c>
+      <c r="C55">
+        <v>5.7</v>
+      </c>
+      <c r="D55">
+        <v>43.597938144329895</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A56" t="str">
+        <v>std</v>
+      </c>
+      <c r="B56">
+        <v>215.73323312713649</v>
+      </c>
+      <c r="C56">
+        <v>2.7252771745993041</v>
+      </c>
+      <c r="D56">
+        <v>13.286527356620564</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A57" t="str">
+        <v>min</v>
+      </c>
+      <c r="B57">
+        <v>2.17</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A58" t="str">
+        <v>10%</v>
+      </c>
+      <c r="B58">
+        <v>13.033000000000001</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A59" t="str">
+        <v>50%</v>
+      </c>
+      <c r="B59">
+        <v>111.38</v>
+      </c>
+      <c r="C59">
+        <v>5.5</v>
+      </c>
+      <c r="D59">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A60" t="str">
+        <v>90%</v>
+      </c>
+      <c r="B60">
+        <v>512.85599999999999</v>
+      </c>
+      <c r="C60">
+        <v>9.0999999999999943</v>
+      </c>
+      <c r="D60">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A61" t="str">
+        <v>max</v>
+      </c>
+      <c r="B61">
+        <v>760.69</v>
+      </c>
+      <c r="C61">
+        <v>10</v>
+      </c>
+      <c r="D61">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A63" t="str" cm="1">
+        <f t="array" ref="A63:E67">_xlfn._xlws.PY(10,0)</f>
+        <v/>
+      </c>
+      <c r="B63" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C63" t="str">
+        <v>product</v>
+      </c>
+      <c r="D63" t="str">
+        <v>category</v>
+      </c>
+      <c r="E63" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A64" t="str">
+        <v>count</v>
+      </c>
+      <c r="B64">
+        <v>200</v>
+      </c>
+      <c r="C64">
+        <v>200</v>
+      </c>
+      <c r="D64">
+        <v>200</v>
+      </c>
+      <c r="E64">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A65" t="str">
+        <v>unique</v>
+      </c>
+      <c r="B65">
+        <v>200</v>
+      </c>
+      <c r="C65">
+        <v>15</v>
+      </c>
+      <c r="D65">
+        <v>3</v>
+      </c>
+      <c r="E65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A66" t="str">
+        <v>top</v>
+      </c>
+      <c r="B66" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E66" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A67" t="str">
+        <v>freq</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>19</v>
+      </c>
+      <c r="D67">
+        <v>80</v>
+      </c>
+      <c r="E67">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A69" t="str" cm="1">
+        <f t="array" ref="A69:C74">_xlfn._xlws.PY(11,0)</f>
+        <v>product</v>
+      </c>
+      <c r="B69" t="str">
+        <v>category</v>
+      </c>
+      <c r="C69" t="str">
+        <v>unit_price</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A70" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C70">
+        <v>68.760000000000005</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A71" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C71">
+        <v>115.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A72" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C72">
+        <v>69.900000000000006</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A73" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C73">
+        <v>15.35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A74" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C74">
+        <v>479.68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A76" t="str" cm="1">
+        <f t="array" ref="A76:A81">_xlfn._xlws.PY(12,0)</f>
+        <v>country</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A77" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A78" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A79" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A80" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A81" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A84" t="str" cm="1">
+        <f t="array" ref="A84:H89">_xlfn._xlws.PY(13,0)</f>
+        <v/>
+      </c>
+      <c r="B84" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C84" t="str">
+        <v>product</v>
+      </c>
+      <c r="D84" t="str">
+        <v>category</v>
+      </c>
+      <c r="E84" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F84" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G84" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H84" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A85">
+        <v>0</v>
+      </c>
+      <c r="B85" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E85">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="F85">
+        <v>5</v>
+      </c>
+      <c r="G85">
+        <v>37</v>
+      </c>
+      <c r="H85" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A86">
+        <v>1</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ORD-0002</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E86">
+        <v>115.2</v>
+      </c>
+      <c r="F86">
+        <v>7</v>
+      </c>
+      <c r="G86">
+        <v>24</v>
+      </c>
+      <c r="H86" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A87">
+        <v>4</v>
+      </c>
+      <c r="B87" t="str">
+        <v>ORD-0005</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E87">
+        <v>479.68</v>
+      </c>
+      <c r="F87">
+        <v>6</v>
+      </c>
+      <c r="G87">
+        <v>28</v>
+      </c>
+      <c r="H87" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A88">
+        <v>11</v>
+      </c>
+      <c r="B88" t="str">
+        <v>ORD-0012</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E88">
+        <v>415.36</v>
+      </c>
+      <c r="F88">
+        <v>6</v>
+      </c>
+      <c r="G88">
+        <v>47</v>
+      </c>
+      <c r="H88" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A89">
+        <v>13</v>
+      </c>
+      <c r="B89" t="str">
+        <v>ORD-0014</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Headphones</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E89">
+        <v>91.32</v>
+      </c>
+      <c r="F89">
+        <v>9</v>
+      </c>
+      <c r="G89">
+        <v>56</v>
+      </c>
+      <c r="H89" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A91" t="str" cm="1">
+        <f t="array" ref="A91:H96">_xlfn._xlws.PY(14,0)</f>
+        <v/>
+      </c>
+      <c r="B91" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C91" t="str">
+        <v>product</v>
+      </c>
+      <c r="D91" t="str">
+        <v>category</v>
+      </c>
+      <c r="E91" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F91" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G91" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H91" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A92">
+        <v>0</v>
+      </c>
+      <c r="B92" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E92">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="F92">
+        <v>5</v>
+      </c>
+      <c r="G92">
+        <v>37</v>
+      </c>
+      <c r="H92" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A93">
+        <v>1</v>
+      </c>
+      <c r="B93" t="str">
+        <v>ORD-0002</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E93">
+        <v>115.2</v>
+      </c>
+      <c r="F93">
+        <v>7</v>
+      </c>
+      <c r="G93">
+        <v>24</v>
+      </c>
+      <c r="H93" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A94">
+        <v>4</v>
+      </c>
+      <c r="B94" t="str">
+        <v>ORD-0005</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E94">
+        <v>479.68</v>
+      </c>
+      <c r="F94">
+        <v>6</v>
+      </c>
+      <c r="G94">
+        <v>28</v>
+      </c>
+      <c r="H94" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A95">
+        <v>11</v>
+      </c>
+      <c r="B95" t="str">
+        <v>ORD-0012</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E95">
+        <v>415.36</v>
+      </c>
+      <c r="F95">
+        <v>6</v>
+      </c>
+      <c r="G95">
+        <v>47</v>
+      </c>
+      <c r="H95" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A96">
+        <v>13</v>
+      </c>
+      <c r="B96" t="str">
+        <v>ORD-0014</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Headphones</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E96">
+        <v>91.32</v>
+      </c>
+      <c r="F96">
+        <v>9</v>
+      </c>
+      <c r="G96">
+        <v>56</v>
+      </c>
+      <c r="H96" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A98" t="str" cm="1">
+        <f t="array" ref="A98:H103">_xlfn._xlws.PY(15,0)</f>
+        <v/>
+      </c>
+      <c r="B98" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C98" t="str">
+        <v>product</v>
+      </c>
+      <c r="D98" t="str">
+        <v>category</v>
+      </c>
+      <c r="E98" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F98" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G98" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H98" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A99">
+        <v>0</v>
+      </c>
+      <c r="B99" t="str">
+        <v>ORD-0001</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E99">
+        <v>68.760000000000005</v>
+      </c>
+      <c r="F99">
+        <v>5</v>
+      </c>
+      <c r="G99">
+        <v>37</v>
+      </c>
+      <c r="H99" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A100">
+        <v>1</v>
+      </c>
+      <c r="B100" t="str">
+        <v>ORD-0002</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Lamp</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E100">
+        <v>115.2</v>
+      </c>
+      <c r="F100">
+        <v>7</v>
+      </c>
+      <c r="G100">
+        <v>24</v>
+      </c>
+      <c r="H100" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A101">
+        <v>4</v>
+      </c>
+      <c r="B101" t="str">
+        <v>ORD-0005</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E101">
+        <v>479.68</v>
+      </c>
+      <c r="F101">
+        <v>6</v>
+      </c>
+      <c r="G101">
+        <v>28</v>
+      </c>
+      <c r="H101" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A102">
+        <v>11</v>
+      </c>
+      <c r="B102" t="str">
+        <v>ORD-0012</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E102">
+        <v>415.36</v>
+      </c>
+      <c r="F102">
+        <v>6</v>
+      </c>
+      <c r="G102">
+        <v>47</v>
+      </c>
+      <c r="H102" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A103">
+        <v>13</v>
+      </c>
+      <c r="B103" t="str">
+        <v>ORD-0014</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Headphones</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E103">
+        <v>91.32</v>
+      </c>
+      <c r="F103">
+        <v>9</v>
+      </c>
+      <c r="G103">
+        <v>56</v>
+      </c>
+      <c r="H103" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A105" t="str" cm="1">
+        <f t="array" ref="A105:H110">_xlfn._xlws.PY(16,0)</f>
+        <v/>
+      </c>
+      <c r="B105" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C105" t="str">
+        <v>product</v>
+      </c>
+      <c r="D105" t="str">
+        <v>category</v>
+      </c>
+      <c r="E105" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F105" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G105" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H105" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A106">
+        <v>48</v>
+      </c>
+      <c r="B106" t="str">
+        <v>ORD-0049</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Printer Paper</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E106">
+        <v>2.17</v>
+      </c>
+      <c r="F106">
+        <v>3</v>
+      </c>
+      <c r="G106">
+        <v>62</v>
+      </c>
+      <c r="H106" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A107">
+        <v>79</v>
+      </c>
+      <c r="B107" t="str">
+        <v>ORD-0080</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Stapler</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E107">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="F107">
+        <v>6</v>
+      </c>
+      <c r="G107">
+        <v>41</v>
+      </c>
+      <c r="H107" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A108">
+        <v>99</v>
+      </c>
+      <c r="B108" t="str">
+        <v>ORD-0100</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E108">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="F108">
+        <v>4</v>
+      </c>
+      <c r="G108">
+        <v>27</v>
+      </c>
+      <c r="H108" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A109">
+        <v>142</v>
+      </c>
+      <c r="B109" t="str">
+        <v>ORD-0143</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E109">
+        <v>3.72</v>
+      </c>
+      <c r="F109">
+        <v>2</v>
+      </c>
+      <c r="G109">
+        <v>37</v>
+      </c>
+      <c r="H109" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A110">
+        <v>21</v>
+      </c>
+      <c r="B110" t="str">
+        <v>ORD-0022</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Pens</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E110">
+        <v>4.78</v>
+      </c>
+      <c r="F110">
+        <v>10</v>
+      </c>
+      <c r="G110">
+        <v>27</v>
+      </c>
+      <c r="H110" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A113" t="str" cm="1">
+        <f t="array" ref="A113:H118">_xlfn._xlws.PY(17,0)</f>
+        <v/>
+      </c>
+      <c r="B113" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C113" t="str">
+        <v>product</v>
+      </c>
+      <c r="D113" t="str">
+        <v>category</v>
+      </c>
+      <c r="E113" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F113" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G113" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H113" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>ORD-0114</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E114">
+        <v>760.69</v>
+      </c>
+      <c r="F114">
+        <v>4</v>
+      </c>
+      <c r="G114">
+        <v>62</v>
+      </c>
+      <c r="H114" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A115">
+        <v>165</v>
+      </c>
+      <c r="B115" t="str">
+        <v>ORD-0166</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Filing Cabinet</v>
+      </c>
+      <c r="D115" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E115">
+        <v>754.29</v>
+      </c>
+      <c r="F115">
+        <v>5</v>
+      </c>
+      <c r="G115">
+        <v>24</v>
+      </c>
+      <c r="H115" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A116">
+        <v>45</v>
+      </c>
+      <c r="B116" t="str">
+        <v>ORD-0046</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E116">
+        <v>754.2</v>
+      </c>
+      <c r="F116">
+        <v>3</v>
+      </c>
+      <c r="G116">
+        <v>38</v>
+      </c>
+      <c r="H116" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A117">
+        <v>40</v>
+      </c>
+      <c r="B117" t="str">
+        <v>ORD-0041</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Bookshelf</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E117">
+        <v>751.03</v>
+      </c>
+      <c r="F117">
+        <v>4</v>
+      </c>
+      <c r="G117">
+        <v>64</v>
+      </c>
+      <c r="H117" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A118">
+        <v>152</v>
+      </c>
+      <c r="B118" t="str">
+        <v>ORD-0153</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E118">
+        <v>732.96</v>
+      </c>
+      <c r="F118">
+        <v>8</v>
+      </c>
+      <c r="G118">
+        <v>40</v>
+      </c>
+      <c r="H118" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A121" t="str" cm="1">
+        <f t="array" ref="A121:H126">_xlfn._xlws.PY(18,0)</f>
+        <v/>
+      </c>
+      <c r="B121" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C121" t="str">
+        <v>product</v>
+      </c>
+      <c r="D121" t="str">
+        <v>category</v>
+      </c>
+      <c r="E121" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F121" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G121" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H121" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A122">
+        <v>48</v>
+      </c>
+      <c r="B122" t="str">
+        <v>ORD-0049</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Printer Paper</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E122">
+        <v>2.17</v>
+      </c>
+      <c r="F122">
+        <v>3</v>
+      </c>
+      <c r="G122">
+        <v>62</v>
+      </c>
+      <c r="H122" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A123">
+        <v>32</v>
+      </c>
+      <c r="B123" t="str">
+        <v>ORD-0033</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Notebook</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E123">
+        <v>6.7</v>
+      </c>
+      <c r="F123">
+        <v>9</v>
+      </c>
+      <c r="G123">
+        <v>22</v>
+      </c>
+      <c r="H123" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A124">
+        <v>119</v>
+      </c>
+      <c r="B124" t="str">
+        <v>ORD-0120</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Stapler</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E124">
+        <v>7.97</v>
+      </c>
+      <c r="F124">
+        <v>5</v>
+      </c>
+      <c r="G124">
+        <v>47</v>
+      </c>
+      <c r="H124" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A125">
+        <v>181</v>
+      </c>
+      <c r="B125" t="str">
+        <v>ORD-0182</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Binder</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="E125">
+        <v>19.97</v>
+      </c>
+      <c r="F125">
+        <v>3</v>
+      </c>
+      <c r="G125">
+        <v>65</v>
+      </c>
+      <c r="H125" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A126">
+        <v>34</v>
+      </c>
+      <c r="B126" t="str">
+        <v>ORD-0035</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Monitor</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="E126">
+        <v>26.02</v>
+      </c>
+      <c r="F126">
+        <v>7</v>
+      </c>
+      <c r="G126">
+        <v>38</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Australia</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A129" t="str" cm="1">
+        <f t="array" ref="A129:H134">_xlfn._xlws.PY(19,0)</f>
+        <v/>
+      </c>
+      <c r="B129" t="str">
+        <v>order_id</v>
+      </c>
+      <c r="C129" t="str">
+        <v>product</v>
+      </c>
+      <c r="D129" t="str">
+        <v>category</v>
+      </c>
+      <c r="E129" t="str">
+        <v>unit_price</v>
+      </c>
+      <c r="F129" t="str">
+        <v>quantity</v>
+      </c>
+      <c r="G129" t="str">
+        <v>customer_age</v>
+      </c>
+      <c r="H129" t="str">
+        <v>country</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A130">
+        <v>113</v>
+      </c>
+      <c r="B130" t="str">
+        <v>ORD-0114</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E130">
+        <v>760.69</v>
+      </c>
+      <c r="F130">
+        <v>4</v>
+      </c>
+      <c r="G130">
+        <v>62</v>
+      </c>
+      <c r="H130" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A131">
+        <v>165</v>
+      </c>
+      <c r="B131" t="str">
+        <v>ORD-0166</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Filing Cabinet</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E131">
+        <v>754.29</v>
+      </c>
+      <c r="F131">
+        <v>5</v>
+      </c>
+      <c r="G131">
+        <v>24</v>
+      </c>
+      <c r="H131" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A132">
+        <v>45</v>
+      </c>
+      <c r="B132" t="str">
+        <v>ORD-0046</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E132">
+        <v>754.2</v>
+      </c>
+      <c r="F132">
+        <v>3</v>
+      </c>
+      <c r="G132">
+        <v>38</v>
+      </c>
+      <c r="H132" t="str">
+        <v>United States</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A133">
+        <v>40</v>
+      </c>
+      <c r="B133" t="str">
+        <v>ORD-0041</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Bookshelf</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E133">
+        <v>751.03</v>
+      </c>
+      <c r="F133">
+        <v>4</v>
+      </c>
+      <c r="G133">
+        <v>64</v>
+      </c>
+      <c r="H133" t="str">
+        <v>Germany</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A134">
+        <v>152</v>
+      </c>
+      <c r="B134" t="str">
+        <v>ORD-0153</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Desk</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="E134">
+        <v>732.96</v>
+      </c>
+      <c r="F134">
+        <v>8</v>
+      </c>
+      <c r="G134">
+        <v>40</v>
+      </c>
+      <c r="H134" t="str">
+        <v>Canada</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A136" t="str" cm="1">
+        <f t="array" ref="A136:B141">_xlfn._xlws.PY(20,0)</f>
+        <v>country</v>
+      </c>
+      <c r="B136" t="str">
+        <v>count</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A137" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B137">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A138" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B138">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A139" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B139">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A140" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B140">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A141" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B141">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.5">
+      <c r="A144" t="str" cm="1">
+        <f t="array" ref="A144:B147">_xlfn._xlws.PY(21,0)</f>
+        <v>category</v>
+      </c>
+      <c r="B144" t="str">
+        <v>proportion</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A145" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="B145">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A146" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="B146">
+        <v>0.32500000000000001</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A147" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="B147">
+        <v>0.27500000000000002</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A149" t="str" cm="1">
+        <f t="array" ref="A149:B154">_xlfn._xlws.PY(22,0)</f>
+        <v>country</v>
+      </c>
+      <c r="B149" t="str">
+        <v>unit_price</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A150" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B150">
+        <v>167.16199999999998</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A151" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B151">
+        <v>201.18230769230769</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A152" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B152">
+        <v>182.58790697674419</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A153" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B153">
+        <v>274.43128205128204</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A154" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B154">
+        <v>209.05701298701297</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A156" t="str" cm="1">
+        <f t="array" ref="A156:B159">_xlfn._xlws.PY(23,0)</f>
+        <v>category</v>
+      </c>
+      <c r="B156" t="str">
+        <v>quantity</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A157" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="B157">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A158" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="B158">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.5">
+      <c r="A159" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="B159">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A161" t="str" cm="1">
+        <f t="array" ref="A161:C176">_xlfn._xlws.PY(24,0)</f>
+        <v>country</v>
+      </c>
+      <c r="B161" t="str">
+        <v>category</v>
+      </c>
+      <c r="C161" t="str">
+        <v>unit_price</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A162" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C162">
+        <v>270.6516666666667</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A163" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C163">
+        <v>256.68</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A164" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C164">
+        <v>18.91333333333333</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A165" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C165">
+        <v>274.04250000000002</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A166" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C166">
+        <v>529.45000000000005</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A167" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C167">
+        <v>30.088461538461541</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A168" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C168">
+        <v>230.67818181818183</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A169" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C169">
+        <v>350.0864285714286</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A170" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C170">
+        <v>22.922777777777778</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A171" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C171">
+        <v>272.95764705882351</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A172" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C172">
+        <v>529.8054545454545</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A173" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C173">
+        <v>21.334545454545456</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A174" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C174">
+        <v>296.6995652173913</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A175" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Furniture</v>
+      </c>
+      <c r="C175">
+        <v>383.92954545454546</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.5">
+      <c r="A176" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C176">
+        <v>25.839062500000001</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A178" t="str" cm="1">
+        <f t="array" ref="A178:D184">_xlfn._xlws.PY(25,0)</f>
+        <v/>
+      </c>
+      <c r="B178" t="str">
+        <v>mean</v>
+      </c>
+      <c r="C178" t="str">
+        <v>min</v>
+      </c>
+      <c r="D178" t="str">
+        <v>max</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A179" t="str">
+        <v>country</v>
+      </c>
+      <c r="B179" t="str">
+        <v/>
+      </c>
+      <c r="C179" t="str">
+        <v/>
+      </c>
+      <c r="D179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A180" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="B180">
+        <v>167.16199999999998</v>
+      </c>
+      <c r="C180">
+        <v>2.17</v>
+      </c>
+      <c r="D180">
+        <v>486.65</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A181" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="B181">
+        <v>201.18230769230769</v>
+      </c>
+      <c r="C181">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="D181">
+        <v>732.96</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A182" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B182">
+        <v>182.58790697674419</v>
+      </c>
+      <c r="C182">
+        <v>3.72</v>
+      </c>
+      <c r="D182">
+        <v>754.29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A183" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="B183">
+        <v>274.43128205128204</v>
+      </c>
+      <c r="C183">
+        <v>7.32</v>
+      </c>
+      <c r="D183">
+        <v>689.59</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A184" t="str">
+        <v>United States</v>
+      </c>
+      <c r="B184">
+        <v>209.05701298701297</v>
+      </c>
+      <c r="C184">
+        <v>2.4900000000000002</v>
+      </c>
+      <c r="D184">
+        <v>760.69</v>
       </c>
     </row>
   </sheetData>
